--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A28AE57-5FC4-44B8-9D1E-2785FF0A01AA}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88ECE4E8-38B4-48E6-9676-52B7E69AFAA0}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15725" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16079" uniqueCount="197">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -488,15 +488,6 @@
     <t>Racing Bulls</t>
   </si>
   <si>
-    <t>Tomas</t>
-  </si>
-  <si>
-    <t>Aston</t>
-  </si>
-  <si>
-    <t>red bull</t>
-  </si>
-  <si>
     <t>xx</t>
   </si>
   <si>
@@ -709,7 +700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -720,11 +711,292 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="44">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="6" tint="0.39997558519241921"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -764,10 +1036,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16469,9 +16737,9 @@
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{92556F97-259D-4A7E-93EF-C3265CCF3547}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" gridDropZones="1" multipleFieldFilters="0">
-  <location ref="A9:C18" firstHeaderRow="2" firstDataRow="2" firstDataCol="2" rowPageCount="6" colPageCount="1"/>
+  <location ref="A10:D327" firstHeaderRow="2" firstDataRow="2" firstDataCol="3" rowPageCount="5" colPageCount="1"/>
   <pivotFields count="9">
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
       <items count="6">
         <item x="0"/>
         <item x="1"/>
@@ -16514,38 +16782,38 @@
         <item x="27"/>
       </items>
     </pivotField>
-    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
       <items count="27">
         <item x="26"/>
-        <item h="1" x="8"/>
-        <item h="1" x="25"/>
-        <item h="1" x="14"/>
-        <item h="1" x="24"/>
-        <item h="1" x="2"/>
-        <item h="1" x="5"/>
-        <item h="1" x="23"/>
-        <item h="1" x="19"/>
-        <item h="1" x="12"/>
-        <item h="1" x="20"/>
-        <item h="1" x="9"/>
-        <item h="1" x="18"/>
-        <item h="1" x="13"/>
-        <item h="1" x="0"/>
-        <item h="1" x="1"/>
-        <item h="1" x="21"/>
-        <item h="1" x="3"/>
-        <item h="1" x="6"/>
-        <item h="1" x="11"/>
-        <item h="1" x="10"/>
-        <item h="1" x="17"/>
-        <item h="1" x="16"/>
-        <item h="1" x="7"/>
-        <item h="1" x="22"/>
-        <item h="1" x="4"/>
-        <item h="1" x="15"/>
+        <item x="8"/>
+        <item x="25"/>
+        <item x="14"/>
+        <item x="24"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="23"/>
+        <item x="19"/>
+        <item x="12"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="18"/>
+        <item x="13"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="21"/>
+        <item x="3"/>
+        <item x="6"/>
+        <item x="11"/>
+        <item x="10"/>
+        <item x="17"/>
+        <item x="16"/>
+        <item x="7"/>
+        <item x="22"/>
+        <item x="4"/>
+        <item x="15"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
       <items count="19">
         <item x="1"/>
         <item x="2"/>
@@ -16568,10 +16836,10 @@
         <item x="0"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
       <items count="25">
         <item x="21"/>
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item x="14"/>
         <item x="9"/>
         <item x="6"/>
@@ -16597,7 +16865,7 @@
         <item x="20"/>
       </items>
     </pivotField>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0">
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0" sortType="descending" defaultSubtotal="0">
       <items count="37">
         <item x="26"/>
         <item x="31"/>
@@ -16690,38 +16958,1010 @@
     </pivotField>
     <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
   </pivotFields>
-  <rowFields count="2">
-    <field x="3"/>
-    <field x="4"/>
+  <rowFields count="3">
+    <field x="2"/>
+    <field x="0"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="8">
+  <rowItems count="316">
     <i>
+      <x/>
+      <x v="5"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="28"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="10"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="25"/>
+    </i>
+    <i r="2">
+      <x v="13"/>
+    </i>
+    <i r="2">
+      <x v="27"/>
+    </i>
+    <i r="2">
+      <x v="20"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="1"/>
+      <x v="1"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i>
+      <x v="2"/>
+      <x v="5"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="1"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="28"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="25"/>
+    </i>
+    <i r="2">
+      <x v="20"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="13"/>
+    </i>
+    <i r="2">
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="3"/>
+      <x v="1"/>
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="4"/>
+      <x v="4"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="28"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="21"/>
+    </i>
+    <i r="2">
+      <x v="12"/>
+    </i>
+    <i r="2">
+      <x v="25"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="35"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="5"/>
+      <x/>
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="6"/>
       <x/>
       <x v="8"/>
     </i>
-    <i>
-      <x v="1"/>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
       <x v="6"/>
     </i>
     <i>
+      <x v="7"/>
+      <x v="3"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="15"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="35"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i r="2">
+      <x v="12"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i>
+      <x v="8"/>
       <x v="2"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="33"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="26"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="9"/>
+      <x v="1"/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="10"/>
+      <x v="2"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="33"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="26"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="11"/>
+      <x v="1"/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
       <x v="15"/>
     </i>
     <i>
+      <x v="12"/>
+      <x v="2"/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
       <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="26"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="13"/>
+      <x v="1"/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="14"/>
+      <x/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="31"/>
+    </i>
+    <i>
+      <x v="15"/>
+      <x/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="16"/>
+      <x v="2"/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="26"/>
+    </i>
+    <i>
+      <x v="17"/>
+      <x/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="18"/>
+      <x v="1"/>
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="31"/>
+    </i>
+    <i r="2">
+      <x v="33"/>
+    </i>
+    <i>
+      <x v="19"/>
+      <x v="1"/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
       <x v="5"/>
     </i>
     <i>
-      <x v="4"/>
+      <x v="20"/>
+      <x v="1"/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="21"/>
+      <x v="2"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
       <x v="22"/>
     </i>
-    <i>
-      <x v="5"/>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
       <x v="18"/>
     </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
+      <x v="3"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i r="2">
+      <x v="26"/>
+    </i>
     <i>
-      <x v="6"/>
+      <x v="22"/>
+      <x v="2"/>
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="16"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x v="11"/>
+    </i>
+    <i r="2">
+      <x v="2"/>
+    </i>
+    <i r="2">
+      <x v="26"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="23"/>
+      <x v="1"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i>
+      <x v="24"/>
+      <x v="3"/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="9"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="36"/>
+    </i>
+    <i r="2">
+      <x v="7"/>
+    </i>
+    <i r="2">
+      <x v="18"/>
+    </i>
+    <i r="2">
+      <x v="5"/>
+    </i>
+    <i r="2">
+      <x v="29"/>
+    </i>
+    <i r="2">
+      <x v="35"/>
+    </i>
+    <i r="2">
+      <x v="15"/>
+    </i>
+    <i r="2">
+      <x v="17"/>
+    </i>
+    <i r="2">
+      <x/>
+    </i>
+    <i r="2">
+      <x v="23"/>
+    </i>
+    <i r="2">
+      <x v="32"/>
+    </i>
+    <i r="2">
       <x v="12"/>
+    </i>
+    <i r="2">
+      <x v="24"/>
+    </i>
+    <i>
+      <x v="25"/>
+      <x/>
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="22"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i>
+      <x v="26"/>
+      <x v="1"/>
+      <x v="34"/>
+    </i>
+    <i r="2">
+      <x v="30"/>
+    </i>
+    <i r="2">
+      <x v="8"/>
+    </i>
+    <i r="2">
+      <x v="19"/>
+    </i>
+    <i r="2">
+      <x v="4"/>
+    </i>
+    <i r="2">
+      <x v="31"/>
     </i>
     <i t="grand">
       <x/>
@@ -16730,19 +17970,18 @@
   <colItems count="1">
     <i/>
   </colItems>
-  <pageFields count="6">
+  <pageFields count="5">
     <pageField fld="6" hier="-1"/>
     <pageField fld="1" hier="-1"/>
-    <pageField fld="0" hier="-1"/>
-    <pageField fld="2" hier="-1"/>
+    <pageField fld="4" hier="-1"/>
+    <pageField fld="3" hier="-1"/>
     <pageField fld="7" hier="-1"/>
-    <pageField fld="5" hier="-1"/>
   </pageFields>
   <dataFields count="1">
     <dataField name="Sum of Points" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="3">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -16759,7 +17998,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="2">
+    <format dxfId="42">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -16772,7 +18011,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="1">
+    <format dxfId="41">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -16784,7 +18023,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="40">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -17844,7 +19083,7 @@
         <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D26" t="s">
         <v>41</v>
@@ -17873,7 +19112,7 @@
         <v>92</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D27" t="s">
         <v>41</v>
@@ -17902,7 +19141,7 @@
         <v>92</v>
       </c>
       <c r="C28" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D28" t="s">
         <v>41</v>
@@ -17931,7 +19170,7 @@
         <v>92</v>
       </c>
       <c r="C29" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
         <v>41</v>
@@ -17960,7 +19199,7 @@
         <v>92</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D30" t="s">
         <v>41</v>
@@ -17989,7 +19228,7 @@
         <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D31" t="s">
         <v>41</v>
@@ -20048,7 +21287,7 @@
         <v>65</v>
       </c>
       <c r="C102" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D102" t="s">
         <v>41</v>
@@ -20077,7 +21316,7 @@
         <v>65</v>
       </c>
       <c r="C103" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D103" t="s">
         <v>41</v>
@@ -20106,7 +21345,7 @@
         <v>65</v>
       </c>
       <c r="C104" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D104" t="s">
         <v>41</v>
@@ -20135,7 +21374,7 @@
         <v>65</v>
       </c>
       <c r="C105" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D105" t="s">
         <v>41</v>
@@ -20164,7 +21403,7 @@
         <v>65</v>
       </c>
       <c r="C106" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D106" t="s">
         <v>41</v>
@@ -20193,7 +21432,7 @@
         <v>65</v>
       </c>
       <c r="C107" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D107" t="s">
         <v>41</v>
@@ -85868,22 +87107,22 @@
         <v>25</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>26</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>26</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
@@ -85905,13 +87144,13 @@
         <v>Silverstone Circuit</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
@@ -85934,13 +87173,13 @@
         <v>Circuit de Spa-Francorchamps</v>
       </c>
       <c r="F3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K3" t="s">
         <v>129</v>
       </c>
       <c r="L3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -85963,13 +87202,13 @@
         <v>Suzuka International Racing Course</v>
       </c>
       <c r="F4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K4" t="s">
         <v>115</v>
       </c>
       <c r="L4" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
@@ -85992,13 +87231,13 @@
         <v>Bahrain International Circuit</v>
       </c>
       <c r="F5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K5" t="s">
         <v>126</v>
       </c>
       <c r="L5" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
@@ -86021,13 +87260,13 @@
         <v>Jeddah Corniche Circuit</v>
       </c>
       <c r="F6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K6" t="s">
         <v>122</v>
       </c>
       <c r="L6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
@@ -86050,13 +87289,13 @@
         <v>Miami International Autodrome</v>
       </c>
       <c r="F7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K7" t="s">
         <v>15</v>
       </c>
       <c r="L7" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
@@ -86079,13 +87318,13 @@
         <v>Autodromo Enzo e Dino Ferrari (Imola)</v>
       </c>
       <c r="F8" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K8" t="s">
         <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
@@ -86107,13 +87346,13 @@
         <v>Circuit de Barcelona-Catalunya</v>
       </c>
       <c r="F9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K9" t="s">
         <v>18</v>
       </c>
       <c r="L9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
@@ -86125,7 +87364,6 @@
         <v>9</v>
       </c>
       <c r="C10" s="9">
-        <f>C9+7</f>
         <v>46081</v>
       </c>
       <c r="D10" t="s">
@@ -86136,13 +87374,13 @@
         <v>Circuit Gilles Villeneuve</v>
       </c>
       <c r="F10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K10" t="s">
         <v>119</v>
       </c>
       <c r="L10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
@@ -86154,8 +87392,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="9">
-        <f t="shared" ref="C11:C25" si="4">C10+7</f>
-        <v>46088</v>
+        <v>46095</v>
       </c>
       <c r="D11" t="s">
         <v>126</v>
@@ -86165,13 +87402,13 @@
         <v>Red Bull Ring</v>
       </c>
       <c r="F11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K11" t="s">
         <v>117</v>
       </c>
       <c r="L11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
@@ -86183,8 +87420,8 @@
         <v>11</v>
       </c>
       <c r="C12" s="9">
-        <f t="shared" si="4"/>
-        <v>46095</v>
+        <f t="shared" ref="C11:C25" si="4">C11+7</f>
+        <v>46102</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -86194,13 +87431,13 @@
         <v>Hungaroring</v>
       </c>
       <c r="F12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K12" t="s">
         <v>128</v>
       </c>
       <c r="L12" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
@@ -86213,7 +87450,7 @@
       </c>
       <c r="C13" s="9">
         <f t="shared" si="4"/>
-        <v>46102</v>
+        <v>46109</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -86223,13 +87460,13 @@
         <v>Circuit Zandvoort</v>
       </c>
       <c r="F13" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K13" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L13" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
@@ -86242,23 +87479,23 @@
       </c>
       <c r="C14" s="9">
         <f t="shared" si="4"/>
-        <v>46109</v>
+        <v>46116</v>
       </c>
       <c r="D14" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="3"/>
         <v>Autodromo Nazionale Monza</v>
       </c>
       <c r="F14" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K14" t="s">
         <v>38</v>
       </c>
       <c r="L14" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
@@ -86271,7 +87508,7 @@
       </c>
       <c r="C15" s="9">
         <f t="shared" si="4"/>
-        <v>46116</v>
+        <v>46123</v>
       </c>
       <c r="D15" t="s">
         <v>122</v>
@@ -86281,13 +87518,13 @@
         <v>Baku City Circuit</v>
       </c>
       <c r="F15" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K15" t="s">
         <v>125</v>
       </c>
       <c r="L15" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
@@ -86300,23 +87537,23 @@
       </c>
       <c r="C16" s="9">
         <f t="shared" si="4"/>
-        <v>46123</v>
+        <v>46130</v>
       </c>
       <c r="D16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="3"/>
         <v>Marina Bay Street Circuit</v>
       </c>
       <c r="F16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K16" t="s">
         <v>127</v>
       </c>
       <c r="L16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.45">
@@ -86329,7 +87566,7 @@
       </c>
       <c r="C17" s="9">
         <f t="shared" si="4"/>
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="D17" t="s">
         <v>120</v>
@@ -86339,13 +87576,13 @@
         <v>Circuit of the Americas</v>
       </c>
       <c r="F17" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K17" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.45">
@@ -86358,23 +87595,23 @@
       </c>
       <c r="C18" s="9">
         <f t="shared" si="4"/>
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="D18" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="3"/>
         <v>Autódromo Hermanos Rodríguez</v>
       </c>
       <c r="F18" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K18" t="s">
         <v>17</v>
       </c>
       <c r="L18" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.45">
@@ -86387,7 +87624,7 @@
       </c>
       <c r="C19" s="9">
         <f t="shared" si="4"/>
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="D19" t="s">
         <v>115</v>
@@ -86397,13 +87634,13 @@
         <v>Albert Park Circuit</v>
       </c>
       <c r="F19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K19" t="s">
         <v>118</v>
       </c>
       <c r="L19" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.45">
@@ -86416,7 +87653,7 @@
       </c>
       <c r="C20" s="9">
         <f t="shared" si="4"/>
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="D20" t="s">
         <v>117</v>
@@ -86426,13 +87663,13 @@
         <v>Shanghai International Circuit</v>
       </c>
       <c r="F20" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L20" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.45">
@@ -86445,7 +87682,7 @@
       </c>
       <c r="C21" s="9">
         <f t="shared" si="4"/>
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
@@ -86455,13 +87692,13 @@
         <v>Jeddah Corniche Circuit</v>
       </c>
       <c r="F21" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K21" t="s">
         <v>20</v>
       </c>
       <c r="L21" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.45">
@@ -86474,23 +87711,23 @@
       </c>
       <c r="C22" s="9">
         <f t="shared" si="4"/>
-        <v>46165</v>
+        <v>46172</v>
       </c>
       <c r="D22" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="3"/>
         <v>Autódromo José Carlos Pace (Interlagos)</v>
       </c>
       <c r="F22" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K22" t="s">
         <v>124</v>
       </c>
       <c r="L22" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.45">
@@ -86503,7 +87740,7 @@
       </c>
       <c r="C23" s="9">
         <f t="shared" si="4"/>
-        <v>46172</v>
+        <v>46179</v>
       </c>
       <c r="D23" t="s">
         <v>118</v>
@@ -86513,13 +87750,13 @@
         <v>Las Vegas Strip Circuit</v>
       </c>
       <c r="F23" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K23" t="s">
         <v>123</v>
       </c>
       <c r="L23" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.45">
@@ -86532,7 +87769,7 @@
       </c>
       <c r="C24" s="9">
         <f t="shared" si="4"/>
-        <v>46179</v>
+        <v>46186</v>
       </c>
       <c r="D24" t="s">
         <v>121</v>
@@ -86542,13 +87779,13 @@
         <v>Lusail International Circuit</v>
       </c>
       <c r="F24" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K24" t="s">
         <v>121</v>
       </c>
       <c r="L24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
@@ -86561,7 +87798,7 @@
       </c>
       <c r="C25" s="9">
         <f t="shared" si="4"/>
-        <v>46186</v>
+        <v>46193</v>
       </c>
       <c r="D25" t="s">
         <v>129</v>
@@ -86571,21 +87808,21 @@
         <v>Yas Marina Circuit</v>
       </c>
       <c r="F25" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="K25" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.45">
       <c r="K26" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="L26" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.45">
@@ -86593,15 +87830,15 @@
         <v>16</v>
       </c>
       <c r="L27" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.45">
       <c r="K28" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.45">
@@ -86609,31 +87846,31 @@
         <v>116</v>
       </c>
       <c r="L29" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.45">
       <c r="K30" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="L30" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.45">
       <c r="K31" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="L31" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.45">
       <c r="K32" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33" spans="11:12" x14ac:dyDescent="0.45">
@@ -86641,7 +87878,7 @@
         <v>120</v>
       </c>
       <c r="L33" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -86654,196 +87891,2767 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E2081E8-0B1B-45EE-BD85-5154A30D7385}">
-  <dimension ref="A2:I315"/>
+  <dimension ref="A4:G327"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="17.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="18.06640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.73046875" bestFit="1" customWidth="1"/>
     <col min="5" max="55" width="19.265625" bestFit="1" customWidth="1"/>
     <col min="56" max="56" width="18.19921875" bestFit="1" customWidth="1"/>
     <col min="57" max="57" width="16.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="B4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B7" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" s="5" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A10" s="5" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="10">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C14" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="10">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C17" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C18" t="s">
+        <v>0</v>
+      </c>
+      <c r="D18" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="10">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="10">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="10">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C22" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C24" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C25" t="s">
+        <v>12</v>
+      </c>
+      <c r="D25" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C29" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" t="s">
+        <v>32</v>
+      </c>
+      <c r="D32" s="10">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C33" t="s">
+        <v>34</v>
+      </c>
+      <c r="D33" s="10">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C34" t="s">
+        <v>33</v>
+      </c>
+      <c r="D34" s="10">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C35" t="s">
+        <v>0</v>
+      </c>
+      <c r="D35" s="10">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C36" t="s">
+        <v>1</v>
+      </c>
+      <c r="D36" s="10">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="10">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="10">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C39" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="10">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C40" t="s">
+        <v>1</v>
+      </c>
+      <c r="D40" s="10">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C41" t="s">
+        <v>0</v>
+      </c>
+      <c r="D41" s="10">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="10">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C43" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D44" s="10">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C45" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" s="10">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C46" t="s">
+        <v>3</v>
+      </c>
+      <c r="D46" s="10">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D47" s="10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" s="10">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C49" t="s">
+        <v>33</v>
+      </c>
+      <c r="D49" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C54" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C55" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C56" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C57" t="s">
+        <v>86</v>
+      </c>
+      <c r="D57" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A58" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" t="s">
+        <v>53</v>
+      </c>
+      <c r="C58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="10">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C59" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="10">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C60" t="s">
+        <v>34</v>
+      </c>
+      <c r="D60" s="10">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C61" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="10">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
+        <v>32</v>
+      </c>
+      <c r="D62" s="10">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C63" t="s">
+        <v>33</v>
+      </c>
+      <c r="D63" s="10">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C64" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" s="10">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C65" t="s">
+        <v>0</v>
+      </c>
+      <c r="D65" s="10">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C66" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="10">
+        <v>144</v>
+      </c>
+      <c r="G66" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="67" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C67" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" s="10">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C68" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="10">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="69" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C69" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="70" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" s="10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C71" t="s">
+        <v>68</v>
+      </c>
+      <c r="D71" s="10">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="72" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" s="10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="74" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C74" t="s">
+        <v>84</v>
+      </c>
+      <c r="D74" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="75" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C75" t="s">
+        <v>80</v>
+      </c>
+      <c r="D75" s="10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="76" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76" s="10">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="77" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C77" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="78" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C78" t="s">
+        <v>79</v>
+      </c>
+      <c r="D78" s="10">
         <v>25</v>
       </c>
-      <c r="B10" s="5" t="s">
+    </row>
+    <row r="79" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C79" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="C80" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C82" t="s">
+        <v>49</v>
+      </c>
+      <c r="D82" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A83" t="s">
+        <v>46</v>
+      </c>
+      <c r="B83" t="s">
+        <v>39</v>
+      </c>
+      <c r="C83" t="s">
+        <v>0</v>
+      </c>
+      <c r="D83" s="10">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C84" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" s="10">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C85" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="10">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C86" t="s">
+        <v>32</v>
+      </c>
+      <c r="D86" s="10">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C87" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C88" t="s">
+        <v>33</v>
+      </c>
+      <c r="D88" s="10">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>51</v>
+      </c>
+      <c r="B89" t="s">
+        <v>39</v>
+      </c>
+      <c r="C89" t="s">
+        <v>34</v>
+      </c>
+      <c r="D89" s="10">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C90" t="s">
+        <v>32</v>
+      </c>
+      <c r="D90" s="10">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C91" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C92" t="s">
+        <v>33</v>
+      </c>
+      <c r="D92" s="10">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C93" t="s">
+        <v>45</v>
+      </c>
+      <c r="D93" s="10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C94" t="s">
+        <v>52</v>
+      </c>
+      <c r="D94" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>78</v>
+      </c>
+      <c r="B95" t="s">
+        <v>77</v>
+      </c>
+      <c r="C95" t="s">
+        <v>32</v>
+      </c>
+      <c r="D95" s="10">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C96" t="s">
+        <v>1</v>
+      </c>
+      <c r="D96" s="10">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C97" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="98" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C98" t="s">
+        <v>0</v>
+      </c>
+      <c r="D98" s="10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="99" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C99" t="s">
+        <v>34</v>
+      </c>
+      <c r="D99" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="100" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C100" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" s="10">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="101" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C101" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101" s="10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="102" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C102" t="s">
+        <v>33</v>
+      </c>
+      <c r="D102" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="103" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C103" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="104" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C104" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C105" t="s">
+        <v>49</v>
+      </c>
+      <c r="D105" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C106" t="s">
+        <v>3</v>
+      </c>
+      <c r="D106" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="107" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C107" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C108" t="s">
+        <v>43</v>
+      </c>
+      <c r="D108" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C109" t="s">
+        <v>45</v>
+      </c>
+      <c r="D109" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C110" t="s">
+        <v>69</v>
+      </c>
+      <c r="D110" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C111" t="s">
+        <v>80</v>
+      </c>
+      <c r="D111" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C112" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C113" t="s">
+        <v>71</v>
+      </c>
+      <c r="D113" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C114" t="s">
+        <v>12</v>
+      </c>
+      <c r="D114" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>67</v>
+      </c>
+      <c r="B115" t="s">
+        <v>66</v>
+      </c>
+      <c r="C115" t="s">
+        <v>32</v>
+      </c>
+      <c r="D115" s="10">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C116" t="s">
+        <v>34</v>
+      </c>
+      <c r="D116" s="10">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C117" t="s">
+        <v>55</v>
+      </c>
+      <c r="D117" s="10">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C118" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" s="10">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C119" t="s">
+        <v>68</v>
+      </c>
+      <c r="D119" s="10">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C120" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="10">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C121" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="10">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C122" t="s">
+        <v>43</v>
+      </c>
+      <c r="D122" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C123" t="s">
+        <v>2</v>
+      </c>
+      <c r="D123" s="10">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C124" t="s">
+        <v>33</v>
+      </c>
+      <c r="D124" s="10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C125" t="s">
+        <v>45</v>
+      </c>
+      <c r="D125" s="10">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C126" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="10">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C127" t="s">
+        <v>9</v>
+      </c>
+      <c r="D127" s="10">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C128" t="s">
+        <v>11</v>
+      </c>
+      <c r="D128" s="10">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C129" t="s">
+        <v>48</v>
+      </c>
+      <c r="D129" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C130" t="s">
+        <v>4</v>
+      </c>
+      <c r="D130" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C131" t="s">
+        <v>69</v>
+      </c>
+      <c r="D131" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C132" t="s">
+        <v>110</v>
+      </c>
+      <c r="D132" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C133" t="s">
+        <v>70</v>
+      </c>
+      <c r="D133" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C134" t="s">
+        <v>71</v>
+      </c>
+      <c r="D134" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>61</v>
+      </c>
+      <c r="B135" t="s">
+        <v>53</v>
+      </c>
+      <c r="C135" t="s">
+        <v>34</v>
+      </c>
+      <c r="D135" s="10">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C136" t="s">
+        <v>32</v>
+      </c>
+      <c r="D136" s="10">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C137" t="s">
+        <v>33</v>
+      </c>
+      <c r="D137" s="10">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C138" t="s">
+        <v>0</v>
+      </c>
+      <c r="D138" s="10">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C139" t="s">
+        <v>1</v>
+      </c>
+      <c r="D139" s="10">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C140" t="s">
+        <v>48</v>
+      </c>
+      <c r="D140" s="10">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>75</v>
+      </c>
+      <c r="B141" t="s">
+        <v>66</v>
+      </c>
+      <c r="C141" t="s">
+        <v>32</v>
+      </c>
+      <c r="D141" s="10">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C142" t="s">
+        <v>34</v>
+      </c>
+      <c r="D142" s="10">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C143" t="s">
+        <v>55</v>
+      </c>
+      <c r="D143" s="10">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C144" t="s">
+        <v>3</v>
+      </c>
+      <c r="D144" s="10">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="145" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C145" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" s="10">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="146" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C146" t="s">
+        <v>68</v>
+      </c>
+      <c r="D146" s="10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="147" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C147" t="s">
+        <v>9</v>
+      </c>
+      <c r="D147" s="10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="148" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C148" t="s">
+        <v>2</v>
+      </c>
+      <c r="D148" s="10">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="149" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C149" t="s">
+        <v>5</v>
+      </c>
+      <c r="D149" s="10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="150" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C150" t="s">
+        <v>45</v>
+      </c>
+      <c r="D150" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="151" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C151" t="s">
+        <v>43</v>
+      </c>
+      <c r="D151" s="10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="152" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C152" t="s">
+        <v>48</v>
+      </c>
+      <c r="D152" s="10">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="153" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C153" t="s">
+        <v>8</v>
+      </c>
+      <c r="D153" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="154" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C154" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="155" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C155" t="s">
+        <v>110</v>
+      </c>
+      <c r="D155" s="10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="156" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C156" t="s">
+        <v>33</v>
+      </c>
+      <c r="D156" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="157" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C157" t="s">
+        <v>70</v>
+      </c>
+      <c r="D157" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="158" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C158" t="s">
+        <v>71</v>
+      </c>
+      <c r="D158" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C159" t="s">
+        <v>69</v>
+      </c>
+      <c r="D159" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="160" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C160" t="s">
+        <v>4</v>
+      </c>
+      <c r="D160" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A161" t="s">
+        <v>58</v>
+      </c>
+      <c r="B161" t="s">
+        <v>53</v>
+      </c>
+      <c r="C161" t="s">
+        <v>34</v>
+      </c>
+      <c r="D161" s="10">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C162" t="s">
+        <v>32</v>
+      </c>
+      <c r="D162" s="10">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C163" t="s">
+        <v>33</v>
+      </c>
+      <c r="D163" s="10">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C164" t="s">
+        <v>48</v>
+      </c>
+      <c r="D164" s="10">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C165" t="s">
+        <v>4</v>
+      </c>
+      <c r="D165" s="10">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C166" t="s">
+        <v>49</v>
+      </c>
+      <c r="D166" s="10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A167" t="s">
+        <v>72</v>
+      </c>
+      <c r="B167" t="s">
+        <v>66</v>
+      </c>
+      <c r="C167" t="s">
+        <v>34</v>
+      </c>
+      <c r="D167" s="10">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C168" t="s">
+        <v>32</v>
+      </c>
+      <c r="D168" s="10">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C169" t="s">
+        <v>1</v>
+      </c>
+      <c r="D169" s="10">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C170" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="10">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C171" t="s">
+        <v>43</v>
+      </c>
+      <c r="D171" s="10">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C172" t="s">
+        <v>5</v>
+      </c>
+      <c r="D172" s="10">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C173" t="s">
+        <v>2</v>
+      </c>
+      <c r="D173" s="10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C174" t="s">
+        <v>6</v>
+      </c>
+      <c r="D174" s="10">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C175" t="s">
+        <v>68</v>
+      </c>
+      <c r="D175" s="10">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C176" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C177" t="s">
+        <v>33</v>
+      </c>
+      <c r="D177" s="10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C178" t="s">
+        <v>45</v>
+      </c>
+      <c r="D178" s="10">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C179" t="s">
+        <v>9</v>
+      </c>
+      <c r="D179" s="10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C180" t="s">
+        <v>48</v>
+      </c>
+      <c r="D180" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C181" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" s="10">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C182" t="s">
+        <v>70</v>
+      </c>
+      <c r="D182" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C183" t="s">
+        <v>4</v>
+      </c>
+      <c r="D183" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C184" t="s">
+        <v>110</v>
+      </c>
+      <c r="D184" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C185" t="s">
+        <v>69</v>
+      </c>
+      <c r="D185" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C186" t="s">
+        <v>71</v>
+      </c>
+      <c r="D186" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A187" t="s">
+        <v>50</v>
+      </c>
+      <c r="B187" t="s">
+        <v>53</v>
+      </c>
+      <c r="C187" t="s">
+        <v>34</v>
+      </c>
+      <c r="D187" s="10">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C188" t="s">
+        <v>33</v>
+      </c>
+      <c r="D188" s="10">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C189" t="s">
+        <v>1</v>
+      </c>
+      <c r="D189" s="10">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C190" t="s">
+        <v>32</v>
+      </c>
+      <c r="D190" s="10">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C191" t="s">
+        <v>0</v>
+      </c>
+      <c r="D191" s="10">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C192" t="s">
+        <v>3</v>
+      </c>
+      <c r="D192" s="10">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A193" t="s">
+        <v>40</v>
+      </c>
+      <c r="B193" t="s">
+        <v>39</v>
+      </c>
+      <c r="C193" t="s">
+        <v>32</v>
+      </c>
+      <c r="D193" s="10">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C194" t="s">
+        <v>1</v>
+      </c>
+      <c r="D194" s="10">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C195" t="s">
+        <v>33</v>
+      </c>
+      <c r="D195" s="10">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C196" t="s">
+        <v>34</v>
+      </c>
+      <c r="D196" s="10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C197" t="s">
+        <v>43</v>
+      </c>
+      <c r="D197" s="10">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C198" t="s">
+        <v>42</v>
+      </c>
+      <c r="D198" s="10">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A199" t="s">
+        <v>44</v>
+      </c>
+      <c r="B199" t="s">
+        <v>39</v>
+      </c>
+      <c r="C199" t="s">
+        <v>34</v>
+      </c>
+      <c r="D199" s="10">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C200" t="s">
+        <v>0</v>
+      </c>
+      <c r="D200" s="10">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C201" t="s">
+        <v>32</v>
+      </c>
+      <c r="D201" s="10">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C202" t="s">
+        <v>33</v>
+      </c>
+      <c r="D202" s="10">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C203" t="s">
+        <v>1</v>
+      </c>
+      <c r="D203" s="10">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C204" t="s">
+        <v>45</v>
+      </c>
+      <c r="D204" s="10">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A205" t="s">
+        <v>76</v>
+      </c>
+      <c r="B205" t="s">
+        <v>66</v>
+      </c>
+      <c r="C205" t="s">
+        <v>34</v>
+      </c>
+      <c r="D205" s="10">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C206" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C207" t="s">
+        <v>2</v>
+      </c>
+      <c r="D207" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" s="10">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="209" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C209" t="s">
+        <v>1</v>
+      </c>
+      <c r="D209" s="10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C210" t="s">
+        <v>33</v>
+      </c>
+      <c r="D210" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="211" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C211" t="s">
+        <v>8</v>
+      </c>
+      <c r="D211" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="212" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C212" t="s">
+        <v>9</v>
+      </c>
+      <c r="D212" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="213" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C213" t="s">
+        <v>6</v>
+      </c>
+      <c r="D213" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="214" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C214" t="s">
+        <v>11</v>
+      </c>
+      <c r="D214" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C215" t="s">
+        <v>45</v>
+      </c>
+      <c r="D215" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C216" t="s">
+        <v>43</v>
+      </c>
+      <c r="D216" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C217" t="s">
+        <v>48</v>
+      </c>
+      <c r="D217" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C218" t="s">
+        <v>5</v>
+      </c>
+      <c r="D218" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C219" t="s">
+        <v>71</v>
+      </c>
+      <c r="D219" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C220" t="s">
+        <v>69</v>
+      </c>
+      <c r="D220" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C221" t="s">
+        <v>32</v>
+      </c>
+      <c r="D221" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C222" t="s">
+        <v>110</v>
+      </c>
+      <c r="D222" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C223" t="s">
+        <v>4</v>
+      </c>
+      <c r="D223" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C224" t="s">
+        <v>70</v>
+      </c>
+      <c r="D224" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A225" t="s">
+        <v>47</v>
+      </c>
+      <c r="B225" t="s">
+        <v>39</v>
+      </c>
+      <c r="C225" t="s">
+        <v>34</v>
+      </c>
+      <c r="D225" s="10">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C226" t="s">
+        <v>1</v>
+      </c>
+      <c r="D226" s="10">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C227" t="s">
+        <v>32</v>
+      </c>
+      <c r="D227" s="10">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C228" t="s">
+        <v>33</v>
+      </c>
+      <c r="D228" s="10">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C229" t="s">
+        <v>48</v>
+      </c>
+      <c r="D229" s="10">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C230" t="s">
+        <v>49</v>
+      </c>
+      <c r="D230" s="10">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A231" t="s">
+        <v>54</v>
+      </c>
+      <c r="B231" t="s">
+        <v>53</v>
+      </c>
+      <c r="C231" t="s">
+        <v>33</v>
+      </c>
+      <c r="D231" s="10">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C232" t="s">
+        <v>34</v>
+      </c>
+      <c r="D232" s="10">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C233" t="s">
+        <v>48</v>
+      </c>
+      <c r="D233" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C234" t="s">
+        <v>32</v>
+      </c>
+      <c r="D234" s="10">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C235" t="s">
+        <v>42</v>
+      </c>
+      <c r="D235" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C236" t="s">
+        <v>55</v>
+      </c>
+      <c r="D236" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A237" t="s">
+        <v>60</v>
+      </c>
+      <c r="B237" t="s">
+        <v>53</v>
+      </c>
+      <c r="C237" t="s">
+        <v>34</v>
+      </c>
+      <c r="D237" s="10">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C238" t="s">
+        <v>32</v>
+      </c>
+      <c r="D238" s="10">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C239" t="s">
+        <v>33</v>
+      </c>
+      <c r="D239" s="10">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C240" t="s">
+        <v>0</v>
+      </c>
+      <c r="D240" s="10">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C241" t="s">
+        <v>4</v>
+      </c>
+      <c r="D241" s="10">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C242" t="s">
+        <v>43</v>
+      </c>
+      <c r="D242" s="10">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A243" t="s">
+        <v>59</v>
+      </c>
+      <c r="B243" t="s">
+        <v>53</v>
+      </c>
+      <c r="C243" t="s">
+        <v>34</v>
+      </c>
+      <c r="D243" s="10">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C244" t="s">
+        <v>32</v>
+      </c>
+      <c r="D244" s="10">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C245" t="s">
+        <v>33</v>
+      </c>
+      <c r="D245" s="10">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C246" t="s">
+        <v>48</v>
+      </c>
+      <c r="D246" s="10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C247" t="s">
+        <v>8</v>
+      </c>
+      <c r="D247" s="10">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C248" t="s">
+        <v>43</v>
+      </c>
+      <c r="D248" s="10">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A249" t="s">
+        <v>73</v>
+      </c>
+      <c r="B249" t="s">
+        <v>66</v>
+      </c>
+      <c r="C249" t="s">
+        <v>32</v>
+      </c>
+      <c r="D249" s="10">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C250" t="s">
+        <v>1</v>
+      </c>
+      <c r="D250" s="10">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C251" t="s">
+        <v>0</v>
+      </c>
+      <c r="D251" s="10">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C252" t="s">
+        <v>34</v>
+      </c>
+      <c r="D252" s="10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" s="10">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C254" t="s">
+        <v>2</v>
+      </c>
+      <c r="D254" s="10">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C255" t="s">
+        <v>3</v>
+      </c>
+      <c r="D255" s="10">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C256" t="s">
+        <v>6</v>
+      </c>
+      <c r="D256" s="10">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C257" t="s">
+        <v>8</v>
+      </c>
+      <c r="D257" s="10">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C258" t="s">
+        <v>45</v>
+      </c>
+      <c r="D258" s="10">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C259" t="s">
+        <v>5</v>
+      </c>
+      <c r="D259" s="10">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C260" t="s">
+        <v>9</v>
+      </c>
+      <c r="D260" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C261" t="s">
+        <v>33</v>
+      </c>
+      <c r="D261" s="10">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C262" t="s">
+        <v>11</v>
+      </c>
+      <c r="D262" s="10">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C263" t="s">
+        <v>48</v>
+      </c>
+      <c r="D263" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C264" t="s">
+        <v>4</v>
+      </c>
+      <c r="D264" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C265" t="s">
+        <v>110</v>
+      </c>
+      <c r="D265" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C266" t="s">
+        <v>69</v>
+      </c>
+      <c r="D266" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C267" t="s">
+        <v>71</v>
+      </c>
+      <c r="D267" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C268" t="s">
+        <v>70</v>
+      </c>
+      <c r="D268" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A269" t="s">
+        <v>74</v>
+      </c>
+      <c r="B269" t="s">
+        <v>66</v>
+      </c>
+      <c r="C269" t="s">
+        <v>0</v>
+      </c>
+      <c r="D269" s="10">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C270" t="s">
+        <v>1</v>
+      </c>
+      <c r="D270" s="10">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C271" t="s">
+        <v>34</v>
+      </c>
+      <c r="D271" s="10">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C272" t="s">
+        <v>32</v>
+      </c>
+      <c r="D272" s="10">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="273" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C273" t="s">
+        <v>2</v>
+      </c>
+      <c r="D273" s="10">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="274" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C274" t="s">
+        <v>3</v>
+      </c>
+      <c r="D274" s="10">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="275" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C275" t="s">
+        <v>43</v>
+      </c>
+      <c r="D275" s="10">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="276" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C276" t="s">
+        <v>68</v>
+      </c>
+      <c r="D276" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="277" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C277" t="s">
+        <v>9</v>
+      </c>
+      <c r="D277" s="10">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="278" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C278" t="s">
+        <v>6</v>
+      </c>
+      <c r="D278" s="10">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="279" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C279" t="s">
+        <v>45</v>
+      </c>
+      <c r="D279" s="10">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="280" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C280" t="s">
+        <v>33</v>
+      </c>
+      <c r="D280" s="10">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="281" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C281" t="s">
+        <v>8</v>
+      </c>
+      <c r="D281" s="10">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="282" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C282" t="s">
+        <v>48</v>
+      </c>
+      <c r="D282" s="10">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="283" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C283" t="s">
+        <v>11</v>
+      </c>
+      <c r="D283" s="10">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="284" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C284" t="s">
+        <v>4</v>
+      </c>
+      <c r="D284" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C285" t="s">
+        <v>110</v>
+      </c>
+      <c r="D285" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C286" t="s">
+        <v>70</v>
+      </c>
+      <c r="D286" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="287" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C287" t="s">
+        <v>69</v>
+      </c>
+      <c r="D287" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="3:4" x14ac:dyDescent="0.45">
+      <c r="C288" t="s">
+        <v>71</v>
+      </c>
+      <c r="D288" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A289" t="s">
+        <v>56</v>
+      </c>
+      <c r="B289" t="s">
+        <v>53</v>
+      </c>
+      <c r="C289" t="s">
+        <v>32</v>
+      </c>
+      <c r="D289" s="10">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C290" t="s">
+        <v>0</v>
+      </c>
+      <c r="D290" s="10">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C291" t="s">
+        <v>1</v>
+      </c>
+      <c r="D291" s="10">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C292" t="s">
+        <v>34</v>
+      </c>
+      <c r="D292" s="10">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C293" t="s">
+        <v>33</v>
+      </c>
+      <c r="D293" s="10">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C294" t="s">
+        <v>45</v>
+      </c>
+      <c r="D294" s="10">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A295" t="s">
+        <v>81</v>
+      </c>
+      <c r="B295" t="s">
+        <v>77</v>
+      </c>
+      <c r="C295" t="s">
+        <v>34</v>
+      </c>
+      <c r="D295" s="10">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C296" t="s">
+        <v>32</v>
+      </c>
+      <c r="D296" s="10">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C297" t="s">
+        <v>2</v>
+      </c>
+      <c r="D297" s="10">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C298" t="s">
+        <v>1</v>
+      </c>
+      <c r="D298" s="10">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C299" t="s">
+        <v>33</v>
+      </c>
+      <c r="D299" s="10">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C300" t="s">
+        <v>6</v>
+      </c>
+      <c r="D300" s="10">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C301" t="s">
+        <v>0</v>
+      </c>
+      <c r="D301" s="10">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C302" t="s">
+        <v>68</v>
+      </c>
+      <c r="D302" s="10">
         <v>154</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A11">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C303" t="s">
+        <v>9</v>
+      </c>
+      <c r="D303" s="10">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C304" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" s="10">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C305" t="s">
+        <v>43</v>
+      </c>
+      <c r="D305" s="10">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C306" t="s">
+        <v>8</v>
+      </c>
+      <c r="D306" s="10">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C307" t="s">
+        <v>79</v>
+      </c>
+      <c r="D307" s="10">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C308" t="s">
+        <v>49</v>
+      </c>
+      <c r="D308" s="10">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C309" t="s">
+        <v>11</v>
+      </c>
+      <c r="D309" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C310" t="s">
+        <v>12</v>
+      </c>
+      <c r="D310" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C311" t="s">
+        <v>71</v>
+      </c>
+      <c r="D311" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C312" t="s">
+        <v>45</v>
+      </c>
+      <c r="D312" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C313" t="s">
+        <v>80</v>
+      </c>
+      <c r="D313" s="10">
         <v>1</v>
       </c>
-      <c r="B11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11">
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C314" t="s">
+        <v>69</v>
+      </c>
+      <c r="D314" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A315" t="s">
+        <v>149</v>
+      </c>
+      <c r="B315" t="s">
+        <v>39</v>
+      </c>
+      <c r="C315" t="s">
+        <v>34</v>
+      </c>
+      <c r="D315" s="10">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C316" t="s">
+        <v>0</v>
+      </c>
+      <c r="D316" s="10">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C317" t="s">
+        <v>32</v>
+      </c>
+      <c r="D317" s="10">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C318" t="s">
+        <v>1</v>
+      </c>
+      <c r="D318" s="10">
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A12">
+    <row r="319" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C319" t="s">
         <v>2</v>
       </c>
-      <c r="B12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A16">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A17">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
+      <c r="D319" s="10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C320" t="s">
+        <v>33</v>
+      </c>
+      <c r="D320" s="10">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A321" t="s">
+        <v>150</v>
+      </c>
+      <c r="B321" t="s">
+        <v>53</v>
+      </c>
+      <c r="C321" t="s">
+        <v>32</v>
+      </c>
+      <c r="D321" s="10">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C322" t="s">
+        <v>33</v>
+      </c>
+      <c r="D322" s="10">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C323" t="s">
+        <v>34</v>
+      </c>
+      <c r="D323" s="10">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C324" t="s">
+        <v>0</v>
+      </c>
+      <c r="D324" s="10">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C325" t="s">
+        <v>2</v>
+      </c>
+      <c r="D325" s="10">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C326" t="s">
+        <v>42</v>
+      </c>
+      <c r="D326" s="10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A327" t="s">
         <v>111</v>
       </c>
-      <c r="C18">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.45">
-      <c r="G66" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="313" spans="7:9" x14ac:dyDescent="0.45">
-      <c r="G313" t="s">
-        <v>34</v>
-      </c>
-      <c r="H313" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="314" spans="7:9" x14ac:dyDescent="0.45">
-      <c r="G314" t="s">
-        <v>148</v>
-      </c>
-      <c r="H314" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="315" spans="7:9" x14ac:dyDescent="0.45">
-      <c r="G315" t="s">
-        <v>33</v>
-      </c>
-      <c r="H315" t="s">
-        <v>149</v>
-      </c>
-      <c r="I315" t="s">
-        <v>150</v>
+      <c r="D327" s="10">
+        <v>34681</v>
       </c>
     </row>
   </sheetData>
@@ -86864,7 +90672,7 @@
         <v>22</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.45">

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88ECE4E8-38B4-48E6-9676-52B7E69AFAA0}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42AF9F97-F603-4E41-AD77-759F2A45D507}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16079" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16139" uniqueCount="197">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -700,7 +700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -711,292 +711,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="6" tint="0.39997558519241921"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -17981,7 +17700,7 @@
     <dataField name="Sum of Points" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="43">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -17998,7 +17717,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="42">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -18011,7 +17730,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="41">
+    <format dxfId="1">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -18023,7 +17742,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="40">
+    <format dxfId="0">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1" selected="0">
@@ -59173,7 +58892,7 @@
         <v>32</v>
       </c>
       <c r="G1408" t="str">
-        <f t="shared" ref="G1408:G1447" si="0">VLOOKUP(F1408,$M$1408:$N$1427,2,FALSE)</f>
+        <f t="shared" ref="G1408:G1467" si="0">VLOOKUP(F1408,$M$1408:$N$1427,2,FALSE)</f>
         <v>Alpine</v>
       </c>
       <c r="H1408">
@@ -60474,166 +60193,606 @@
       </c>
     </row>
     <row r="1448" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1448" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1448" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1448">
+        <v>10</v>
+      </c>
       <c r="E1448" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1448" t="s">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="F1448" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1448" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1448">
+        <v>1</v>
+      </c>
+      <c r="I1448">
+        <v>25</v>
       </c>
     </row>
     <row r="1449" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1449" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1449" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1449">
+        <v>10</v>
+      </c>
       <c r="E1449" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1449" t="s">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="F1449" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1449" t="str">
+        <f t="shared" si="0"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1449">
+        <v>2</v>
+      </c>
+      <c r="I1449">
+        <v>18</v>
       </c>
     </row>
     <row r="1450" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1450" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1450" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1450">
+        <v>10</v>
+      </c>
       <c r="E1450" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1450" t="s">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="F1450" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1450" t="str">
+        <f t="shared" si="0"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1450">
+        <v>3</v>
+      </c>
+      <c r="I1450">
+        <v>15</v>
       </c>
     </row>
     <row r="1451" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1451" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1451" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1451">
+        <v>10</v>
+      </c>
       <c r="E1451" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1451" t="s">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="F1451" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1451" t="str">
+        <f t="shared" si="0"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1451">
+        <v>4</v>
+      </c>
+      <c r="I1451">
+        <v>12</v>
       </c>
     </row>
     <row r="1452" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1452" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1452" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1452">
+        <v>10</v>
+      </c>
       <c r="E1452" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1452" t="s">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="F1452" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1452" t="str">
+        <f t="shared" si="0"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1452">
+        <v>5</v>
+      </c>
+      <c r="I1452">
+        <v>10</v>
       </c>
     </row>
     <row r="1453" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1453" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1453" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1453">
+        <v>10</v>
+      </c>
       <c r="E1453" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1453" t="s">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="F1453" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1453" t="str">
+        <f t="shared" si="0"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1453">
+        <v>6</v>
+      </c>
+      <c r="I1453">
+        <v>8</v>
       </c>
     </row>
     <row r="1454" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1454" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1454" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1454">
+        <v>10</v>
+      </c>
       <c r="E1454" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1454" t="s">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="F1454" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1454" t="str">
+        <f t="shared" si="0"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1454">
+        <v>7</v>
+      </c>
+      <c r="I1454">
+        <v>6</v>
       </c>
     </row>
     <row r="1455" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1455" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1455" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1455">
+        <v>10</v>
+      </c>
       <c r="E1455" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1455" t="s">
-        <v>37</v>
+        <v>126</v>
+      </c>
+      <c r="F1455" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1455" t="str">
+        <f t="shared" si="0"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1455">
+        <v>8</v>
+      </c>
+      <c r="I1455">
+        <v>4</v>
       </c>
     </row>
     <row r="1456" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1456" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1456" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1456">
+        <v>10</v>
+      </c>
       <c r="E1456" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1456" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1457" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1456" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1456" t="str">
+        <f t="shared" si="0"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1456">
+        <v>9</v>
+      </c>
+      <c r="I1456">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1457" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1457" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1457">
+        <v>10</v>
+      </c>
       <c r="E1457" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1457" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1458" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1457" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1457" t="str">
+        <f t="shared" si="0"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1457">
+        <v>10</v>
+      </c>
+      <c r="I1457">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1458" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1458" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1458">
+        <v>10</v>
+      </c>
       <c r="E1458" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1458" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1459" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1458" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1458" t="str">
+        <f t="shared" si="0"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1458">
+        <v>11</v>
+      </c>
+      <c r="I1458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1459" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1459" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1459">
+        <v>10</v>
+      </c>
       <c r="E1459" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1459" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1460" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1459" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1459" t="str">
+        <f t="shared" si="0"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1459">
+        <v>12</v>
+      </c>
+      <c r="I1459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1460" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1460">
+        <v>10</v>
+      </c>
       <c r="E1460" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1460" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1461" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1460" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1460" t="str">
+        <f t="shared" si="0"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1460">
+        <v>13</v>
+      </c>
+      <c r="I1460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1461" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1461">
+        <v>10</v>
+      </c>
       <c r="E1461" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1461" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1462" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1461" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1461" t="str">
+        <f t="shared" si="0"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1461">
+        <v>14</v>
+      </c>
+      <c r="I1461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1462" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1462">
+        <v>10</v>
+      </c>
       <c r="E1462" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1462" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1463" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1462" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1462" t="str">
+        <f t="shared" si="0"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1462">
+        <v>15</v>
+      </c>
+      <c r="I1462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1463" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1463">
+        <v>10</v>
+      </c>
       <c r="E1463" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1463" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1464" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1463" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1463" t="str">
+        <f t="shared" si="0"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1463">
+        <v>16</v>
+      </c>
+      <c r="I1463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1464" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1464">
+        <v>10</v>
+      </c>
       <c r="E1464" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1464" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1465" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1464" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1464" t="str">
+        <f t="shared" si="0"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1464">
+        <v>17</v>
+      </c>
+      <c r="I1464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1465" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1465">
+        <v>10</v>
+      </c>
       <c r="E1465" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1465" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1466" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1465" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1465" t="str">
+        <f t="shared" si="0"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1465">
+        <v>18</v>
+      </c>
+      <c r="I1465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1466" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1466">
+        <v>10</v>
+      </c>
       <c r="E1466" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1466" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1467" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1466" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1466" t="str">
+        <f t="shared" si="0"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1466">
+        <v>19</v>
+      </c>
+      <c r="I1466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1467" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1467">
+        <v>10</v>
+      </c>
       <c r="E1467" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1467" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1468" spans="5:9" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+      <c r="F1467" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1467" t="str">
+        <f t="shared" si="0"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1467">
+        <v>20</v>
+      </c>
+      <c r="I1467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E1468" t="s">
         <v>37</v>
       </c>
@@ -60641,7 +60800,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1469" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1469" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E1469" t="s">
         <v>37</v>
       </c>
@@ -60649,7 +60808,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1470" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1470" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E1470" t="s">
         <v>37</v>
       </c>
@@ -60657,7 +60816,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1471" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1471" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E1471" t="s">
         <v>37</v>
       </c>
@@ -60665,7 +60824,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1472" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1472" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E1472" t="s">
         <v>37</v>
       </c>
@@ -87392,7 +87551,7 @@
         <v>10</v>
       </c>
       <c r="C11" s="9">
-        <v>46095</v>
+        <v>46096</v>
       </c>
       <c r="D11" t="s">
         <v>126</v>
@@ -87420,8 +87579,8 @@
         <v>11</v>
       </c>
       <c r="C12" s="9">
-        <f t="shared" ref="C11:C25" si="4">C11+7</f>
-        <v>46102</v>
+        <f t="shared" ref="C12:C25" si="4">C11+7</f>
+        <v>46103</v>
       </c>
       <c r="D12" t="s">
         <v>127</v>
@@ -87450,7 +87609,7 @@
       </c>
       <c r="C13" s="9">
         <f t="shared" si="4"/>
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="D13" t="s">
         <v>128</v>
@@ -87479,7 +87638,7 @@
       </c>
       <c r="C14" s="9">
         <f t="shared" si="4"/>
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="D14" t="s">
         <v>168</v>
@@ -87508,7 +87667,7 @@
       </c>
       <c r="C15" s="9">
         <f t="shared" si="4"/>
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="D15" t="s">
         <v>122</v>
@@ -87537,7 +87696,7 @@
       </c>
       <c r="C16" s="9">
         <f t="shared" si="4"/>
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="D16" t="s">
         <v>171</v>
@@ -87566,7 +87725,7 @@
       </c>
       <c r="C17" s="9">
         <f t="shared" si="4"/>
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="D17" t="s">
         <v>120</v>
@@ -87595,7 +87754,7 @@
       </c>
       <c r="C18" s="9">
         <f t="shared" si="4"/>
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="D18" t="s">
         <v>174</v>
@@ -87624,7 +87783,7 @@
       </c>
       <c r="C19" s="9">
         <f t="shared" si="4"/>
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="D19" t="s">
         <v>115</v>
@@ -87653,7 +87812,7 @@
       </c>
       <c r="C20" s="9">
         <f t="shared" si="4"/>
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="D20" t="s">
         <v>117</v>
@@ -87682,7 +87841,7 @@
       </c>
       <c r="C21" s="9">
         <f t="shared" si="4"/>
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="D21" t="s">
         <v>16</v>
@@ -87711,7 +87870,7 @@
       </c>
       <c r="C22" s="9">
         <f t="shared" si="4"/>
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="D22" t="s">
         <v>176</v>
@@ -87740,7 +87899,7 @@
       </c>
       <c r="C23" s="9">
         <f t="shared" si="4"/>
-        <v>46179</v>
+        <v>46180</v>
       </c>
       <c r="D23" t="s">
         <v>118</v>
@@ -87769,7 +87928,7 @@
       </c>
       <c r="C24" s="9">
         <f t="shared" si="4"/>
-        <v>46186</v>
+        <v>46187</v>
       </c>
       <c r="D24" t="s">
         <v>121</v>
@@ -87798,7 +87957,7 @@
       </c>
       <c r="C25" s="9">
         <f t="shared" si="4"/>
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="D25" t="s">
         <v>129</v>
@@ -87971,7 +88130,7 @@
       <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12">
         <v>118</v>
       </c>
     </row>
@@ -87979,7 +88138,7 @@
       <c r="C13" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13">
         <v>83</v>
       </c>
     </row>
@@ -87987,7 +88146,7 @@
       <c r="C14" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14">
         <v>72</v>
       </c>
     </row>
@@ -87995,7 +88154,7 @@
       <c r="C15" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15">
         <v>67</v>
       </c>
     </row>
@@ -88003,7 +88162,7 @@
       <c r="C16" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16">
         <v>59</v>
       </c>
     </row>
@@ -88011,7 +88170,7 @@
       <c r="C17" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17">
         <v>54</v>
       </c>
     </row>
@@ -88019,7 +88178,7 @@
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="D18" s="10">
+      <c r="D18">
         <v>50</v>
       </c>
     </row>
@@ -88027,7 +88186,7 @@
       <c r="C19" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="10">
+      <c r="D19">
         <v>44</v>
       </c>
     </row>
@@ -88035,7 +88194,7 @@
       <c r="C20" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20">
         <v>43</v>
       </c>
     </row>
@@ -88043,7 +88202,7 @@
       <c r="C21" t="s">
         <v>34</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21">
         <v>37</v>
       </c>
     </row>
@@ -88051,7 +88210,7 @@
       <c r="C22" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22">
         <v>27</v>
       </c>
     </row>
@@ -88059,7 +88218,7 @@
       <c r="C23" t="s">
         <v>5</v>
       </c>
-      <c r="D23" s="10">
+      <c r="D23">
         <v>17</v>
       </c>
     </row>
@@ -88067,7 +88226,7 @@
       <c r="C24" t="s">
         <v>9</v>
       </c>
-      <c r="D24" s="10">
+      <c r="D24">
         <v>14</v>
       </c>
     </row>
@@ -88075,7 +88234,7 @@
       <c r="C25" t="s">
         <v>12</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25">
         <v>8</v>
       </c>
     </row>
@@ -88083,7 +88242,7 @@
       <c r="C26" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26">
         <v>7</v>
       </c>
     </row>
@@ -88091,7 +88250,7 @@
       <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27">
         <v>2</v>
       </c>
     </row>
@@ -88099,7 +88258,7 @@
       <c r="C28" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28">
         <v>2</v>
       </c>
     </row>
@@ -88107,7 +88266,7 @@
       <c r="C29" t="s">
         <v>14</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29">
         <v>2</v>
       </c>
     </row>
@@ -88115,7 +88274,7 @@
       <c r="C30" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30">
         <v>1</v>
       </c>
     </row>
@@ -88123,7 +88282,7 @@
       <c r="C31" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31">
         <v>0</v>
       </c>
     </row>
@@ -88137,7 +88296,7 @@
       <c r="C32" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32">
         <v>562</v>
       </c>
     </row>
@@ -88145,7 +88304,7 @@
       <c r="C33" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="10">
+      <c r="D33">
         <v>516</v>
       </c>
     </row>
@@ -88153,7 +88312,7 @@
       <c r="C34" t="s">
         <v>33</v>
       </c>
-      <c r="D34" s="10">
+      <c r="D34">
         <v>471</v>
       </c>
     </row>
@@ -88161,7 +88320,7 @@
       <c r="C35" t="s">
         <v>0</v>
       </c>
-      <c r="D35" s="10">
+      <c r="D35">
         <v>389</v>
       </c>
     </row>
@@ -88169,7 +88328,7 @@
       <c r="C36" t="s">
         <v>1</v>
       </c>
-      <c r="D36" s="10">
+      <c r="D36">
         <v>329</v>
       </c>
     </row>
@@ -88177,7 +88336,7 @@
       <c r="C37" t="s">
         <v>8</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D37">
         <v>115</v>
       </c>
     </row>
@@ -88191,7 +88350,7 @@
       <c r="C38" t="s">
         <v>32</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D38">
         <v>190</v>
       </c>
     </row>
@@ -88199,7 +88358,7 @@
       <c r="C39" t="s">
         <v>85</v>
       </c>
-      <c r="D39" s="10">
+      <c r="D39">
         <v>187</v>
       </c>
     </row>
@@ -88207,7 +88366,7 @@
       <c r="C40" t="s">
         <v>1</v>
       </c>
-      <c r="D40" s="10">
+      <c r="D40">
         <v>183</v>
       </c>
     </row>
@@ -88215,7 +88374,7 @@
       <c r="C41" t="s">
         <v>0</v>
       </c>
-      <c r="D41" s="10">
+      <c r="D41">
         <v>179</v>
       </c>
     </row>
@@ -88223,7 +88382,7 @@
       <c r="C42" t="s">
         <v>7</v>
       </c>
-      <c r="D42" s="10">
+      <c r="D42">
         <v>141</v>
       </c>
     </row>
@@ -88231,7 +88390,7 @@
       <c r="C43" t="s">
         <v>2</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43">
         <v>99</v>
       </c>
     </row>
@@ -88239,7 +88398,7 @@
       <c r="C44" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="10">
+      <c r="D44">
         <v>90</v>
       </c>
     </row>
@@ -88247,7 +88406,7 @@
       <c r="C45" t="s">
         <v>6</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45">
         <v>74</v>
       </c>
     </row>
@@ -88255,7 +88414,7 @@
       <c r="C46" t="s">
         <v>3</v>
       </c>
-      <c r="D46" s="10">
+      <c r="D46">
         <v>52</v>
       </c>
     </row>
@@ -88263,7 +88422,7 @@
       <c r="C47" t="s">
         <v>68</v>
       </c>
-      <c r="D47" s="10">
+      <c r="D47">
         <v>40</v>
       </c>
     </row>
@@ -88271,7 +88430,7 @@
       <c r="C48" t="s">
         <v>12</v>
       </c>
-      <c r="D48" s="10">
+      <c r="D48">
         <v>22</v>
       </c>
     </row>
@@ -88279,7 +88438,7 @@
       <c r="C49" t="s">
         <v>33</v>
       </c>
-      <c r="D49" s="10">
+      <c r="D49">
         <v>17</v>
       </c>
     </row>
@@ -88287,7 +88446,7 @@
       <c r="C50" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="10">
+      <c r="D50">
         <v>16</v>
       </c>
     </row>
@@ -88295,7 +88454,7 @@
       <c r="C51" t="s">
         <v>34</v>
       </c>
-      <c r="D51" s="10">
+      <c r="D51">
         <v>8</v>
       </c>
     </row>
@@ -88303,7 +88462,7 @@
       <c r="C52" t="s">
         <v>10</v>
       </c>
-      <c r="D52" s="10">
+      <c r="D52">
         <v>7</v>
       </c>
     </row>
@@ -88311,7 +88470,7 @@
       <c r="C53" t="s">
         <v>13</v>
       </c>
-      <c r="D53" s="10">
+      <c r="D53">
         <v>6</v>
       </c>
     </row>
@@ -88319,7 +88478,7 @@
       <c r="C54" t="s">
         <v>8</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D54">
         <v>2</v>
       </c>
     </row>
@@ -88327,7 +88486,7 @@
       <c r="C55" t="s">
         <v>9</v>
       </c>
-      <c r="D55" s="10">
+      <c r="D55">
         <v>0</v>
       </c>
     </row>
@@ -88335,7 +88494,7 @@
       <c r="C56" t="s">
         <v>36</v>
       </c>
-      <c r="D56" s="10">
+      <c r="D56">
         <v>0</v>
       </c>
     </row>
@@ -88343,7 +88502,7 @@
       <c r="C57" t="s">
         <v>86</v>
       </c>
-      <c r="D57" s="10">
+      <c r="D57">
         <v>0</v>
       </c>
     </row>
@@ -88357,7 +88516,7 @@
       <c r="C58" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="10">
+      <c r="D58">
         <v>265</v>
       </c>
     </row>
@@ -88365,7 +88524,7 @@
       <c r="C59" t="s">
         <v>32</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D59">
         <v>236</v>
       </c>
     </row>
@@ -88373,7 +88532,7 @@
       <c r="C60" t="s">
         <v>34</v>
       </c>
-      <c r="D60" s="10">
+      <c r="D60">
         <v>217</v>
       </c>
     </row>
@@ -88381,7 +88540,7 @@
       <c r="C61" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="10">
+      <c r="D61">
         <v>47</v>
       </c>
     </row>
@@ -88395,7 +88554,7 @@
       <c r="C62" t="s">
         <v>32</v>
       </c>
-      <c r="D62" s="10">
+      <c r="D62">
         <v>307</v>
       </c>
     </row>
@@ -88403,7 +88562,7 @@
       <c r="C63" t="s">
         <v>33</v>
       </c>
-      <c r="D63" s="10">
+      <c r="D63">
         <v>176</v>
       </c>
     </row>
@@ -88411,7 +88570,7 @@
       <c r="C64" t="s">
         <v>1</v>
       </c>
-      <c r="D64" s="10">
+      <c r="D64">
         <v>165</v>
       </c>
     </row>
@@ -88419,7 +88578,7 @@
       <c r="C65" t="s">
         <v>0</v>
       </c>
-      <c r="D65" s="10">
+      <c r="D65">
         <v>156</v>
       </c>
     </row>
@@ -88427,7 +88586,7 @@
       <c r="C66" t="s">
         <v>2</v>
       </c>
-      <c r="D66" s="10">
+      <c r="D66">
         <v>144</v>
       </c>
       <c r="G66" t="s">
@@ -88438,7 +88597,7 @@
       <c r="C67" t="s">
         <v>6</v>
       </c>
-      <c r="D67" s="10">
+      <c r="D67">
         <v>138</v>
       </c>
     </row>
@@ -88446,7 +88605,7 @@
       <c r="C68" t="s">
         <v>34</v>
       </c>
-      <c r="D68" s="10">
+      <c r="D68">
         <v>125</v>
       </c>
     </row>
@@ -88454,7 +88613,7 @@
       <c r="C69" t="s">
         <v>3</v>
       </c>
-      <c r="D69" s="10">
+      <c r="D69">
         <v>109</v>
       </c>
     </row>
@@ -88462,7 +88621,7 @@
       <c r="C70" t="s">
         <v>7</v>
       </c>
-      <c r="D70" s="10">
+      <c r="D70">
         <v>97</v>
       </c>
     </row>
@@ -88470,7 +88629,7 @@
       <c r="C71" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="10">
+      <c r="D71">
         <v>94</v>
       </c>
     </row>
@@ -88478,7 +88637,7 @@
       <c r="C72" t="s">
         <v>12</v>
       </c>
-      <c r="D72" s="10">
+      <c r="D72">
         <v>76</v>
       </c>
     </row>
@@ -88486,7 +88645,7 @@
       <c r="C73" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="10">
+      <c r="D73">
         <v>40</v>
       </c>
     </row>
@@ -88494,7 +88653,7 @@
       <c r="C74" t="s">
         <v>84</v>
       </c>
-      <c r="D74" s="10">
+      <c r="D74">
         <v>34</v>
       </c>
     </row>
@@ -88502,7 +88661,7 @@
       <c r="C75" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="10">
+      <c r="D75">
         <v>32</v>
       </c>
     </row>
@@ -88510,7 +88669,7 @@
       <c r="C76" t="s">
         <v>10</v>
       </c>
-      <c r="D76" s="10">
+      <c r="D76">
         <v>32</v>
       </c>
     </row>
@@ -88518,7 +88677,7 @@
       <c r="C77" t="s">
         <v>8</v>
       </c>
-      <c r="D77" s="10">
+      <c r="D77">
         <v>29</v>
       </c>
     </row>
@@ -88526,7 +88685,7 @@
       <c r="C78" t="s">
         <v>79</v>
       </c>
-      <c r="D78" s="10">
+      <c r="D78">
         <v>25</v>
       </c>
     </row>
@@ -88534,7 +88693,7 @@
       <c r="C79" t="s">
         <v>43</v>
       </c>
-      <c r="D79" s="10">
+      <c r="D79">
         <v>25</v>
       </c>
     </row>
@@ -88542,7 +88701,7 @@
       <c r="C80" t="s">
         <v>11</v>
       </c>
-      <c r="D80" s="10">
+      <c r="D80">
         <v>11</v>
       </c>
     </row>
@@ -88550,7 +88709,7 @@
       <c r="C81" t="s">
         <v>5</v>
       </c>
-      <c r="D81" s="10">
+      <c r="D81">
         <v>10</v>
       </c>
     </row>
@@ -88558,7 +88717,7 @@
       <c r="C82" t="s">
         <v>49</v>
       </c>
-      <c r="D82" s="10">
+      <c r="D82">
         <v>8</v>
       </c>
     </row>
@@ -88572,7 +88731,7 @@
       <c r="C83" t="s">
         <v>0</v>
       </c>
-      <c r="D83" s="10">
+      <c r="D83">
         <v>218</v>
       </c>
     </row>
@@ -88580,7 +88739,7 @@
       <c r="C84" t="s">
         <v>34</v>
       </c>
-      <c r="D84" s="10">
+      <c r="D84">
         <v>186</v>
       </c>
     </row>
@@ -88588,7 +88747,7 @@
       <c r="C85" t="s">
         <v>1</v>
       </c>
-      <c r="D85" s="10">
+      <c r="D85">
         <v>166</v>
       </c>
     </row>
@@ -88596,7 +88755,7 @@
       <c r="C86" t="s">
         <v>32</v>
       </c>
-      <c r="D86" s="10">
+      <c r="D86">
         <v>123</v>
       </c>
     </row>
@@ -88604,7 +88763,7 @@
       <c r="C87" t="s">
         <v>2</v>
       </c>
-      <c r="D87" s="10">
+      <c r="D87">
         <v>99</v>
       </c>
     </row>
@@ -88612,7 +88771,7 @@
       <c r="C88" t="s">
         <v>33</v>
       </c>
-      <c r="D88" s="10">
+      <c r="D88">
         <v>82</v>
       </c>
     </row>
@@ -88626,7 +88785,7 @@
       <c r="C89" t="s">
         <v>34</v>
       </c>
-      <c r="D89" s="10">
+      <c r="D89">
         <v>312</v>
       </c>
     </row>
@@ -88634,7 +88793,7 @@
       <c r="C90" t="s">
         <v>32</v>
       </c>
-      <c r="D90" s="10">
+      <c r="D90">
         <v>209</v>
       </c>
     </row>
@@ -88642,7 +88801,7 @@
       <c r="C91" t="s">
         <v>0</v>
       </c>
-      <c r="D91" s="10">
+      <c r="D91">
         <v>129</v>
       </c>
     </row>
@@ -88650,7 +88809,7 @@
       <c r="C92" t="s">
         <v>33</v>
       </c>
-      <c r="D92" s="10">
+      <c r="D92">
         <v>115</v>
       </c>
     </row>
@@ -88658,7 +88817,7 @@
       <c r="C93" t="s">
         <v>45</v>
       </c>
-      <c r="D93" s="10">
+      <c r="D93">
         <v>97</v>
       </c>
     </row>
@@ -88666,7 +88825,7 @@
       <c r="C94" t="s">
         <v>52</v>
       </c>
-      <c r="D94" s="10">
+      <c r="D94">
         <v>65</v>
       </c>
     </row>
@@ -88680,7 +88839,7 @@
       <c r="C95" t="s">
         <v>32</v>
       </c>
-      <c r="D95" s="10">
+      <c r="D95">
         <v>135</v>
       </c>
     </row>
@@ -88688,7 +88847,7 @@
       <c r="C96" t="s">
         <v>1</v>
       </c>
-      <c r="D96" s="10">
+      <c r="D96">
         <v>98</v>
       </c>
     </row>
@@ -88696,7 +88855,7 @@
       <c r="C97" t="s">
         <v>2</v>
       </c>
-      <c r="D97" s="10">
+      <c r="D97">
         <v>89</v>
       </c>
     </row>
@@ -88704,7 +88863,7 @@
       <c r="C98" t="s">
         <v>0</v>
       </c>
-      <c r="D98" s="10">
+      <c r="D98">
         <v>64</v>
       </c>
     </row>
@@ -88712,7 +88871,7 @@
       <c r="C99" t="s">
         <v>34</v>
       </c>
-      <c r="D99" s="10">
+      <c r="D99">
         <v>60</v>
       </c>
     </row>
@@ -88720,7 +88879,7 @@
       <c r="C100" t="s">
         <v>6</v>
       </c>
-      <c r="D100" s="10">
+      <c r="D100">
         <v>55</v>
       </c>
     </row>
@@ -88728,7 +88887,7 @@
       <c r="C101" t="s">
         <v>9</v>
       </c>
-      <c r="D101" s="10">
+      <c r="D101">
         <v>54</v>
       </c>
     </row>
@@ -88736,7 +88895,7 @@
       <c r="C102" t="s">
         <v>33</v>
       </c>
-      <c r="D102" s="10">
+      <c r="D102">
         <v>50</v>
       </c>
     </row>
@@ -88744,7 +88903,7 @@
       <c r="C103" t="s">
         <v>68</v>
       </c>
-      <c r="D103" s="10">
+      <c r="D103">
         <v>31</v>
       </c>
     </row>
@@ -88752,7 +88911,7 @@
       <c r="C104" t="s">
         <v>8</v>
       </c>
-      <c r="D104" s="10">
+      <c r="D104">
         <v>25</v>
       </c>
     </row>
@@ -88760,7 +88919,7 @@
       <c r="C105" t="s">
         <v>49</v>
       </c>
-      <c r="D105" s="10">
+      <c r="D105">
         <v>16</v>
       </c>
     </row>
@@ -88768,7 +88927,7 @@
       <c r="C106" t="s">
         <v>3</v>
       </c>
-      <c r="D106" s="10">
+      <c r="D106">
         <v>16</v>
       </c>
     </row>
@@ -88776,7 +88935,7 @@
       <c r="C107" t="s">
         <v>79</v>
       </c>
-      <c r="D107" s="10">
+      <c r="D107">
         <v>12</v>
       </c>
     </row>
@@ -88784,7 +88943,7 @@
       <c r="C108" t="s">
         <v>43</v>
       </c>
-      <c r="D108" s="10">
+      <c r="D108">
         <v>4</v>
       </c>
     </row>
@@ -88792,7 +88951,7 @@
       <c r="C109" t="s">
         <v>45</v>
       </c>
-      <c r="D109" s="10">
+      <c r="D109">
         <v>2</v>
       </c>
     </row>
@@ -88800,7 +88959,7 @@
       <c r="C110" t="s">
         <v>69</v>
       </c>
-      <c r="D110" s="10">
+      <c r="D110">
         <v>1</v>
       </c>
     </row>
@@ -88808,7 +88967,7 @@
       <c r="C111" t="s">
         <v>80</v>
       </c>
-      <c r="D111" s="10">
+      <c r="D111">
         <v>0</v>
       </c>
     </row>
@@ -88816,7 +88975,7 @@
       <c r="C112" t="s">
         <v>11</v>
       </c>
-      <c r="D112" s="10">
+      <c r="D112">
         <v>0</v>
       </c>
     </row>
@@ -88824,7 +88983,7 @@
       <c r="C113" t="s">
         <v>71</v>
       </c>
-      <c r="D113" s="10">
+      <c r="D113">
         <v>0</v>
       </c>
     </row>
@@ -88832,7 +88991,7 @@
       <c r="C114" t="s">
         <v>12</v>
       </c>
-      <c r="D114" s="10">
+      <c r="D114">
         <v>0</v>
       </c>
     </row>
@@ -88846,7 +89005,7 @@
       <c r="C115" t="s">
         <v>32</v>
       </c>
-      <c r="D115" s="10">
+      <c r="D115">
         <v>364</v>
       </c>
     </row>
@@ -88854,7 +89013,7 @@
       <c r="C116" t="s">
         <v>34</v>
       </c>
-      <c r="D116" s="10">
+      <c r="D116">
         <v>354</v>
       </c>
     </row>
@@ -88862,7 +89021,7 @@
       <c r="C117" t="s">
         <v>55</v>
       </c>
-      <c r="D117" s="10">
+      <c r="D117">
         <v>286</v>
       </c>
     </row>
@@ -88870,7 +89029,7 @@
       <c r="C118" t="s">
         <v>6</v>
       </c>
-      <c r="D118" s="10">
+      <c r="D118">
         <v>174</v>
       </c>
     </row>
@@ -88878,7 +89037,7 @@
       <c r="C119" t="s">
         <v>68</v>
       </c>
-      <c r="D119" s="10">
+      <c r="D119">
         <v>163</v>
       </c>
     </row>
@@ -88886,7 +89045,7 @@
       <c r="C120" t="s">
         <v>5</v>
       </c>
-      <c r="D120" s="10">
+      <c r="D120">
         <v>159</v>
       </c>
     </row>
@@ -88894,7 +89053,7 @@
       <c r="C121" t="s">
         <v>3</v>
       </c>
-      <c r="D121" s="10">
+      <c r="D121">
         <v>155</v>
       </c>
     </row>
@@ -88902,7 +89061,7 @@
       <c r="C122" t="s">
         <v>43</v>
       </c>
-      <c r="D122" s="10">
+      <c r="D122">
         <v>129</v>
       </c>
     </row>
@@ -88910,7 +89069,7 @@
       <c r="C123" t="s">
         <v>2</v>
       </c>
-      <c r="D123" s="10">
+      <c r="D123">
         <v>128</v>
       </c>
     </row>
@@ -88918,7 +89077,7 @@
       <c r="C124" t="s">
         <v>33</v>
       </c>
-      <c r="D124" s="10">
+      <c r="D124">
         <v>97</v>
       </c>
     </row>
@@ -88926,7 +89085,7 @@
       <c r="C125" t="s">
         <v>45</v>
       </c>
-      <c r="D125" s="10">
+      <c r="D125">
         <v>57</v>
       </c>
     </row>
@@ -88934,7 +89093,7 @@
       <c r="C126" t="s">
         <v>8</v>
       </c>
-      <c r="D126" s="10">
+      <c r="D126">
         <v>57</v>
       </c>
     </row>
@@ -88942,7 +89101,7 @@
       <c r="C127" t="s">
         <v>9</v>
       </c>
-      <c r="D127" s="10">
+      <c r="D127">
         <v>55</v>
       </c>
     </row>
@@ -88950,7 +89109,7 @@
       <c r="C128" t="s">
         <v>11</v>
       </c>
-      <c r="D128" s="10">
+      <c r="D128">
         <v>31</v>
       </c>
     </row>
@@ -88958,7 +89117,7 @@
       <c r="C129" t="s">
         <v>48</v>
       </c>
-      <c r="D129" s="10">
+      <c r="D129">
         <v>20</v>
       </c>
     </row>
@@ -88966,7 +89125,7 @@
       <c r="C130" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="10">
+      <c r="D130">
         <v>8</v>
       </c>
     </row>
@@ -88974,7 +89133,7 @@
       <c r="C131" t="s">
         <v>69</v>
       </c>
-      <c r="D131" s="10">
+      <c r="D131">
         <v>3</v>
       </c>
     </row>
@@ -88982,7 +89141,7 @@
       <c r="C132" t="s">
         <v>110</v>
       </c>
-      <c r="D132" s="10">
+      <c r="D132">
         <v>2</v>
       </c>
     </row>
@@ -88990,7 +89149,7 @@
       <c r="C133" t="s">
         <v>70</v>
       </c>
-      <c r="D133" s="10">
+      <c r="D133">
         <v>0</v>
       </c>
     </row>
@@ -88998,7 +89157,7 @@
       <c r="C134" t="s">
         <v>71</v>
       </c>
-      <c r="D134" s="10">
+      <c r="D134">
         <v>0</v>
       </c>
     </row>
@@ -89012,7 +89171,7 @@
       <c r="C135" t="s">
         <v>34</v>
       </c>
-      <c r="D135" s="10">
+      <c r="D135">
         <v>375</v>
       </c>
     </row>
@@ -89020,7 +89179,7 @@
       <c r="C136" t="s">
         <v>32</v>
       </c>
-      <c r="D136" s="10">
+      <c r="D136">
         <v>244</v>
       </c>
     </row>
@@ -89028,7 +89187,7 @@
       <c r="C137" t="s">
         <v>33</v>
       </c>
-      <c r="D137" s="10">
+      <c r="D137">
         <v>214</v>
       </c>
     </row>
@@ -89036,7 +89195,7 @@
       <c r="C138" t="s">
         <v>0</v>
       </c>
-      <c r="D138" s="10">
+      <c r="D138">
         <v>177</v>
       </c>
     </row>
@@ -89044,7 +89203,7 @@
       <c r="C139" t="s">
         <v>1</v>
       </c>
-      <c r="D139" s="10">
+      <c r="D139">
         <v>167</v>
       </c>
     </row>
@@ -89052,7 +89211,7 @@
       <c r="C140" t="s">
         <v>48</v>
       </c>
-      <c r="D140" s="10">
+      <c r="D140">
         <v>108</v>
       </c>
     </row>
@@ -89066,7 +89225,7 @@
       <c r="C141" t="s">
         <v>32</v>
       </c>
-      <c r="D141" s="10">
+      <c r="D141">
         <v>187</v>
       </c>
     </row>
@@ -89074,7 +89233,7 @@
       <c r="C142" t="s">
         <v>34</v>
       </c>
-      <c r="D142" s="10">
+      <c r="D142">
         <v>156</v>
       </c>
     </row>
@@ -89082,7 +89241,7 @@
       <c r="C143" t="s">
         <v>55</v>
       </c>
-      <c r="D143" s="10">
+      <c r="D143">
         <v>138</v>
       </c>
     </row>
@@ -89090,7 +89249,7 @@
       <c r="C144" t="s">
         <v>3</v>
       </c>
-      <c r="D144" s="10">
+      <c r="D144">
         <v>121</v>
       </c>
     </row>
@@ -89098,7 +89257,7 @@
       <c r="C145" t="s">
         <v>6</v>
       </c>
-      <c r="D145" s="10">
+      <c r="D145">
         <v>103</v>
       </c>
     </row>
@@ -89106,7 +89265,7 @@
       <c r="C146" t="s">
         <v>68</v>
       </c>
-      <c r="D146" s="10">
+      <c r="D146">
         <v>100</v>
       </c>
     </row>
@@ -89114,7 +89273,7 @@
       <c r="C147" t="s">
         <v>9</v>
       </c>
-      <c r="D147" s="10">
+      <c r="D147">
         <v>89</v>
       </c>
     </row>
@@ -89122,7 +89281,7 @@
       <c r="C148" t="s">
         <v>2</v>
       </c>
-      <c r="D148" s="10">
+      <c r="D148">
         <v>80</v>
       </c>
     </row>
@@ -89130,7 +89289,7 @@
       <c r="C149" t="s">
         <v>5</v>
       </c>
-      <c r="D149" s="10">
+      <c r="D149">
         <v>71</v>
       </c>
     </row>
@@ -89138,7 +89297,7 @@
       <c r="C150" t="s">
         <v>45</v>
       </c>
-      <c r="D150" s="10">
+      <c r="D150">
         <v>58</v>
       </c>
     </row>
@@ -89146,7 +89305,7 @@
       <c r="C151" t="s">
         <v>43</v>
       </c>
-      <c r="D151" s="10">
+      <c r="D151">
         <v>54</v>
       </c>
     </row>
@@ -89154,7 +89313,7 @@
       <c r="C152" t="s">
         <v>48</v>
       </c>
-      <c r="D152" s="10">
+      <c r="D152">
         <v>38</v>
       </c>
     </row>
@@ -89162,7 +89321,7 @@
       <c r="C153" t="s">
         <v>8</v>
       </c>
-      <c r="D153" s="10">
+      <c r="D153">
         <v>34</v>
       </c>
     </row>
@@ -89170,7 +89329,7 @@
       <c r="C154" t="s">
         <v>11</v>
       </c>
-      <c r="D154" s="10">
+      <c r="D154">
         <v>34</v>
       </c>
     </row>
@@ -89178,7 +89337,7 @@
       <c r="C155" t="s">
         <v>110</v>
       </c>
-      <c r="D155" s="10">
+      <c r="D155">
         <v>19</v>
       </c>
     </row>
@@ -89186,7 +89345,7 @@
       <c r="C156" t="s">
         <v>33</v>
       </c>
-      <c r="D156" s="10">
+      <c r="D156">
         <v>17</v>
       </c>
     </row>
@@ -89194,7 +89353,7 @@
       <c r="C157" t="s">
         <v>70</v>
       </c>
-      <c r="D157" s="10">
+      <c r="D157">
         <v>15</v>
       </c>
     </row>
@@ -89202,7 +89361,7 @@
       <c r="C158" t="s">
         <v>71</v>
       </c>
-      <c r="D158" s="10">
+      <c r="D158">
         <v>8</v>
       </c>
     </row>
@@ -89210,7 +89369,7 @@
       <c r="C159" t="s">
         <v>69</v>
       </c>
-      <c r="D159" s="10">
+      <c r="D159">
         <v>2</v>
       </c>
     </row>
@@ -89218,7 +89377,7 @@
       <c r="C160" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="10">
+      <c r="D160">
         <v>2</v>
       </c>
     </row>
@@ -89232,7 +89391,7 @@
       <c r="C161" t="s">
         <v>34</v>
       </c>
-      <c r="D161" s="10">
+      <c r="D161">
         <v>674</v>
       </c>
     </row>
@@ -89240,7 +89399,7 @@
       <c r="C162" t="s">
         <v>32</v>
       </c>
-      <c r="D162" s="10">
+      <c r="D162">
         <v>528</v>
       </c>
     </row>
@@ -89248,7 +89407,7 @@
       <c r="C163" t="s">
         <v>33</v>
       </c>
-      <c r="D163" s="10">
+      <c r="D163">
         <v>305</v>
       </c>
     </row>
@@ -89256,7 +89415,7 @@
       <c r="C164" t="s">
         <v>48</v>
       </c>
-      <c r="D164" s="10">
+      <c r="D164">
         <v>217</v>
       </c>
     </row>
@@ -89264,7 +89423,7 @@
       <c r="C165" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="10">
+      <c r="D165">
         <v>117</v>
       </c>
     </row>
@@ -89272,7 +89431,7 @@
       <c r="C166" t="s">
         <v>49</v>
       </c>
-      <c r="D166" s="10">
+      <c r="D166">
         <v>64</v>
       </c>
     </row>
@@ -89286,7 +89445,7 @@
       <c r="C167" t="s">
         <v>34</v>
       </c>
-      <c r="D167" s="10">
+      <c r="D167">
         <v>464</v>
       </c>
     </row>
@@ -89294,7 +89453,7 @@
       <c r="C168" t="s">
         <v>32</v>
       </c>
-      <c r="D168" s="10">
+      <c r="D168">
         <v>239</v>
       </c>
     </row>
@@ -89302,7 +89461,7 @@
       <c r="C169" t="s">
         <v>1</v>
       </c>
-      <c r="D169" s="10">
+      <c r="D169">
         <v>235</v>
       </c>
     </row>
@@ -89310,7 +89469,7 @@
       <c r="C170" t="s">
         <v>3</v>
       </c>
-      <c r="D170" s="10">
+      <c r="D170">
         <v>182</v>
       </c>
     </row>
@@ -89318,7 +89477,7 @@
       <c r="C171" t="s">
         <v>43</v>
       </c>
-      <c r="D171" s="10">
+      <c r="D171">
         <v>154</v>
       </c>
     </row>
@@ -89326,7 +89485,7 @@
       <c r="C172" t="s">
         <v>5</v>
       </c>
-      <c r="D172" s="10">
+      <c r="D172">
         <v>153</v>
       </c>
     </row>
@@ -89334,7 +89493,7 @@
       <c r="C173" t="s">
         <v>2</v>
       </c>
-      <c r="D173" s="10">
+      <c r="D173">
         <v>152</v>
       </c>
     </row>
@@ -89342,7 +89501,7 @@
       <c r="C174" t="s">
         <v>6</v>
       </c>
-      <c r="D174" s="10">
+      <c r="D174">
         <v>149</v>
       </c>
     </row>
@@ -89350,7 +89509,7 @@
       <c r="C175" t="s">
         <v>68</v>
       </c>
-      <c r="D175" s="10">
+      <c r="D175">
         <v>142</v>
       </c>
     </row>
@@ -89358,7 +89517,7 @@
       <c r="C176" t="s">
         <v>8</v>
       </c>
-      <c r="D176" s="10">
+      <c r="D176">
         <v>83</v>
       </c>
     </row>
@@ -89366,7 +89525,7 @@
       <c r="C177" t="s">
         <v>33</v>
       </c>
-      <c r="D177" s="10">
+      <c r="D177">
         <v>77</v>
       </c>
     </row>
@@ -89374,7 +89533,7 @@
       <c r="C178" t="s">
         <v>45</v>
       </c>
-      <c r="D178" s="10">
+      <c r="D178">
         <v>68</v>
       </c>
     </row>
@@ -89382,7 +89541,7 @@
       <c r="C179" t="s">
         <v>9</v>
       </c>
-      <c r="D179" s="10">
+      <c r="D179">
         <v>64</v>
       </c>
     </row>
@@ -89390,7 +89549,7 @@
       <c r="C180" t="s">
         <v>48</v>
       </c>
-      <c r="D180" s="10">
+      <c r="D180">
         <v>25</v>
       </c>
     </row>
@@ -89398,7 +89557,7 @@
       <c r="C181" t="s">
         <v>11</v>
       </c>
-      <c r="D181" s="10">
+      <c r="D181">
         <v>17</v>
       </c>
     </row>
@@ -89406,7 +89565,7 @@
       <c r="C182" t="s">
         <v>70</v>
       </c>
-      <c r="D182" s="10">
+      <c r="D182">
         <v>10</v>
       </c>
     </row>
@@ -89414,7 +89573,7 @@
       <c r="C183" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="10">
+      <c r="D183">
         <v>4</v>
       </c>
     </row>
@@ -89422,7 +89581,7 @@
       <c r="C184" t="s">
         <v>110</v>
       </c>
-      <c r="D184" s="10">
+      <c r="D184">
         <v>4</v>
       </c>
     </row>
@@ -89430,7 +89589,7 @@
       <c r="C185" t="s">
         <v>69</v>
       </c>
-      <c r="D185" s="10">
+      <c r="D185">
         <v>0</v>
       </c>
     </row>
@@ -89438,7 +89597,7 @@
       <c r="C186" t="s">
         <v>71</v>
       </c>
-      <c r="D186" s="10">
+      <c r="D186">
         <v>0</v>
       </c>
     </row>
@@ -89452,7 +89611,7 @@
       <c r="C187" t="s">
         <v>34</v>
       </c>
-      <c r="D187" s="10">
+      <c r="D187">
         <v>300</v>
       </c>
     </row>
@@ -89460,7 +89619,7 @@
       <c r="C188" t="s">
         <v>33</v>
       </c>
-      <c r="D188" s="10">
+      <c r="D188">
         <v>251</v>
       </c>
     </row>
@@ -89468,7 +89627,7 @@
       <c r="C189" t="s">
         <v>1</v>
       </c>
-      <c r="D189" s="10">
+      <c r="D189">
         <v>180</v>
       </c>
     </row>
@@ -89476,7 +89635,7 @@
       <c r="C190" t="s">
         <v>32</v>
       </c>
-      <c r="D190" s="10">
+      <c r="D190">
         <v>167</v>
       </c>
     </row>
@@ -89484,7 +89643,7 @@
       <c r="C191" t="s">
         <v>0</v>
       </c>
-      <c r="D191" s="10">
+      <c r="D191">
         <v>158</v>
       </c>
     </row>
@@ -89492,7 +89651,7 @@
       <c r="C192" t="s">
         <v>3</v>
       </c>
-      <c r="D192" s="10">
+      <c r="D192">
         <v>120</v>
       </c>
     </row>
@@ -89506,7 +89665,7 @@
       <c r="C193" t="s">
         <v>32</v>
       </c>
-      <c r="D193" s="10">
+      <c r="D193">
         <v>245</v>
       </c>
     </row>
@@ -89514,7 +89673,7 @@
       <c r="C194" t="s">
         <v>1</v>
       </c>
-      <c r="D194" s="10">
+      <c r="D194">
         <v>141</v>
       </c>
     </row>
@@ -89522,7 +89681,7 @@
       <c r="C195" t="s">
         <v>33</v>
       </c>
-      <c r="D195" s="10">
+      <c r="D195">
         <v>136</v>
       </c>
     </row>
@@ -89530,7 +89689,7 @@
       <c r="C196" t="s">
         <v>34</v>
       </c>
-      <c r="D196" s="10">
+      <c r="D196">
         <v>97</v>
       </c>
     </row>
@@ -89538,7 +89697,7 @@
       <c r="C197" t="s">
         <v>43</v>
       </c>
-      <c r="D197" s="10">
+      <c r="D197">
         <v>35</v>
       </c>
     </row>
@@ -89546,7 +89705,7 @@
       <c r="C198" t="s">
         <v>42</v>
       </c>
-      <c r="D198" s="10">
+      <c r="D198">
         <v>26</v>
       </c>
     </row>
@@ -89560,7 +89719,7 @@
       <c r="C199" t="s">
         <v>34</v>
       </c>
-      <c r="D199" s="10">
+      <c r="D199">
         <v>269</v>
       </c>
     </row>
@@ -89568,7 +89727,7 @@
       <c r="C200" t="s">
         <v>0</v>
       </c>
-      <c r="D200" s="10">
+      <c r="D200">
         <v>164</v>
       </c>
     </row>
@@ -89576,7 +89735,7 @@
       <c r="C201" t="s">
         <v>32</v>
       </c>
-      <c r="D201" s="10">
+      <c r="D201">
         <v>158</v>
       </c>
     </row>
@@ -89584,7 +89743,7 @@
       <c r="C202" t="s">
         <v>33</v>
       </c>
-      <c r="D202" s="10">
+      <c r="D202">
         <v>125</v>
       </c>
     </row>
@@ -89592,7 +89751,7 @@
       <c r="C203" t="s">
         <v>1</v>
       </c>
-      <c r="D203" s="10">
+      <c r="D203">
         <v>120</v>
       </c>
     </row>
@@ -89600,7 +89759,7 @@
       <c r="C204" t="s">
         <v>45</v>
       </c>
-      <c r="D204" s="10">
+      <c r="D204">
         <v>65</v>
       </c>
     </row>
@@ -89614,7 +89773,7 @@
       <c r="C205" t="s">
         <v>34</v>
       </c>
-      <c r="D205" s="10">
+      <c r="D205">
         <v>51</v>
       </c>
     </row>
@@ -89622,7 +89781,7 @@
       <c r="C206" t="s">
         <v>3</v>
       </c>
-      <c r="D206" s="10">
+      <c r="D206">
         <v>33</v>
       </c>
     </row>
@@ -89630,7 +89789,7 @@
       <c r="C207" t="s">
         <v>2</v>
       </c>
-      <c r="D207" s="10">
+      <c r="D207">
         <v>24</v>
       </c>
     </row>
@@ -89638,7 +89797,7 @@
       <c r="C208" t="s">
         <v>68</v>
       </c>
-      <c r="D208" s="10">
+      <c r="D208">
         <v>20</v>
       </c>
     </row>
@@ -89646,7 +89805,7 @@
       <c r="C209" t="s">
         <v>1</v>
       </c>
-      <c r="D209" s="10">
+      <c r="D209">
         <v>15</v>
       </c>
     </row>
@@ -89654,7 +89813,7 @@
       <c r="C210" t="s">
         <v>33</v>
       </c>
-      <c r="D210" s="10">
+      <c r="D210">
         <v>14</v>
       </c>
     </row>
@@ -89662,7 +89821,7 @@
       <c r="C211" t="s">
         <v>8</v>
       </c>
-      <c r="D211" s="10">
+      <c r="D211">
         <v>10</v>
       </c>
     </row>
@@ -89670,7 +89829,7 @@
       <c r="C212" t="s">
         <v>9</v>
       </c>
-      <c r="D212" s="10">
+      <c r="D212">
         <v>10</v>
       </c>
     </row>
@@ -89678,7 +89837,7 @@
       <c r="C213" t="s">
         <v>6</v>
       </c>
-      <c r="D213" s="10">
+      <c r="D213">
         <v>8</v>
       </c>
     </row>
@@ -89686,7 +89845,7 @@
       <c r="C214" t="s">
         <v>11</v>
       </c>
-      <c r="D214" s="10">
+      <c r="D214">
         <v>6</v>
       </c>
     </row>
@@ -89694,7 +89853,7 @@
       <c r="C215" t="s">
         <v>45</v>
       </c>
-      <c r="D215" s="10">
+      <c r="D215">
         <v>5</v>
       </c>
     </row>
@@ -89702,7 +89861,7 @@
       <c r="C216" t="s">
         <v>43</v>
       </c>
-      <c r="D216" s="10">
+      <c r="D216">
         <v>4</v>
       </c>
     </row>
@@ -89710,7 +89869,7 @@
       <c r="C217" t="s">
         <v>48</v>
       </c>
-      <c r="D217" s="10">
+      <c r="D217">
         <v>2</v>
       </c>
     </row>
@@ -89718,7 +89877,7 @@
       <c r="C218" t="s">
         <v>5</v>
       </c>
-      <c r="D218" s="10">
+      <c r="D218">
         <v>1</v>
       </c>
     </row>
@@ -89726,7 +89885,7 @@
       <c r="C219" t="s">
         <v>71</v>
       </c>
-      <c r="D219" s="10">
+      <c r="D219">
         <v>0</v>
       </c>
     </row>
@@ -89734,7 +89893,7 @@
       <c r="C220" t="s">
         <v>69</v>
       </c>
-      <c r="D220" s="10">
+      <c r="D220">
         <v>0</v>
       </c>
     </row>
@@ -89742,7 +89901,7 @@
       <c r="C221" t="s">
         <v>32</v>
       </c>
-      <c r="D221" s="10">
+      <c r="D221">
         <v>0</v>
       </c>
     </row>
@@ -89750,7 +89909,7 @@
       <c r="C222" t="s">
         <v>110</v>
       </c>
-      <c r="D222" s="10">
+      <c r="D222">
         <v>0</v>
       </c>
     </row>
@@ -89758,7 +89917,7 @@
       <c r="C223" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="10">
+      <c r="D223">
         <v>0</v>
       </c>
     </row>
@@ -89766,7 +89925,7 @@
       <c r="C224" t="s">
         <v>70</v>
       </c>
-      <c r="D224" s="10">
+      <c r="D224">
         <v>0</v>
       </c>
     </row>
@@ -89780,7 +89939,7 @@
       <c r="C225" t="s">
         <v>34</v>
       </c>
-      <c r="D225" s="10">
+      <c r="D225">
         <v>275</v>
       </c>
     </row>
@@ -89788,7 +89947,7 @@
       <c r="C226" t="s">
         <v>1</v>
       </c>
-      <c r="D226" s="10">
+      <c r="D226">
         <v>175</v>
       </c>
     </row>
@@ -89796,7 +89955,7 @@
       <c r="C227" t="s">
         <v>32</v>
       </c>
-      <c r="D227" s="10">
+      <c r="D227">
         <v>113</v>
       </c>
     </row>
@@ -89804,7 +89963,7 @@
       <c r="C228" t="s">
         <v>33</v>
       </c>
-      <c r="D228" s="10">
+      <c r="D228">
         <v>93</v>
       </c>
     </row>
@@ -89812,7 +89971,7 @@
       <c r="C229" t="s">
         <v>48</v>
       </c>
-      <c r="D229" s="10">
+      <c r="D229">
         <v>77</v>
       </c>
     </row>
@@ -89820,7 +89979,7 @@
       <c r="C230" t="s">
         <v>49</v>
       </c>
-      <c r="D230" s="10">
+      <c r="D230">
         <v>70</v>
       </c>
     </row>
@@ -89834,7 +89993,7 @@
       <c r="C231" t="s">
         <v>33</v>
       </c>
-      <c r="D231" s="10">
+      <c r="D231">
         <v>173</v>
       </c>
     </row>
@@ -89842,7 +90001,7 @@
       <c r="C232" t="s">
         <v>34</v>
       </c>
-      <c r="D232" s="10">
+      <c r="D232">
         <v>139</v>
       </c>
     </row>
@@ -89850,7 +90009,7 @@
       <c r="C233" t="s">
         <v>48</v>
       </c>
-      <c r="D233" s="10">
+      <c r="D233">
         <v>33</v>
       </c>
     </row>
@@ -89858,7 +90017,7 @@
       <c r="C234" t="s">
         <v>32</v>
       </c>
-      <c r="D234" s="10">
+      <c r="D234">
         <v>33</v>
       </c>
     </row>
@@ -89866,7 +90025,7 @@
       <c r="C235" t="s">
         <v>42</v>
       </c>
-      <c r="D235" s="10">
+      <c r="D235">
         <v>16</v>
       </c>
     </row>
@@ -89874,7 +90033,7 @@
       <c r="C236" t="s">
         <v>55</v>
       </c>
-      <c r="D236" s="10">
+      <c r="D236">
         <v>7</v>
       </c>
     </row>
@@ -89888,7 +90047,7 @@
       <c r="C237" t="s">
         <v>34</v>
       </c>
-      <c r="D237" s="10">
+      <c r="D237">
         <v>318</v>
       </c>
     </row>
@@ -89896,7 +90055,7 @@
       <c r="C238" t="s">
         <v>32</v>
       </c>
-      <c r="D238" s="10">
+      <c r="D238">
         <v>271</v>
       </c>
     </row>
@@ -89904,7 +90063,7 @@
       <c r="C239" t="s">
         <v>33</v>
       </c>
-      <c r="D239" s="10">
+      <c r="D239">
         <v>211</v>
       </c>
     </row>
@@ -89912,7 +90071,7 @@
       <c r="C240" t="s">
         <v>0</v>
       </c>
-      <c r="D240" s="10">
+      <c r="D240">
         <v>162</v>
       </c>
     </row>
@@ -89920,7 +90079,7 @@
       <c r="C241" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="10">
+      <c r="D241">
         <v>83</v>
       </c>
     </row>
@@ -89928,7 +90087,7 @@
       <c r="C242" t="s">
         <v>43</v>
       </c>
-      <c r="D242" s="10">
+      <c r="D242">
         <v>73</v>
       </c>
     </row>
@@ -89942,7 +90101,7 @@
       <c r="C243" t="s">
         <v>34</v>
       </c>
-      <c r="D243" s="10">
+      <c r="D243">
         <v>295</v>
       </c>
     </row>
@@ -89950,7 +90109,7 @@
       <c r="C244" t="s">
         <v>32</v>
       </c>
-      <c r="D244" s="10">
+      <c r="D244">
         <v>242</v>
       </c>
     </row>
@@ -89958,7 +90117,7 @@
       <c r="C245" t="s">
         <v>33</v>
       </c>
-      <c r="D245" s="10">
+      <c r="D245">
         <v>152</v>
       </c>
     </row>
@@ -89966,7 +90125,7 @@
       <c r="C246" t="s">
         <v>48</v>
       </c>
-      <c r="D246" s="10">
+      <c r="D246">
         <v>109</v>
       </c>
     </row>
@@ -89974,7 +90133,7 @@
       <c r="C247" t="s">
         <v>8</v>
       </c>
-      <c r="D247" s="10">
+      <c r="D247">
         <v>103</v>
       </c>
     </row>
@@ -89982,7 +90141,7 @@
       <c r="C248" t="s">
         <v>43</v>
       </c>
-      <c r="D248" s="10">
+      <c r="D248">
         <v>40</v>
       </c>
     </row>
@@ -89996,7 +90155,7 @@
       <c r="C249" t="s">
         <v>32</v>
       </c>
-      <c r="D249" s="10">
+      <c r="D249">
         <v>413</v>
       </c>
     </row>
@@ -90004,7 +90163,7 @@
       <c r="C250" t="s">
         <v>1</v>
       </c>
-      <c r="D250" s="10">
+      <c r="D250">
         <v>387</v>
       </c>
     </row>
@@ -90012,7 +90171,7 @@
       <c r="C251" t="s">
         <v>0</v>
       </c>
-      <c r="D251" s="10">
+      <c r="D251">
         <v>307</v>
       </c>
     </row>
@@ -90020,7 +90179,7 @@
       <c r="C252" t="s">
         <v>34</v>
       </c>
-      <c r="D252" s="10">
+      <c r="D252">
         <v>221</v>
       </c>
     </row>
@@ -90028,7 +90187,7 @@
       <c r="C253" t="s">
         <v>68</v>
       </c>
-      <c r="D253" s="10">
+      <c r="D253">
         <v>198</v>
       </c>
     </row>
@@ -90036,7 +90195,7 @@
       <c r="C254" t="s">
         <v>2</v>
       </c>
-      <c r="D254" s="10">
+      <c r="D254">
         <v>179</v>
       </c>
     </row>
@@ -90044,7 +90203,7 @@
       <c r="C255" t="s">
         <v>3</v>
       </c>
-      <c r="D255" s="10">
+      <c r="D255">
         <v>132</v>
       </c>
     </row>
@@ -90052,7 +90211,7 @@
       <c r="C256" t="s">
         <v>6</v>
       </c>
-      <c r="D256" s="10">
+      <c r="D256">
         <v>109</v>
       </c>
     </row>
@@ -90060,7 +90219,7 @@
       <c r="C257" t="s">
         <v>8</v>
       </c>
-      <c r="D257" s="10">
+      <c r="D257">
         <v>93</v>
       </c>
     </row>
@@ -90068,7 +90227,7 @@
       <c r="C258" t="s">
         <v>45</v>
       </c>
-      <c r="D258" s="10">
+      <c r="D258">
         <v>75</v>
       </c>
     </row>
@@ -90076,7 +90235,7 @@
       <c r="C259" t="s">
         <v>5</v>
       </c>
-      <c r="D259" s="10">
+      <c r="D259">
         <v>71</v>
       </c>
     </row>
@@ -90084,7 +90243,7 @@
       <c r="C260" t="s">
         <v>9</v>
       </c>
-      <c r="D260" s="10">
+      <c r="D260">
         <v>58</v>
       </c>
     </row>
@@ -90092,7 +90251,7 @@
       <c r="C261" t="s">
         <v>33</v>
       </c>
-      <c r="D261" s="10">
+      <c r="D261">
         <v>39</v>
       </c>
     </row>
@@ -90100,7 +90259,7 @@
       <c r="C262" t="s">
         <v>11</v>
       </c>
-      <c r="D262" s="10">
+      <c r="D262">
         <v>29</v>
       </c>
     </row>
@@ -90108,7 +90267,7 @@
       <c r="C263" t="s">
         <v>48</v>
       </c>
-      <c r="D263" s="10">
+      <c r="D263">
         <v>16</v>
       </c>
     </row>
@@ -90116,7 +90275,7 @@
       <c r="C264" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="10">
+      <c r="D264">
         <v>6</v>
       </c>
     </row>
@@ -90124,7 +90283,7 @@
       <c r="C265" t="s">
         <v>110</v>
       </c>
-      <c r="D265" s="10">
+      <c r="D265">
         <v>4</v>
       </c>
     </row>
@@ -90132,7 +90291,7 @@
       <c r="C266" t="s">
         <v>69</v>
       </c>
-      <c r="D266" s="10">
+      <c r="D266">
         <v>3</v>
       </c>
     </row>
@@ -90140,7 +90299,7 @@
       <c r="C267" t="s">
         <v>71</v>
       </c>
-      <c r="D267" s="10">
+      <c r="D267">
         <v>1</v>
       </c>
     </row>
@@ -90148,7 +90307,7 @@
       <c r="C268" t="s">
         <v>70</v>
       </c>
-      <c r="D268" s="10">
+      <c r="D268">
         <v>0</v>
       </c>
     </row>
@@ -90162,7 +90321,7 @@
       <c r="C269" t="s">
         <v>0</v>
       </c>
-      <c r="D269" s="10">
+      <c r="D269">
         <v>319</v>
       </c>
     </row>
@@ -90170,7 +90329,7 @@
       <c r="C270" t="s">
         <v>1</v>
       </c>
-      <c r="D270" s="10">
+      <c r="D270">
         <v>295</v>
       </c>
     </row>
@@ -90178,7 +90337,7 @@
       <c r="C271" t="s">
         <v>34</v>
       </c>
-      <c r="D271" s="10">
+      <c r="D271">
         <v>278</v>
       </c>
     </row>
@@ -90186,7 +90345,7 @@
       <c r="C272" t="s">
         <v>32</v>
       </c>
-      <c r="D272" s="10">
+      <c r="D272">
         <v>266</v>
       </c>
     </row>
@@ -90194,7 +90353,7 @@
       <c r="C273" t="s">
         <v>2</v>
       </c>
-      <c r="D273" s="10">
+      <c r="D273">
         <v>185</v>
       </c>
     </row>
@@ -90202,7 +90361,7 @@
       <c r="C274" t="s">
         <v>3</v>
       </c>
-      <c r="D274" s="10">
+      <c r="D274">
         <v>165</v>
       </c>
     </row>
@@ -90210,7 +90369,7 @@
       <c r="C275" t="s">
         <v>43</v>
       </c>
-      <c r="D275" s="10">
+      <c r="D275">
         <v>133</v>
       </c>
     </row>
@@ -90218,7 +90377,7 @@
       <c r="C276" t="s">
         <v>68</v>
       </c>
-      <c r="D276" s="10">
+      <c r="D276">
         <v>129</v>
       </c>
     </row>
@@ -90226,7 +90385,7 @@
       <c r="C277" t="s">
         <v>9</v>
       </c>
-      <c r="D277" s="10">
+      <c r="D277">
         <v>117</v>
       </c>
     </row>
@@ -90234,7 +90393,7 @@
       <c r="C278" t="s">
         <v>6</v>
       </c>
-      <c r="D278" s="10">
+      <c r="D278">
         <v>97</v>
       </c>
     </row>
@@ -90242,7 +90401,7 @@
       <c r="C279" t="s">
         <v>45</v>
       </c>
-      <c r="D279" s="10">
+      <c r="D279">
         <v>78</v>
       </c>
     </row>
@@ -90250,7 +90409,7 @@
       <c r="C280" t="s">
         <v>33</v>
       </c>
-      <c r="D280" s="10">
+      <c r="D280">
         <v>54</v>
       </c>
     </row>
@@ -90258,7 +90417,7 @@
       <c r="C281" t="s">
         <v>8</v>
       </c>
-      <c r="D281" s="10">
+      <c r="D281">
         <v>36</v>
       </c>
     </row>
@@ -90266,7 +90425,7 @@
       <c r="C282" t="s">
         <v>48</v>
       </c>
-      <c r="D282" s="10">
+      <c r="D282">
         <v>28</v>
       </c>
     </row>
@@ -90274,7 +90433,7 @@
       <c r="C283" t="s">
         <v>11</v>
       </c>
-      <c r="D283" s="10">
+      <c r="D283">
         <v>27</v>
       </c>
     </row>
@@ -90282,7 +90441,7 @@
       <c r="C284" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="10">
+      <c r="D284">
         <v>6</v>
       </c>
     </row>
@@ -90290,7 +90449,7 @@
       <c r="C285" t="s">
         <v>110</v>
       </c>
-      <c r="D285" s="10">
+      <c r="D285">
         <v>4</v>
       </c>
     </row>
@@ -90298,7 +90457,7 @@
       <c r="C286" t="s">
         <v>70</v>
       </c>
-      <c r="D286" s="10">
+      <c r="D286">
         <v>2</v>
       </c>
     </row>
@@ -90306,7 +90465,7 @@
       <c r="C287" t="s">
         <v>69</v>
       </c>
-      <c r="D287" s="10">
+      <c r="D287">
         <v>1</v>
       </c>
     </row>
@@ -90314,7 +90473,7 @@
       <c r="C288" t="s">
         <v>71</v>
       </c>
-      <c r="D288" s="10">
+      <c r="D288">
         <v>0</v>
       </c>
     </row>
@@ -90328,7 +90487,7 @@
       <c r="C289" t="s">
         <v>32</v>
       </c>
-      <c r="D289" s="10">
+      <c r="D289">
         <v>241</v>
       </c>
     </row>
@@ -90336,7 +90495,7 @@
       <c r="C290" t="s">
         <v>0</v>
       </c>
-      <c r="D290" s="10">
+      <c r="D290">
         <v>211</v>
       </c>
     </row>
@@ -90344,7 +90503,7 @@
       <c r="C291" t="s">
         <v>1</v>
       </c>
-      <c r="D291" s="10">
+      <c r="D291">
         <v>197</v>
       </c>
     </row>
@@ -90352,7 +90511,7 @@
       <c r="C292" t="s">
         <v>34</v>
       </c>
-      <c r="D292" s="10">
+      <c r="D292">
         <v>123</v>
       </c>
     </row>
@@ -90360,7 +90519,7 @@
       <c r="C293" t="s">
         <v>33</v>
       </c>
-      <c r="D293" s="10">
+      <c r="D293">
         <v>119</v>
       </c>
     </row>
@@ -90368,7 +90527,7 @@
       <c r="C294" t="s">
         <v>45</v>
       </c>
-      <c r="D294" s="10">
+      <c r="D294">
         <v>114</v>
       </c>
     </row>
@@ -90382,7 +90541,7 @@
       <c r="C295" t="s">
         <v>34</v>
       </c>
-      <c r="D295" s="10">
+      <c r="D295">
         <v>332</v>
       </c>
     </row>
@@ -90390,7 +90549,7 @@
       <c r="C296" t="s">
         <v>32</v>
       </c>
-      <c r="D296" s="10">
+      <c r="D296">
         <v>282</v>
       </c>
     </row>
@@ -90398,7 +90557,7 @@
       <c r="C297" t="s">
         <v>2</v>
       </c>
-      <c r="D297" s="10">
+      <c r="D297">
         <v>258</v>
       </c>
     </row>
@@ -90406,7 +90565,7 @@
       <c r="C298" t="s">
         <v>1</v>
       </c>
-      <c r="D298" s="10">
+      <c r="D298">
         <v>257</v>
       </c>
     </row>
@@ -90414,7 +90573,7 @@
       <c r="C299" t="s">
         <v>33</v>
       </c>
-      <c r="D299" s="10">
+      <c r="D299">
         <v>256</v>
       </c>
     </row>
@@ -90422,7 +90581,7 @@
       <c r="C300" t="s">
         <v>6</v>
       </c>
-      <c r="D300" s="10">
+      <c r="D300">
         <v>242</v>
       </c>
     </row>
@@ -90430,7 +90589,7 @@
       <c r="C301" t="s">
         <v>0</v>
       </c>
-      <c r="D301" s="10">
+      <c r="D301">
         <v>221</v>
       </c>
     </row>
@@ -90438,7 +90597,7 @@
       <c r="C302" t="s">
         <v>68</v>
       </c>
-      <c r="D302" s="10">
+      <c r="D302">
         <v>154</v>
       </c>
     </row>
@@ -90446,7 +90605,7 @@
       <c r="C303" t="s">
         <v>9</v>
       </c>
-      <c r="D303" s="10">
+      <c r="D303">
         <v>129</v>
       </c>
     </row>
@@ -90454,7 +90613,7 @@
       <c r="C304" t="s">
         <v>3</v>
       </c>
-      <c r="D304" s="10">
+      <c r="D304">
         <v>72</v>
       </c>
     </row>
@@ -90462,7 +90621,7 @@
       <c r="C305" t="s">
         <v>43</v>
       </c>
-      <c r="D305" s="10">
+      <c r="D305">
         <v>67</v>
       </c>
     </row>
@@ -90470,7 +90629,7 @@
       <c r="C306" t="s">
         <v>8</v>
       </c>
-      <c r="D306" s="10">
+      <c r="D306">
         <v>60</v>
       </c>
     </row>
@@ -90478,7 +90637,7 @@
       <c r="C307" t="s">
         <v>79</v>
       </c>
-      <c r="D307" s="10">
+      <c r="D307">
         <v>58</v>
       </c>
     </row>
@@ -90486,7 +90645,7 @@
       <c r="C308" t="s">
         <v>49</v>
       </c>
-      <c r="D308" s="10">
+      <c r="D308">
         <v>23</v>
       </c>
     </row>
@@ -90494,7 +90653,7 @@
       <c r="C309" t="s">
         <v>11</v>
       </c>
-      <c r="D309" s="10">
+      <c r="D309">
         <v>14</v>
       </c>
     </row>
@@ -90502,7 +90661,7 @@
       <c r="C310" t="s">
         <v>12</v>
       </c>
-      <c r="D310" s="10">
+      <c r="D310">
         <v>6</v>
       </c>
     </row>
@@ -90510,7 +90669,7 @@
       <c r="C311" t="s">
         <v>71</v>
       </c>
-      <c r="D311" s="10">
+      <c r="D311">
         <v>6</v>
       </c>
     </row>
@@ -90518,7 +90677,7 @@
       <c r="C312" t="s">
         <v>45</v>
       </c>
-      <c r="D312" s="10">
+      <c r="D312">
         <v>6</v>
       </c>
     </row>
@@ -90526,7 +90685,7 @@
       <c r="C313" t="s">
         <v>80</v>
       </c>
-      <c r="D313" s="10">
+      <c r="D313">
         <v>1</v>
       </c>
     </row>
@@ -90534,7 +90693,7 @@
       <c r="C314" t="s">
         <v>69</v>
       </c>
-      <c r="D314" s="10">
+      <c r="D314">
         <v>1</v>
       </c>
     </row>
@@ -90548,7 +90707,7 @@
       <c r="C315" t="s">
         <v>34</v>
       </c>
-      <c r="D315" s="10">
+      <c r="D315">
         <v>404</v>
       </c>
     </row>
@@ -90556,7 +90715,7 @@
       <c r="C316" t="s">
         <v>0</v>
       </c>
-      <c r="D316" s="10">
+      <c r="D316">
         <v>144</v>
       </c>
     </row>
@@ -90564,7 +90723,7 @@
       <c r="C317" t="s">
         <v>32</v>
       </c>
-      <c r="D317" s="10">
+      <c r="D317">
         <v>142</v>
       </c>
     </row>
@@ -90572,7 +90731,7 @@
       <c r="C318" t="s">
         <v>1</v>
       </c>
-      <c r="D318" s="10">
+      <c r="D318">
         <v>101</v>
       </c>
     </row>
@@ -90580,7 +90739,7 @@
       <c r="C319" t="s">
         <v>2</v>
       </c>
-      <c r="D319" s="10">
+      <c r="D319">
         <v>99</v>
       </c>
     </row>
@@ -90588,7 +90747,7 @@
       <c r="C320" t="s">
         <v>33</v>
       </c>
-      <c r="D320" s="10">
+      <c r="D320">
         <v>87</v>
       </c>
     </row>
@@ -90602,7 +90761,7 @@
       <c r="C321" t="s">
         <v>32</v>
       </c>
-      <c r="D321" s="10">
+      <c r="D321">
         <v>225</v>
       </c>
     </row>
@@ -90610,7 +90769,7 @@
       <c r="C322" t="s">
         <v>33</v>
       </c>
-      <c r="D322" s="10">
+      <c r="D322">
         <v>216</v>
       </c>
     </row>
@@ -90618,7 +90777,7 @@
       <c r="C323" t="s">
         <v>34</v>
       </c>
-      <c r="D323" s="10">
+      <c r="D323">
         <v>213</v>
       </c>
     </row>
@@ -90626,7 +90785,7 @@
       <c r="C324" t="s">
         <v>0</v>
       </c>
-      <c r="D324" s="10">
+      <c r="D324">
         <v>158</v>
       </c>
     </row>
@@ -90634,7 +90793,7 @@
       <c r="C325" t="s">
         <v>2</v>
       </c>
-      <c r="D325" s="10">
+      <c r="D325">
         <v>141</v>
       </c>
     </row>
@@ -90642,7 +90801,7 @@
       <c r="C326" t="s">
         <v>42</v>
       </c>
-      <c r="D326" s="10">
+      <c r="D326">
         <v>24</v>
       </c>
     </row>
@@ -90650,7 +90809,7 @@
       <c r="A327" t="s">
         <v>111</v>
       </c>
-      <c r="D327" s="10">
+      <c r="D327">
         <v>34681</v>
       </c>
     </row>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42AF9F97-F603-4E41-AD77-759F2A45D507}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{264BFA19-53BA-425B-AF0F-3355E67EDAF5}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16139" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16136" uniqueCount="197">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -755,6 +755,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -87250,7 +87254,7 @@
   <cols>
     <col min="1" max="1" width="12.53125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="17.265625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="35.73046875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -87561,7 +87565,7 @@
         <v>Red Bull Ring</v>
       </c>
       <c r="F11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K11" t="s">
         <v>117</v>
@@ -87579,7 +87583,6 @@
         <v>11</v>
       </c>
       <c r="C12" s="9">
-        <f t="shared" ref="C12:C25" si="4">C11+7</f>
         <v>46103</v>
       </c>
       <c r="D12" t="s">
@@ -87608,7 +87611,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="C13:C25" si="4">C12+7</f>
         <v>46110</v>
       </c>
       <c r="D13" t="s">
@@ -87844,11 +87847,11 @@
         <v>46166</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>176</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="3"/>
-        <v>Jeddah Corniche Circuit</v>
+        <v>Autódromo José Carlos Pace (Interlagos)</v>
       </c>
       <c r="F21" t="s">
         <v>196</v>
@@ -87873,11 +87876,11 @@
         <v>46173</v>
       </c>
       <c r="D22" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="3"/>
-        <v>Autódromo José Carlos Pace (Interlagos)</v>
+        <v>Las Vegas Strip Circuit</v>
       </c>
       <c r="F22" t="s">
         <v>196</v>
@@ -87902,11 +87905,11 @@
         <v>46180</v>
       </c>
       <c r="D23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E23" t="str">
         <f t="shared" si="3"/>
-        <v>Las Vegas Strip Circuit</v>
+        <v>Lusail International Circuit</v>
       </c>
       <c r="F23" t="s">
         <v>196</v>
@@ -87931,11 +87934,11 @@
         <v>46187</v>
       </c>
       <c r="D24" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="E24" t="str">
         <f t="shared" si="3"/>
-        <v>Lusail International Circuit</v>
+        <v>Yas Marina Circuit</v>
       </c>
       <c r="F24" t="s">
         <v>196</v>
@@ -87948,27 +87951,7 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>31</v>
-      </c>
-      <c r="B25">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="C25" s="9">
-        <f t="shared" si="4"/>
-        <v>46194</v>
-      </c>
-      <c r="D25" t="s">
-        <v>129</v>
-      </c>
-      <c r="E25" t="str">
-        <f t="shared" si="3"/>
-        <v>Yas Marina Circuit</v>
-      </c>
-      <c r="F25" t="s">
-        <v>196</v>
-      </c>
+      <c r="C25" s="9"/>
       <c r="K25" t="s">
         <v>188</v>
       </c>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{264BFA19-53BA-425B-AF0F-3355E67EDAF5}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2093336-7C16-47A7-A5E9-092032614131}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16136" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16196" uniqueCount="197">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -755,10 +755,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -58896,7 +58892,7 @@
         <v>32</v>
       </c>
       <c r="G1408" t="str">
-        <f t="shared" ref="G1408:G1467" si="0">VLOOKUP(F1408,$M$1408:$N$1427,2,FALSE)</f>
+        <f t="shared" ref="G1408:G1471" si="0">VLOOKUP(F1408,$M$1408:$N$1427,2,FALSE)</f>
         <v>Alpine</v>
       </c>
       <c r="H1408">
@@ -60797,166 +60793,606 @@
       </c>
     </row>
     <row r="1468" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1468" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1468">
+        <v>11</v>
+      </c>
       <c r="E1468" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1468" t="s">
-        <v>37</v>
+        <v>127</v>
+      </c>
+      <c r="F1468" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1468" t="str">
+        <f t="shared" si="0"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1468">
+        <v>1</v>
+      </c>
+      <c r="I1468">
+        <v>25</v>
       </c>
     </row>
     <row r="1469" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1469" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1469">
+        <v>11</v>
+      </c>
       <c r="E1469" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1469" t="s">
-        <v>37</v>
+        <v>127</v>
+      </c>
+      <c r="F1469" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1469" t="str">
+        <f t="shared" si="0"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1469">
+        <v>2</v>
+      </c>
+      <c r="I1469">
+        <v>18</v>
       </c>
     </row>
     <row r="1470" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1470" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1470">
+        <v>11</v>
+      </c>
       <c r="E1470" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1470" t="s">
-        <v>37</v>
+        <v>127</v>
+      </c>
+      <c r="F1470" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1470" t="str">
+        <f t="shared" si="0"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1470">
+        <v>3</v>
+      </c>
+      <c r="I1470">
+        <v>15</v>
       </c>
     </row>
     <row r="1471" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1471" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1471">
+        <v>11</v>
+      </c>
       <c r="E1471" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1471" t="s">
-        <v>37</v>
+        <v>127</v>
+      </c>
+      <c r="F1471" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1471" t="str">
+        <f t="shared" si="0"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1471">
+        <v>4</v>
+      </c>
+      <c r="I1471">
+        <v>12</v>
       </c>
     </row>
     <row r="1472" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1472" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1472">
+        <v>11</v>
+      </c>
       <c r="E1472" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1472" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1473" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1472" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1472" t="str">
+        <f t="shared" ref="G1472:G1487" si="1">VLOOKUP(F1472,$M$1408:$N$1427,2,FALSE)</f>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1472">
+        <v>5</v>
+      </c>
+      <c r="I1472">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1473" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1473">
+        <v>11</v>
+      </c>
       <c r="E1473" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1473" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1474" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1473" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1473" t="str">
+        <f t="shared" si="1"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1473">
+        <v>6</v>
+      </c>
+      <c r="I1473">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1474" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1474">
+        <v>11</v>
+      </c>
       <c r="E1474" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1474" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1475" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1474" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1474" t="str">
+        <f t="shared" si="1"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1474">
+        <v>7</v>
+      </c>
+      <c r="I1474">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1475" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1475">
+        <v>11</v>
+      </c>
       <c r="E1475" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1475" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1476" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1475" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1475" t="str">
+        <f t="shared" si="1"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1475">
+        <v>8</v>
+      </c>
+      <c r="I1475">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1476" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1476">
+        <v>11</v>
+      </c>
       <c r="E1476" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1476" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1477" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1476" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1476" t="str">
+        <f t="shared" si="1"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1476">
+        <v>9</v>
+      </c>
+      <c r="I1476">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1477" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1477">
+        <v>11</v>
+      </c>
       <c r="E1477" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1477" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1478" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1477" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1477" t="str">
+        <f t="shared" si="1"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1477">
+        <v>10</v>
+      </c>
+      <c r="I1477">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1478" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1478">
+        <v>11</v>
+      </c>
       <c r="E1478" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1478" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1479" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1478" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1478" t="str">
+        <f t="shared" si="1"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1478">
+        <v>11</v>
+      </c>
+      <c r="I1478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1479" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1479">
+        <v>11</v>
+      </c>
       <c r="E1479" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1479" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1480" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1479" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1479" t="str">
+        <f t="shared" si="1"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1479">
+        <v>12</v>
+      </c>
+      <c r="I1479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1480" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1480">
+        <v>11</v>
+      </c>
       <c r="E1480" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1480" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1481" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1480" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1480" t="str">
+        <f t="shared" si="1"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1480">
+        <v>13</v>
+      </c>
+      <c r="I1480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1481" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1481">
+        <v>11</v>
+      </c>
       <c r="E1481" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1481" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1482" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1481" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1481" t="str">
+        <f t="shared" si="1"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1481">
+        <v>14</v>
+      </c>
+      <c r="I1481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1482" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1482">
+        <v>11</v>
+      </c>
       <c r="E1482" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1482" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1483" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1482" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1482" t="str">
+        <f t="shared" si="1"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1482">
+        <v>15</v>
+      </c>
+      <c r="I1482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1483" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1483">
+        <v>11</v>
+      </c>
       <c r="E1483" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1483" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1484" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1483" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1483" t="str">
+        <f t="shared" si="1"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1483">
+        <v>16</v>
+      </c>
+      <c r="I1483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1484" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1484">
+        <v>11</v>
+      </c>
       <c r="E1484" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1484" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1485" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1484" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1484" t="str">
+        <f t="shared" si="1"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1484">
+        <v>17</v>
+      </c>
+      <c r="I1484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1485" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1485">
+        <v>11</v>
+      </c>
       <c r="E1485" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1485" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1486" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1485" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1485" t="str">
+        <f t="shared" si="1"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1485">
+        <v>18</v>
+      </c>
+      <c r="I1485">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1486" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1486">
+        <v>11</v>
+      </c>
       <c r="E1486" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1486" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1487" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1486" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1486" t="str">
+        <f t="shared" si="1"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1486">
+        <v>19</v>
+      </c>
+      <c r="I1486">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1487" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1487">
+        <v>11</v>
+      </c>
       <c r="E1487" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1487" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1488" spans="5:9" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+      <c r="F1487" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1487" t="str">
+        <f t="shared" si="1"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1487">
+        <v>20</v>
+      </c>
+      <c r="I1487">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:9" x14ac:dyDescent="0.45">
       <c r="E1488" t="s">
         <v>37</v>
       </c>
@@ -87321,7 +87757,7 @@
         <v>31</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B25" si="1">B2+1</f>
+        <f t="shared" ref="B3:B24" si="1">B2+1</f>
         <v>2</v>
       </c>
       <c r="C3" s="9">
@@ -87533,7 +87969,7 @@
         <v>119</v>
       </c>
       <c r="E10" t="str">
-        <f t="shared" ref="E10:E25" si="3">VLOOKUP(D10,$K$1:$L$33,2,FALSE)</f>
+        <f t="shared" ref="E10:E24" si="3">VLOOKUP(D10,$K$1:$L$33,2,FALSE)</f>
         <v>Circuit Gilles Villeneuve</v>
       </c>
       <c r="F10" t="s">
@@ -87593,7 +88029,7 @@
         <v>Hungaroring</v>
       </c>
       <c r="F12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K12" t="s">
         <v>128</v>
@@ -87611,7 +88047,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="9">
-        <f t="shared" ref="C13:C25" si="4">C12+7</f>
+        <f t="shared" ref="C13:C24" si="4">C12+7</f>
         <v>46110</v>
       </c>
       <c r="D13" t="s">

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17CDC799-1E74-49D7-BA40-4959A6CED48C}"/>
+  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCAFB243-1AD3-4970-83B7-71B28E32C6B1}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16316" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16318" uniqueCount="199">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -634,11 +634,20 @@
   <si>
     <t>Upcoming</t>
   </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Fastest Lap</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm:ss.000"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -700,7 +709,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -711,6 +720,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19167,11 +19178,12 @@
     <col min="7" max="7" width="31.9296875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="3.53125" customWidth="1"/>
+    <col min="10" max="10" width="7.86328125" customWidth="1"/>
+    <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="14.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>22</v>
       </c>
@@ -19199,8 +19211,14 @@
       <c r="I1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1" t="s">
+        <v>197</v>
+      </c>
+      <c r="K1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>39</v>
       </c>
@@ -19229,7 +19247,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>39</v>
       </c>
@@ -19258,7 +19276,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -19287,7 +19305,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -19316,7 +19334,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>39</v>
       </c>
@@ -19345,7 +19363,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -19374,7 +19392,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -19403,7 +19421,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>39</v>
       </c>
@@ -19432,7 +19450,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -19461,7 +19479,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -19490,7 +19508,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -19519,7 +19537,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -19548,7 +19566,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -19577,7 +19595,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>39</v>
       </c>
@@ -19606,7 +19624,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -63004,7 +63022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1505" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1505" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1505" t="s">
         <v>30</v>
       </c>
@@ -63034,7 +63052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1506" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1506" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1506" t="s">
         <v>30</v>
       </c>
@@ -63064,7 +63082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1507" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1507" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1507" t="s">
         <v>30</v>
       </c>
@@ -63094,7 +63112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1508" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1508" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1508" t="s">
         <v>30</v>
       </c>
@@ -63123,8 +63141,14 @@
       <c r="I1508">
         <v>25</v>
       </c>
-    </row>
-    <row r="1509" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1508" s="10">
+        <v>5.3289583333333335E-2</v>
+      </c>
+      <c r="K1508" s="11">
+        <v>9.6721064814814825E-4</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1509" t="s">
         <v>30</v>
       </c>
@@ -63153,8 +63177,14 @@
       <c r="I1509">
         <v>18</v>
       </c>
-    </row>
-    <row r="1510" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1509" s="10">
+        <v>5.3919675925925926E-2</v>
+      </c>
+      <c r="K1509" s="11">
+        <v>9.6833333333333331E-4</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1510" t="s">
         <v>30</v>
       </c>
@@ -63183,8 +63213,14 @@
       <c r="I1510">
         <v>15</v>
       </c>
-    </row>
-    <row r="1511" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1510" s="10">
+        <v>5.3942164351851854E-2</v>
+      </c>
+      <c r="K1510" s="11">
+        <v>9.8263888888888901E-4</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1511" t="s">
         <v>30</v>
       </c>
@@ -63213,8 +63249,14 @@
       <c r="I1511">
         <v>12</v>
       </c>
-    </row>
-    <row r="1512" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1511" s="10">
+        <v>5.3988946759259263E-2</v>
+      </c>
+      <c r="K1511" s="11">
+        <v>9.9053240740740742E-4</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1512" t="s">
         <v>30</v>
       </c>
@@ -63243,8 +63285,14 @@
       <c r="I1512">
         <v>10</v>
       </c>
-    </row>
-    <row r="1513" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1512" s="10">
+        <v>5.4000844907407405E-2</v>
+      </c>
+      <c r="K1512" s="11">
+        <v>9.8120370370370375E-4</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1513" t="s">
         <v>30</v>
       </c>
@@ -63273,8 +63321,14 @@
       <c r="I1513">
         <v>8</v>
       </c>
-    </row>
-    <row r="1514" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1513" s="10">
+        <v>5.4079259259259264E-2</v>
+      </c>
+      <c r="K1513" s="11">
+        <v>9.8618055555555568E-4</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1514" t="s">
         <v>30</v>
       </c>
@@ -63303,8 +63357,14 @@
       <c r="I1514">
         <v>6</v>
       </c>
-    </row>
-    <row r="1515" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1514" s="10">
+        <v>5.4120150462962958E-2</v>
+      </c>
+      <c r="K1514" s="11">
+        <v>9.907407407407406E-4</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1515" t="s">
         <v>30</v>
       </c>
@@ -63333,8 +63393,14 @@
       <c r="I1515">
         <v>4</v>
       </c>
-    </row>
-    <row r="1516" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1515" s="10">
+        <v>5.4167152777777783E-2</v>
+      </c>
+      <c r="K1515" s="11">
+        <v>9.8600694444444452E-4</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1516" t="s">
         <v>30</v>
       </c>
@@ -63363,8 +63429,14 @@
       <c r="I1516">
         <v>2</v>
       </c>
-    </row>
-    <row r="1517" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1516" s="10">
+        <v>5.4271226851851845E-2</v>
+      </c>
+      <c r="K1516" s="11">
+        <v>9.9104166666666676E-4</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1517" t="s">
         <v>30</v>
       </c>
@@ -63393,8 +63465,14 @@
       <c r="I1517">
         <v>1</v>
       </c>
-    </row>
-    <row r="1518" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1517" s="10">
+        <v>5.343755787037037E-2</v>
+      </c>
+      <c r="K1517" s="11">
+        <v>1.0015046296296297E-3</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1518" t="s">
         <v>30</v>
       </c>
@@ -63423,8 +63501,14 @@
       <c r="I1518">
         <v>0</v>
       </c>
-    </row>
-    <row r="1519" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1518" s="10">
+        <v>5.3307534722222216E-2</v>
+      </c>
+      <c r="K1518" s="11">
+        <v>1.0099074074074075E-3</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1519" t="s">
         <v>30</v>
       </c>
@@ -63453,8 +63537,14 @@
       <c r="I1519">
         <v>0</v>
       </c>
-    </row>
-    <row r="1520" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1519" s="10">
+        <v>5.3336643518518516E-2</v>
+      </c>
+      <c r="K1519" s="11">
+        <v>1.0014351851851853E-3</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1520" t="s">
         <v>30</v>
       </c>
@@ -63483,8 +63573,14 @@
       <c r="I1520">
         <v>0</v>
       </c>
-    </row>
-    <row r="1521" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1520" s="10">
+        <v>5.3458877314814815E-2</v>
+      </c>
+      <c r="K1520" s="11">
+        <v>9.9278935185185191E-4</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1521" t="s">
         <v>30</v>
       </c>
@@ -63513,8 +63609,14 @@
       <c r="I1521">
         <v>0</v>
       </c>
-    </row>
-    <row r="1522" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1521" s="10">
+        <v>5.3532187499999995E-2</v>
+      </c>
+      <c r="K1521" s="11">
+        <v>9.977083333333333E-4</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1522" t="s">
         <v>30</v>
       </c>
@@ -63543,8 +63645,14 @@
       <c r="I1522">
         <v>0</v>
       </c>
-    </row>
-    <row r="1523" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1522" s="10">
+        <v>5.3568912037037043E-2</v>
+      </c>
+      <c r="K1522" s="11">
+        <v>9.9244212962962958E-4</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1523" t="s">
         <v>30</v>
       </c>
@@ -63573,8 +63681,14 @@
       <c r="I1523">
         <v>0</v>
       </c>
-    </row>
-    <row r="1524" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1523" s="10">
+        <v>5.3636840277777778E-2</v>
+      </c>
+      <c r="K1523" s="11">
+        <v>9.9120370370370378E-4</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1524" t="s">
         <v>30</v>
       </c>
@@ -63603,8 +63717,14 @@
       <c r="I1524">
         <v>0</v>
       </c>
-    </row>
-    <row r="1525" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1524" s="10">
+        <v>5.3662118055555555E-2</v>
+      </c>
+      <c r="K1524" s="11">
+        <v>1.0007754629629629E-3</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1525" t="s">
         <v>30</v>
       </c>
@@ -63633,8 +63753,14 @@
       <c r="I1525">
         <v>0</v>
       </c>
-    </row>
-    <row r="1526" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1525" s="10">
+        <v>5.3717048611111116E-2</v>
+      </c>
+      <c r="K1525" s="11">
+        <v>9.9468750000000013E-4</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1526" t="s">
         <v>30</v>
       </c>
@@ -63663,8 +63789,14 @@
       <c r="I1526">
         <v>0</v>
       </c>
-    </row>
-    <row r="1527" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1526" s="10">
+        <v>5.4284421296296299E-2</v>
+      </c>
+      <c r="K1526" s="11">
+        <v>9.8986111111111106E-4</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1527" t="s">
         <v>30</v>
       </c>
@@ -63693,8 +63825,14 @@
       <c r="I1527">
         <v>0</v>
       </c>
-    </row>
-    <row r="1528" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1527" s="10">
+        <v>2.6500266203703705E-2</v>
+      </c>
+      <c r="K1527" s="11">
+        <v>1.0181944444444446E-3</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1528" t="s">
         <v>37</v>
       </c>
@@ -63702,7 +63840,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1529" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1529" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1529" t="s">
         <v>37</v>
       </c>
@@ -63710,7 +63848,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1530" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1530" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1530" t="s">
         <v>37</v>
       </c>
@@ -63718,7 +63856,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1531" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1531" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1531" t="s">
         <v>37</v>
       </c>
@@ -63726,7 +63864,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1532" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1532" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1532" t="s">
         <v>37</v>
       </c>
@@ -63734,7 +63872,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1533" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1533" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1533" t="s">
         <v>37</v>
       </c>
@@ -63742,7 +63880,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1534" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1534" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1534" t="s">
         <v>37</v>
       </c>
@@ -63750,7 +63888,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1535" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1535" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1535" t="s">
         <v>37</v>
       </c>
@@ -63758,7 +63896,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1536" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1536" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1536" t="s">
         <v>37</v>
       </c>
@@ -90113,7 +90251,7 @@
         <v>15</v>
       </c>
       <c r="C16" s="9">
-        <f t="shared" ref="C14:C24" si="4">C15+7</f>
+        <f t="shared" ref="C16:C24" si="4">C15+7</f>
         <v>46166</v>
       </c>
       <c r="D16" t="s">

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCAFB243-1AD3-4970-83B7-71B28E32C6B1}"/>
+  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0994D33-CC6A-4B36-8ED1-2FE37F2C2198}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16318" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16378" uniqueCount="199">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -646,7 +646,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="mm:ss.000"/>
+    <numFmt numFmtId="164" formatCode="mm:ss.000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -721,7 +721,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -63168,7 +63168,7 @@
         <v>33</v>
       </c>
       <c r="G1509" t="str">
-        <f t="shared" ref="G1509:G1527" si="2">VLOOKUP(F1509,$M$1408:$N$1427,2,FALSE)</f>
+        <f t="shared" ref="G1509:G1547" si="2">VLOOKUP(F1509,$M$1408:$N$1427,2,FALSE)</f>
         <v>Red Bull</v>
       </c>
       <c r="H1509">
@@ -63833,166 +63833,726 @@
       </c>
     </row>
     <row r="1528" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1528" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1528">
+        <v>14</v>
+      </c>
       <c r="E1528" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1528" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="F1528" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1528" t="str">
+        <f t="shared" si="2"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1528">
+        <v>1</v>
+      </c>
+      <c r="I1528">
+        <v>25</v>
+      </c>
+      <c r="J1528" s="10">
+        <v>6.9966458333333328E-2</v>
+      </c>
+      <c r="K1528" s="11">
+        <v>1.2433796296296297E-3</v>
       </c>
     </row>
     <row r="1529" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1529" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1529">
+        <v>14</v>
+      </c>
       <c r="E1529" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1529" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="F1529" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1529" t="str">
+        <f t="shared" si="2"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1529">
+        <v>2</v>
+      </c>
+      <c r="I1529">
+        <v>18</v>
+      </c>
+      <c r="J1529" s="10">
+        <v>6.9966840277777775E-2</v>
+      </c>
+      <c r="K1529" s="11">
+        <v>1.239050925925926E-3</v>
       </c>
     </row>
     <row r="1530" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1530" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1530">
+        <v>14</v>
+      </c>
       <c r="E1530" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1530" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="F1530" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1530" t="str">
+        <f t="shared" si="2"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1530">
+        <v>3</v>
+      </c>
+      <c r="I1530">
+        <v>15</v>
+      </c>
+      <c r="J1530" s="10">
+        <v>6.9990810185185187E-2</v>
+      </c>
+      <c r="K1530" s="11">
+        <v>1.2389004629629629E-3</v>
       </c>
     </row>
     <row r="1531" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1531" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1531">
+        <v>14</v>
+      </c>
       <c r="E1531" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1531" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="F1531" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1531" t="str">
+        <f t="shared" si="2"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1531">
+        <v>4</v>
+      </c>
+      <c r="I1531">
+        <v>12</v>
+      </c>
+      <c r="J1531" s="10">
+        <v>7.00105324074074E-2</v>
+      </c>
+      <c r="K1531" s="11">
+        <v>1.254513888888889E-3</v>
       </c>
     </row>
     <row r="1532" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1532" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1532">
+        <v>14</v>
+      </c>
       <c r="E1532" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1532" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="F1532" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1532" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1532">
+        <v>5</v>
+      </c>
+      <c r="I1532">
+        <v>10</v>
+      </c>
+      <c r="J1532" s="10">
+        <v>7.001512731481481E-2</v>
+      </c>
+      <c r="K1532" s="11">
+        <v>1.2533796296296297E-3</v>
       </c>
     </row>
     <row r="1533" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1533" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1533">
+        <v>14</v>
+      </c>
       <c r="E1533" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1533" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="F1533" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1533" t="str">
+        <f t="shared" si="2"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1533">
+        <v>6</v>
+      </c>
+      <c r="I1533">
+        <v>8</v>
+      </c>
+      <c r="J1533" s="10">
+        <v>7.0028275462962961E-2</v>
+      </c>
+      <c r="K1533" s="11">
+        <v>1.2529166666666667E-3</v>
       </c>
     </row>
     <row r="1534" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1534" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1534">
+        <v>14</v>
+      </c>
       <c r="E1534" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1534" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="F1534" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1534" t="str">
+        <f t="shared" si="2"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1534">
+        <v>7</v>
+      </c>
+      <c r="I1534">
+        <v>6</v>
+      </c>
+      <c r="J1534" s="10">
+        <v>7.0035625000000004E-2</v>
+      </c>
+      <c r="K1534" s="11">
+        <v>1.2514699074074075E-3</v>
       </c>
     </row>
     <row r="1535" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1535" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1535">
+        <v>14</v>
+      </c>
       <c r="E1535" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1535" t="s">
-        <v>37</v>
+        <v>122</v>
+      </c>
+      <c r="F1535" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1535" t="str">
+        <f t="shared" si="2"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1535">
+        <v>8</v>
+      </c>
+      <c r="I1535">
+        <v>4</v>
+      </c>
+      <c r="J1535" s="10">
+        <v>7.0037164351851852E-2</v>
+      </c>
+      <c r="K1535" s="11">
+        <v>1.2495717592592591E-3</v>
       </c>
     </row>
     <row r="1536" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1536" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1536">
+        <v>14</v>
+      </c>
       <c r="E1536" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1536" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1537" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1536" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1536" t="str">
+        <f t="shared" si="2"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1536">
+        <v>9</v>
+      </c>
+      <c r="I1536">
+        <v>2</v>
+      </c>
+      <c r="J1536" s="10">
+        <v>7.0065775462962956E-2</v>
+      </c>
+      <c r="K1536" s="11">
+        <v>1.2634490740740742E-3</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1537" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1537">
+        <v>14</v>
+      </c>
       <c r="E1537" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1537" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1538" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1537" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1537" t="str">
+        <f t="shared" si="2"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1537">
+        <v>10</v>
+      </c>
+      <c r="I1537">
+        <v>1</v>
+      </c>
+      <c r="J1537" s="10">
+        <v>7.0072453703703699E-2</v>
+      </c>
+      <c r="K1537" s="11">
+        <v>1.2550578703703704E-3</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1538" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1538">
+        <v>14</v>
+      </c>
       <c r="E1538" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1538" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1539" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1538" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1538" t="str">
+        <f t="shared" si="2"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1538">
+        <v>11</v>
+      </c>
+      <c r="I1538">
+        <v>0</v>
+      </c>
+      <c r="J1538" s="10">
+        <v>7.0080821759259268E-2</v>
+      </c>
+      <c r="K1538" s="11">
+        <v>1.2644675925925926E-3</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1539" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1539">
+        <v>14</v>
+      </c>
       <c r="E1539" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1539" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1540" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1539" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1539" t="str">
+        <f t="shared" si="2"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1539">
+        <v>12</v>
+      </c>
+      <c r="I1539">
+        <v>0</v>
+      </c>
+      <c r="J1539" s="10">
+        <v>7.0087777777777777E-2</v>
+      </c>
+      <c r="K1539" s="11">
+        <v>1.259224537037037E-3</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1540" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1540">
+        <v>14</v>
+      </c>
       <c r="E1540" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1540" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1541" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1540" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1540" t="str">
+        <f t="shared" si="2"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1540">
+        <v>13</v>
+      </c>
+      <c r="I1540">
+        <v>0</v>
+      </c>
+      <c r="J1540" s="10">
+        <v>7.0100439814814813E-2</v>
+      </c>
+      <c r="K1540" s="11">
+        <v>1.260173611111111E-3</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1541" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1541">
+        <v>14</v>
+      </c>
       <c r="E1541" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1541" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1542" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1541" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1541" t="str">
+        <f t="shared" si="2"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1541">
+        <v>14</v>
+      </c>
+      <c r="I1541">
+        <v>0</v>
+      </c>
+      <c r="J1541" s="10">
+        <v>7.0120324074074064E-2</v>
+      </c>
+      <c r="K1541" s="11">
+        <v>1.2382754629629629E-3</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1542" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1542">
+        <v>14</v>
+      </c>
       <c r="E1542" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1542" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1543" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1542" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1542" t="str">
+        <f t="shared" si="2"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1542">
+        <v>15</v>
+      </c>
+      <c r="I1542">
+        <v>0</v>
+      </c>
+      <c r="J1542" s="10">
+        <v>7.0215254629629631E-2</v>
+      </c>
+      <c r="K1542" s="11">
+        <v>1.2699421296296295E-3</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1543" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1543">
+        <v>14</v>
+      </c>
       <c r="E1543" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1543" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1544" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1543" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1543" t="str">
+        <f t="shared" si="2"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1543">
+        <v>16</v>
+      </c>
+      <c r="I1543">
+        <v>0</v>
+      </c>
+      <c r="J1543" s="10">
+        <v>7.0488495370370371E-2</v>
+      </c>
+      <c r="K1543" s="11">
+        <v>1.2663310185185186E-3</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1544" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1544">
+        <v>14</v>
+      </c>
       <c r="E1544" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1544" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1545" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1544" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1544" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1544">
+        <v>17</v>
+      </c>
+      <c r="I1544">
+        <v>0</v>
+      </c>
+      <c r="J1544" s="10">
+        <v>1.1605243055555556E-2</v>
+      </c>
+      <c r="K1544" s="11">
+        <v>1.2665162037037035E-3</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1545" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1545">
+        <v>14</v>
+      </c>
       <c r="E1545" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1545" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1546" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1545" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1545" t="str">
+        <f t="shared" si="2"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1545">
+        <v>18</v>
+      </c>
+      <c r="I1545">
+        <v>0</v>
+      </c>
+      <c r="J1545" s="10">
+        <v>5.2325891203703706E-2</v>
+      </c>
+      <c r="K1545" s="11">
+        <v>1.2679976851851852E-3</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1546" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1546">
+        <v>14</v>
+      </c>
       <c r="E1546" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1546" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1547" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1546" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1546" t="str">
+        <f t="shared" si="2"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1546">
+        <v>19</v>
+      </c>
+      <c r="I1546">
+        <v>0</v>
+      </c>
+      <c r="J1546" s="10">
+        <v>5.4756238425925932E-2</v>
+      </c>
+      <c r="K1546" s="11">
+        <v>1.2503472222222221E-3</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1547" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1547">
+        <v>14</v>
+      </c>
       <c r="E1547" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1547" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1548" spans="5:9" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+      <c r="F1547" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1547" t="str">
+        <f t="shared" si="2"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1547">
+        <v>20</v>
+      </c>
+      <c r="I1547">
+        <v>0</v>
+      </c>
+      <c r="J1547" s="10">
+        <v>6.0437534722222221E-2</v>
+      </c>
+      <c r="K1547" s="11">
+        <v>1.2340162037037038E-3</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1548" t="s">
         <v>37</v>
       </c>
@@ -64000,7 +64560,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1549" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1549" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1549" t="s">
         <v>37</v>
       </c>
@@ -64008,7 +64568,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1550" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1550" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1550" t="s">
         <v>37</v>
       </c>
@@ -64016,7 +64576,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1551" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1551" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1551" t="s">
         <v>37</v>
       </c>
@@ -64024,7 +64584,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1552" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1552" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1552" t="s">
         <v>37</v>
       </c>
@@ -90233,7 +90793,7 @@
         <v>Baku City Circuit</v>
       </c>
       <c r="F15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K15" t="s">
         <v>125</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="256" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0994D33-CC6A-4B36-8ED1-2FE37F2C2198}"/>
+  <xr:revisionPtr revIDLastSave="259" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8544AE1-A967-41BC-95C3-FDC0F221B19C}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16378" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16383" uniqueCount="200">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -639,6 +639,9 @@
   </si>
   <si>
     <t>Fastest Lap</t>
+  </si>
+  <si>
+    <t>DNF</t>
   </si>
 </sst>
 </file>
@@ -63825,8 +63828,8 @@
       <c r="I1527">
         <v>0</v>
       </c>
-      <c r="J1527" s="10">
-        <v>2.6500266203703705E-2</v>
+      <c r="J1527" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="K1527" s="11">
         <v>1.0181944444444446E-3</v>
@@ -64437,8 +64440,8 @@
       <c r="I1544">
         <v>0</v>
       </c>
-      <c r="J1544" s="10">
-        <v>1.1605243055555556E-2</v>
+      <c r="J1544" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="K1544" s="11">
         <v>1.2665162037037035E-3</v>
@@ -64473,8 +64476,8 @@
       <c r="I1545">
         <v>0</v>
       </c>
-      <c r="J1545" s="10">
-        <v>5.2325891203703706E-2</v>
+      <c r="J1545" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="K1545" s="11">
         <v>1.2679976851851852E-3</v>
@@ -64509,8 +64512,8 @@
       <c r="I1546">
         <v>0</v>
       </c>
-      <c r="J1546" s="10">
-        <v>5.4756238425925932E-2</v>
+      <c r="J1546" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="K1546" s="11">
         <v>1.2503472222222221E-3</v>
@@ -64545,8 +64548,8 @@
       <c r="I1547">
         <v>0</v>
       </c>
-      <c r="J1547" s="10">
-        <v>6.0437534722222221E-2</v>
+      <c r="J1547" s="10" t="s">
+        <v>199</v>
       </c>
       <c r="K1547" s="11">
         <v>1.2340162037037038E-3</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="259" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8544AE1-A967-41BC-95C3-FDC0F221B19C}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77749695-B721-435D-890B-62C0B301389B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16383" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16387" uniqueCount="200">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -61105,7 +61105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1441" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1441" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1441" t="s">
         <v>30</v>
       </c>
@@ -61135,7 +61135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1442" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1442" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1442" t="s">
         <v>30</v>
       </c>
@@ -61165,7 +61165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1443" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1443" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1443" t="s">
         <v>30</v>
       </c>
@@ -61195,7 +61195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1444" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1444" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1444" t="s">
         <v>30</v>
       </c>
@@ -61225,7 +61225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1445" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1445" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1445" t="s">
         <v>30</v>
       </c>
@@ -61255,7 +61255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1446" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1446" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1446" t="s">
         <v>30</v>
       </c>
@@ -61285,7 +61285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1447" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1447" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1447" t="s">
         <v>30</v>
       </c>
@@ -61315,7 +61315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1448" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="1448" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1448" t="s">
         <v>30</v>
       </c>
@@ -61344,8 +61344,14 @@
       <c r="I1448">
         <v>25</v>
       </c>
-    </row>
-    <row r="1449" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1448" s="10">
+        <v>6.1256539351851845E-2</v>
+      </c>
+      <c r="K1448" s="11">
+        <v>8.1130787037037033E-4</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1449" t="s">
         <v>30</v>
       </c>
@@ -61374,8 +61380,14 @@
       <c r="I1449">
         <v>18</v>
       </c>
-    </row>
-    <row r="1450" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1449" s="10">
+        <v>6.1414340277777771E-2</v>
+      </c>
+      <c r="K1449" s="11">
+        <v>8.1802083333333325E-4</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1450" t="s">
         <v>30</v>
       </c>
@@ -61404,8 +61416,14 @@
       <c r="I1450">
         <v>15</v>
       </c>
-    </row>
-    <row r="1451" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1450" s="10">
+        <v>6.1511828703703704E-2</v>
+      </c>
+      <c r="K1450" s="11">
+        <v>8.2483796296296298E-4</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1451" t="s">
         <v>30</v>
       </c>
@@ -61434,8 +61452,14 @@
       <c r="I1451">
         <v>12</v>
       </c>
-    </row>
-    <row r="1452" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1451" s="10">
+        <v>6.1545543981481481E-2</v>
+      </c>
+      <c r="K1451" s="11">
+        <v>8.2541666666666668E-4</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1452" t="s">
         <v>30</v>
       </c>
@@ -61464,8 +61488,14 @@
       <c r="I1452">
         <v>10</v>
       </c>
-    </row>
-    <row r="1453" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1452" s="10">
+        <v>6.1652233796296294E-2</v>
+      </c>
+      <c r="K1452" s="11">
+        <v>8.3271990740740745E-4</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1453" t="s">
         <v>30</v>
       </c>
@@ -61494,8 +61524,14 @@
       <c r="I1453">
         <v>8</v>
       </c>
-    </row>
-    <row r="1454" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1453" s="10">
+        <v>6.1668587962962963E-2</v>
+      </c>
+      <c r="K1453" s="11">
+        <v>8.2479166666666671E-4</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1454" t="s">
         <v>30</v>
       </c>
@@ -61524,8 +61560,14 @@
       <c r="I1454">
         <v>6</v>
       </c>
-    </row>
-    <row r="1455" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1454" s="10">
+        <v>6.1753495370370372E-2</v>
+      </c>
+      <c r="K1454" s="11">
+        <v>8.3015046296296287E-4</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1455" t="s">
         <v>30</v>
       </c>
@@ -61554,8 +61596,14 @@
       <c r="I1455">
         <v>4</v>
       </c>
-    </row>
-    <row r="1456" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1455" s="10">
+        <v>6.1769050925925918E-2</v>
+      </c>
+      <c r="K1455" s="11">
+        <v>8.1621527777777779E-4</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1456" t="s">
         <v>30</v>
       </c>
@@ -61584,8 +61632,14 @@
       <c r="I1456">
         <v>2</v>
       </c>
-    </row>
-    <row r="1457" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1456" s="10">
+        <v>6.1864432870370377E-2</v>
+      </c>
+      <c r="K1456" s="11">
+        <v>7.8887731481481484E-4</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1457" t="s">
         <v>30</v>
       </c>
@@ -61614,8 +61668,14 @@
       <c r="I1457">
         <v>1</v>
       </c>
-    </row>
-    <row r="1458" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1457" s="10">
+        <v>6.1890752314814813E-2</v>
+      </c>
+      <c r="K1457" s="11">
+        <v>8.1930555555555554E-4</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1458" t="s">
         <v>30</v>
       </c>
@@ -61644,8 +61704,14 @@
       <c r="I1458">
         <v>0</v>
       </c>
-    </row>
-    <row r="1459" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1458" s="10">
+        <v>6.126376157407408E-2</v>
+      </c>
+      <c r="K1458" s="11">
+        <v>8.3333333333333339E-4</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1459" t="s">
         <v>30</v>
       </c>
@@ -61674,8 +61740,14 @@
       <c r="I1459">
         <v>0</v>
       </c>
-    </row>
-    <row r="1460" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1459" s="10">
+        <v>6.1293483796296289E-2</v>
+      </c>
+      <c r="K1459" s="11">
+        <v>8.3677083333333325E-4</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1460" t="s">
         <v>30</v>
       </c>
@@ -61704,8 +61776,14 @@
       <c r="I1460">
         <v>0</v>
       </c>
-    </row>
-    <row r="1461" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1460" s="10">
+        <v>6.131076388888889E-2</v>
+      </c>
+      <c r="K1460" s="11">
+        <v>8.3292824074074074E-4</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1461" t="s">
         <v>30</v>
       </c>
@@ -61734,8 +61812,14 @@
       <c r="I1461">
         <v>0</v>
       </c>
-    </row>
-    <row r="1462" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1461" s="10">
+        <v>6.1525983796296299E-2</v>
+      </c>
+      <c r="K1461" s="11">
+        <v>8.4449074074074071E-4</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1462" t="s">
         <v>30</v>
       </c>
@@ -61764,8 +61848,14 @@
       <c r="I1462">
         <v>0</v>
       </c>
-    </row>
-    <row r="1463" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1462" s="10">
+        <v>6.1528287037037034E-2</v>
+      </c>
+      <c r="K1462" s="11">
+        <v>8.4252314814814812E-4</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1463" t="s">
         <v>30</v>
       </c>
@@ -61794,8 +61884,14 @@
       <c r="I1463">
         <v>0</v>
       </c>
-    </row>
-    <row r="1464" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1463" s="10">
+        <v>6.162234953703704E-2</v>
+      </c>
+      <c r="K1463" s="11">
+        <v>8.3163194444444441E-4</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1464" t="s">
         <v>30</v>
       </c>
@@ -61824,8 +61920,14 @@
       <c r="I1464">
         <v>0</v>
       </c>
-    </row>
-    <row r="1465" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1464" s="10">
+        <v>6.1953761574074076E-2</v>
+      </c>
+      <c r="K1464" s="11">
+        <v>8.2912037037037036E-4</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1465" t="s">
         <v>30</v>
       </c>
@@ -61854,8 +61956,14 @@
       <c r="I1465">
         <v>0</v>
       </c>
-    </row>
-    <row r="1466" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1465" s="10">
+        <v>6.1970127314814813E-2</v>
+      </c>
+      <c r="K1465" s="11">
+        <v>8.2393518518518525E-4</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1466" t="s">
         <v>30</v>
       </c>
@@ -61884,8 +61992,14 @@
       <c r="I1466">
         <v>0</v>
       </c>
-    </row>
-    <row r="1467" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1466" s="10">
+        <v>6.204391203703704E-2</v>
+      </c>
+      <c r="K1466" s="11">
+        <v>8.3251157407407406E-4</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1467" t="s">
         <v>30</v>
       </c>
@@ -61914,8 +62028,14 @@
       <c r="I1467">
         <v>0</v>
       </c>
-    </row>
-    <row r="1468" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1467" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1467" s="11">
+        <v>8.2780092592592595E-4</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1468" t="s">
         <v>30</v>
       </c>
@@ -61944,8 +62064,14 @@
       <c r="I1468">
         <v>25</v>
       </c>
-    </row>
-    <row r="1469" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1468" s="10">
+        <v>6.8836458333333336E-2</v>
+      </c>
+      <c r="K1468" s="11">
+        <v>9.5950231481481472E-4</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1469" t="s">
         <v>30</v>
       </c>
@@ -61974,8 +62100,14 @@
       <c r="I1469">
         <v>18</v>
       </c>
-    </row>
-    <row r="1470" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1469" s="10">
+        <v>6.9230578703703707E-2</v>
+      </c>
+      <c r="K1469" s="11">
+        <v>9.661226851851852E-4</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1470" t="s">
         <v>30</v>
       </c>
@@ -62004,8 +62136,14 @@
       <c r="I1470">
         <v>15</v>
       </c>
-    </row>
-    <row r="1471" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1470" s="10">
+        <v>6.9382442129629629E-2</v>
+      </c>
+      <c r="K1470" s="11">
+        <v>9.6331018518518521E-4</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1471" t="s">
         <v>30</v>
       </c>
@@ -62034,8 +62172,14 @@
       <c r="I1471">
         <v>12</v>
       </c>
-    </row>
-    <row r="1472" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1471" s="10">
+        <v>6.9425358796296299E-2</v>
+      </c>
+      <c r="K1471" s="11">
+        <v>9.6582175925925926E-4</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1472" t="s">
         <v>30</v>
       </c>
@@ -62064,8 +62208,14 @@
       <c r="I1472">
         <v>10</v>
       </c>
-    </row>
-    <row r="1473" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1472" s="10">
+        <v>6.9643043981481481E-2</v>
+      </c>
+      <c r="K1472" s="11">
+        <v>9.6216435185185185E-4</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1473" t="s">
         <v>30</v>
       </c>
@@ -62094,8 +62244,14 @@
       <c r="I1473">
         <v>8</v>
       </c>
-    </row>
-    <row r="1474" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1473" s="10">
+        <v>6.9789467592592594E-2</v>
+      </c>
+      <c r="K1473" s="11">
+        <v>9.6343749999999999E-4</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1474" t="s">
         <v>30</v>
       </c>
@@ -62124,8 +62280,14 @@
       <c r="I1474">
         <v>6</v>
       </c>
-    </row>
-    <row r="1475" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1474" s="10">
+        <v>6.9793217592592591E-2</v>
+      </c>
+      <c r="K1474" s="11">
+        <v>9.5971064814814812E-4</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1475" t="s">
         <v>30</v>
       </c>
@@ -62154,8 +62316,14 @@
       <c r="I1475">
         <v>4</v>
       </c>
-    </row>
-    <row r="1476" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1475" s="10">
+        <v>6.9800706018518524E-2</v>
+      </c>
+      <c r="K1475" s="11">
+        <v>9.6349537037037031E-4</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1476" t="s">
         <v>30</v>
       </c>
@@ -62184,8 +62352,14 @@
       <c r="I1476">
         <v>2</v>
       </c>
-    </row>
-    <row r="1477" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1476" s="10">
+        <v>6.9804328703703705E-2</v>
+      </c>
+      <c r="K1476" s="11">
+        <v>9.6129629629629625E-4</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1477" t="s">
         <v>30</v>
       </c>
@@ -62214,8 +62388,14 @@
       <c r="I1477">
         <v>1</v>
       </c>
-    </row>
-    <row r="1478" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1477" s="10">
+        <v>6.9808842592592596E-2</v>
+      </c>
+      <c r="K1477" s="11">
+        <v>9.6226851851851855E-4</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1478" t="s">
         <v>30</v>
       </c>
@@ -62244,8 +62424,14 @@
       <c r="I1478">
         <v>0</v>
       </c>
-    </row>
-    <row r="1479" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1478" s="10">
+        <v>6.8882870370370372E-2</v>
+      </c>
+      <c r="K1478" s="11">
+        <v>9.5677083333333324E-4</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1479" t="s">
         <v>30</v>
       </c>
@@ -62274,8 +62460,14 @@
       <c r="I1479">
         <v>0</v>
       </c>
-    </row>
-    <row r="1480" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1479" s="10">
+        <v>6.8896030092592597E-2</v>
+      </c>
+      <c r="K1479" s="11">
+        <v>9.7400462962962957E-4</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1480" t="s">
         <v>30</v>
       </c>
@@ -62304,8 +62496,14 @@
       <c r="I1480">
         <v>0</v>
       </c>
-    </row>
-    <row r="1481" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1480" s="10">
+        <v>6.8947696759259255E-2</v>
+      </c>
+      <c r="K1480" s="11">
+        <v>9.8912037037037046E-4</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1481" t="s">
         <v>30</v>
       </c>
@@ -62334,8 +62532,14 @@
       <c r="I1481">
         <v>0</v>
       </c>
-    </row>
-    <row r="1482" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1481" s="10">
+        <v>6.915792824074074E-2</v>
+      </c>
+      <c r="K1481" s="11">
+        <v>9.4571759259259273E-4</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1482" t="s">
         <v>30</v>
       </c>
@@ -62364,8 +62568,14 @@
       <c r="I1482">
         <v>0</v>
       </c>
-    </row>
-    <row r="1483" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1482" s="10">
+        <v>6.9266712962962967E-2</v>
+      </c>
+      <c r="K1482" s="11">
+        <v>9.7537037037037026E-4</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1483" t="s">
         <v>30</v>
       </c>
@@ -62394,8 +62604,14 @@
       <c r="I1483">
         <v>0</v>
       </c>
-    </row>
-    <row r="1484" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1483" s="10">
+        <v>6.9368958333333328E-2</v>
+      </c>
+      <c r="K1483" s="11">
+        <v>9.8061342592592579E-4</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1484" t="s">
         <v>30</v>
       </c>
@@ -62424,8 +62640,14 @@
       <c r="I1484">
         <v>0</v>
       </c>
-    </row>
-    <row r="1485" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1484" s="10">
+        <v>6.941252314814815E-2</v>
+      </c>
+      <c r="K1484" s="11">
+        <v>9.7650462962962968E-4</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1485" t="s">
         <v>30</v>
       </c>
@@ -62454,8 +62676,14 @@
       <c r="I1485">
         <v>0</v>
       </c>
-    </row>
-    <row r="1486" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1485" s="10">
+        <v>6.9812766203703705E-2</v>
+      </c>
+      <c r="K1485" s="11">
+        <v>9.6850694444444447E-4</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1486" t="s">
         <v>30</v>
       </c>
@@ -62484,8 +62712,14 @@
       <c r="I1486">
         <v>0</v>
       </c>
-    </row>
-    <row r="1487" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1486" s="10">
+        <v>6.9817557870370375E-2</v>
+      </c>
+      <c r="K1486" s="11">
+        <v>9.6500000000000004E-4</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1487" t="s">
         <v>30</v>
       </c>
@@ -62514,8 +62748,14 @@
       <c r="I1487">
         <v>0</v>
       </c>
-    </row>
-    <row r="1488" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1487" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1487" s="11">
+        <v>9.885300925925925E-4</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1488" t="s">
         <v>30</v>
       </c>
@@ -62544,8 +62784,14 @@
       <c r="I1488">
         <v>25</v>
       </c>
-    </row>
-    <row r="1489" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1488" s="10">
+        <v>6.5227662037037032E-2</v>
+      </c>
+      <c r="K1488" s="11">
+        <v>8.8071759259259255E-4</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1489" t="s">
         <v>30</v>
       </c>
@@ -62574,8 +62820,14 @@
       <c r="I1489">
         <v>18</v>
       </c>
-    </row>
-    <row r="1490" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1489" s="10">
+        <v>6.5437800925925924E-2</v>
+      </c>
+      <c r="K1489" s="11">
+        <v>8.5714120370370371E-4</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1490" t="s">
         <v>30</v>
       </c>
@@ -62604,8 +62856,14 @@
       <c r="I1490">
         <v>15</v>
       </c>
-    </row>
-    <row r="1491" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1490" s="10">
+        <v>6.5704953703703703E-2</v>
+      </c>
+      <c r="K1490" s="11">
+        <v>8.6759259259259266E-4</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1491" t="s">
         <v>30</v>
       </c>
@@ -62634,8 +62892,14 @@
       <c r="I1491">
         <v>12</v>
       </c>
-    </row>
-    <row r="1492" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1491" s="10">
+        <v>6.5708043981481487E-2</v>
+      </c>
+      <c r="K1491" s="11">
+        <v>8.8065972222222224E-4</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1492" t="s">
         <v>30</v>
       </c>
@@ -62664,8 +62928,14 @@
       <c r="I1492">
         <v>10</v>
       </c>
-    </row>
-    <row r="1493" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1492" s="10">
+        <v>6.5763460648148142E-2</v>
+      </c>
+      <c r="K1492" s="11">
+        <v>8.8724537037037038E-4</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1493" t="s">
         <v>30</v>
       </c>
@@ -62694,8 +62964,14 @@
       <c r="I1493">
         <v>8</v>
       </c>
-    </row>
-    <row r="1494" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1493" s="10">
+        <v>6.576636574074074E-2</v>
+      </c>
+      <c r="K1493" s="11">
+        <v>8.8131944444444445E-4</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1494" t="s">
         <v>30</v>
       </c>
@@ -62724,8 +63000,14 @@
       <c r="I1494">
         <v>6</v>
       </c>
-    </row>
-    <row r="1495" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1494" s="10">
+        <v>6.5798275462962963E-2</v>
+      </c>
+      <c r="K1494" s="11">
+        <v>8.8641203703703701E-4</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1495" t="s">
         <v>30</v>
       </c>
@@ -62754,8 +63036,14 @@
       <c r="I1495">
         <v>4</v>
       </c>
-    </row>
-    <row r="1496" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1495" s="10">
+        <v>6.5812835648148146E-2</v>
+      </c>
+      <c r="K1495" s="11">
+        <v>8.9236111111111102E-4</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1496" t="s">
         <v>30</v>
       </c>
@@ -62784,8 +63072,14 @@
       <c r="I1496">
         <v>2</v>
       </c>
-    </row>
-    <row r="1497" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1496" s="10">
+        <v>6.5857106481481478E-2</v>
+      </c>
+      <c r="K1496" s="11">
+        <v>8.8315972222222235E-4</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1497" t="s">
         <v>30</v>
       </c>
@@ -62814,8 +63108,14 @@
       <c r="I1497">
         <v>1</v>
       </c>
-    </row>
-    <row r="1498" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1497" s="10">
+        <v>6.5960798611111107E-2</v>
+      </c>
+      <c r="K1497" s="11">
+        <v>8.848842592592593E-4</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1498" t="s">
         <v>30</v>
       </c>
@@ -62844,8 +63144,14 @@
       <c r="I1498">
         <v>0</v>
       </c>
-    </row>
-    <row r="1499" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1498" s="10">
+        <v>6.5295347222222216E-2</v>
+      </c>
+      <c r="K1498" s="11">
+        <v>8.8865740740740745E-4</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1499" t="s">
         <v>30</v>
       </c>
@@ -62874,8 +63180,14 @@
       <c r="I1499">
         <v>0</v>
       </c>
-    </row>
-    <row r="1500" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1499" s="10">
+        <v>6.548076388888889E-2</v>
+      </c>
+      <c r="K1499" s="11">
+        <v>9.0158564814814799E-4</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1500" t="s">
         <v>30</v>
       </c>
@@ -62904,8 +63216,14 @@
       <c r="I1500">
         <v>0</v>
       </c>
-    </row>
-    <row r="1501" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1500" s="10">
+        <v>6.5714374999999992E-2</v>
+      </c>
+      <c r="K1500" s="11">
+        <v>8.9342592592592598E-4</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1501" t="s">
         <v>30</v>
       </c>
@@ -62934,8 +63252,14 @@
       <c r="I1501">
         <v>0</v>
       </c>
-    </row>
-    <row r="1502" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1501" s="10">
+        <v>6.5828402777777767E-2</v>
+      </c>
+      <c r="K1501" s="11">
+        <v>8.9402777777777777E-4</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1502" t="s">
         <v>30</v>
       </c>
@@ -62964,8 +63288,14 @@
       <c r="I1502">
         <v>0</v>
       </c>
-    </row>
-    <row r="1503" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1502" s="10">
+        <v>6.5840300925925924E-2</v>
+      </c>
+      <c r="K1502" s="11">
+        <v>8.8261574074074067E-4</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1503" t="s">
         <v>30</v>
       </c>
@@ -62994,8 +63324,14 @@
       <c r="I1503">
         <v>0</v>
       </c>
-    </row>
-    <row r="1504" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="J1503" s="10">
+        <v>6.5917974537037044E-2</v>
+      </c>
+      <c r="K1503" s="11">
+        <v>8.9802083333333335E-4</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1504" t="s">
         <v>30</v>
       </c>
@@ -63024,6 +63360,12 @@
       <c r="I1504">
         <v>0</v>
       </c>
+      <c r="J1504" s="10">
+        <v>6.5987349537037041E-2</v>
+      </c>
+      <c r="K1504" s="11">
+        <v>8.8981481481481474E-4</v>
+      </c>
     </row>
     <row r="1505" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1505" t="s">
@@ -63054,6 +63396,12 @@
       <c r="I1505">
         <v>0</v>
       </c>
+      <c r="J1505" s="10">
+        <v>6.6063391203703706E-2</v>
+      </c>
+      <c r="K1505" s="11">
+        <v>8.9569444444444451E-4</v>
+      </c>
     </row>
     <row r="1506" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1506" t="s">
@@ -63084,6 +63432,12 @@
       <c r="I1506">
         <v>0</v>
       </c>
+      <c r="J1506" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1506" s="11">
+        <v>9.0475694444444436E-4</v>
+      </c>
     </row>
     <row r="1507" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1507" t="s">
@@ -63114,6 +63468,12 @@
       <c r="I1507">
         <v>0</v>
       </c>
+      <c r="J1507" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1507" s="11">
+        <v>8.9224537037037039E-4</v>
+      </c>
     </row>
     <row r="1508" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1508" t="s">
@@ -64159,7 +64519,7 @@
         <v>1.2634490740740742E-3</v>
       </c>
     </row>
-    <row r="1537" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1537" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1537" t="s">
         <v>30</v>
       </c>
@@ -64195,7 +64555,7 @@
         <v>1.2550578703703704E-3</v>
       </c>
     </row>
-    <row r="1538" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1538" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1538" t="s">
         <v>30</v>
       </c>
@@ -64231,7 +64591,7 @@
         <v>1.2644675925925926E-3</v>
       </c>
     </row>
-    <row r="1539" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1539" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1539" t="s">
         <v>30</v>
       </c>
@@ -64267,7 +64627,7 @@
         <v>1.259224537037037E-3</v>
       </c>
     </row>
-    <row r="1540" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1540" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1540" t="s">
         <v>30</v>
       </c>
@@ -64303,7 +64663,7 @@
         <v>1.260173611111111E-3</v>
       </c>
     </row>
-    <row r="1541" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1541" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1541" t="s">
         <v>30</v>
       </c>
@@ -64339,7 +64699,7 @@
         <v>1.2382754629629629E-3</v>
       </c>
     </row>
-    <row r="1542" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1542" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1542" t="s">
         <v>30</v>
       </c>
@@ -64375,7 +64735,7 @@
         <v>1.2699421296296295E-3</v>
       </c>
     </row>
-    <row r="1543" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1543" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1543" t="s">
         <v>30</v>
       </c>
@@ -64411,7 +64771,7 @@
         <v>1.2663310185185186E-3</v>
       </c>
     </row>
-    <row r="1544" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1544" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1544" t="s">
         <v>30</v>
       </c>
@@ -64444,10 +64804,11 @@
         <v>199</v>
       </c>
       <c r="K1544" s="11">
-        <v>1.2665162037037035E-3</v>
-      </c>
-    </row>
-    <row r="1545" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1.2340162037037038E-3</v>
+      </c>
+      <c r="L1544" s="11"/>
+    </row>
+    <row r="1545" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1545" t="s">
         <v>30</v>
       </c>
@@ -64480,10 +64841,11 @@
         <v>199</v>
       </c>
       <c r="K1545" s="11">
-        <v>1.2679976851851852E-3</v>
-      </c>
-    </row>
-    <row r="1546" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1.2503472222222221E-3</v>
+      </c>
+      <c r="L1545" s="11"/>
+    </row>
+    <row r="1546" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1546" t="s">
         <v>30</v>
       </c>
@@ -64516,10 +64878,11 @@
         <v>199</v>
       </c>
       <c r="K1546" s="11">
-        <v>1.2503472222222221E-3</v>
-      </c>
-    </row>
-    <row r="1547" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1.2679976851851852E-3</v>
+      </c>
+      <c r="L1546" s="11"/>
+    </row>
+    <row r="1547" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1547" t="s">
         <v>30</v>
       </c>
@@ -64552,10 +64915,11 @@
         <v>199</v>
       </c>
       <c r="K1547" s="11">
-        <v>1.2340162037037038E-3</v>
-      </c>
-    </row>
-    <row r="1548" spans="1:11" x14ac:dyDescent="0.45">
+        <v>1.2665162037037035E-3</v>
+      </c>
+      <c r="L1547" s="11"/>
+    </row>
+    <row r="1548" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1548" t="s">
         <v>37</v>
       </c>
@@ -64563,7 +64927,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1549" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1549" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1549" t="s">
         <v>37</v>
       </c>
@@ -64571,7 +64935,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1550" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1550" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1550" t="s">
         <v>37</v>
       </c>
@@ -64579,7 +64943,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1551" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1551" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1551" t="s">
         <v>37</v>
       </c>
@@ -64587,7 +64951,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1552" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1552" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1552" t="s">
         <v>37</v>
       </c>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="284" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A40A6675-821B-4D23-98A0-A6F13CDF11FC}"/>
+  <xr:revisionPtr revIDLastSave="321" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA0E72C9-EFFF-4A3D-BFF3-06C4E2C94508}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16387" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16450" uniqueCount="200">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -63530,7 +63530,7 @@
         <v>33</v>
       </c>
       <c r="G1509" t="str">
-        <f t="shared" ref="G1509:G1547" si="2">VLOOKUP(F1509,$L$1408:$M$1427,2,FALSE)</f>
+        <f t="shared" ref="G1509:G1567" si="2">VLOOKUP(F1509,$L$1408:$M$1427,2,FALSE)</f>
         <v>Red Bull</v>
       </c>
       <c r="H1509">
@@ -64915,166 +64915,726 @@
       </c>
     </row>
     <row r="1548" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1548" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1548">
+        <v>15</v>
+      </c>
       <c r="E1548" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1548" t="s">
-        <v>37</v>
+        <v>171</v>
+      </c>
+      <c r="F1548" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1548" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1548">
+        <v>1</v>
+      </c>
+      <c r="I1548">
+        <v>25</v>
+      </c>
+      <c r="J1548" s="10">
+        <v>7.3704687500000005E-2</v>
+      </c>
+      <c r="K1548" s="11">
+        <v>1.1031365740740741E-3</v>
       </c>
     </row>
     <row r="1549" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1549" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1549">
+        <v>15</v>
+      </c>
       <c r="E1549" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1549" t="s">
-        <v>37</v>
+        <v>171</v>
+      </c>
+      <c r="F1549" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1549" t="str">
+        <f t="shared" si="2"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1549">
+        <v>2</v>
+      </c>
+      <c r="I1549">
+        <v>18</v>
+      </c>
+      <c r="J1549" s="10">
+        <v>7.3941817129629633E-2</v>
+      </c>
+      <c r="K1549" s="11">
+        <v>1.1323611111111111E-3</v>
       </c>
     </row>
     <row r="1550" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1550" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1550">
+        <v>15</v>
+      </c>
       <c r="E1550" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1550" t="s">
-        <v>37</v>
+        <v>171</v>
+      </c>
+      <c r="F1550" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1550" t="str">
+        <f t="shared" si="2"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1550">
+        <v>3</v>
+      </c>
+      <c r="I1550">
+        <v>15</v>
+      </c>
+      <c r="J1550" s="10">
+        <v>7.3990428240740744E-2</v>
+      </c>
+      <c r="K1550" s="11">
+        <v>1.1340625000000001E-3</v>
       </c>
     </row>
     <row r="1551" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1551" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1551">
+        <v>15</v>
+      </c>
       <c r="E1551" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1551" t="s">
-        <v>37</v>
+        <v>171</v>
+      </c>
+      <c r="F1551" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1551" t="str">
+        <f t="shared" si="2"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1551">
+        <v>4</v>
+      </c>
+      <c r="I1551">
+        <v>12</v>
+      </c>
+      <c r="J1551" s="10">
+        <v>7.40870138888889E-2</v>
+      </c>
+      <c r="K1551" s="11">
+        <v>1.1337384259259258E-3</v>
       </c>
     </row>
     <row r="1552" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1552" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1552">
+        <v>15</v>
+      </c>
       <c r="E1552" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1552" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1553" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1552" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1552" t="str">
+        <f t="shared" si="2"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1552">
+        <v>5</v>
+      </c>
+      <c r="I1552">
+        <v>10</v>
+      </c>
+      <c r="J1552" s="10">
+        <v>7.4109375000000005E-2</v>
+      </c>
+      <c r="K1552" s="11">
+        <v>1.1382407407407407E-3</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1553" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1553">
+        <v>15</v>
+      </c>
       <c r="E1553" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1553" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1554" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1553" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1553" t="str">
+        <f t="shared" si="2"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1553">
+        <v>6</v>
+      </c>
+      <c r="I1553">
+        <v>8</v>
+      </c>
+      <c r="J1553" s="10">
+        <v>7.4116041666666674E-2</v>
+      </c>
+      <c r="K1553" s="11">
+        <v>1.137175925925926E-3</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1554" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1554">
+        <v>15</v>
+      </c>
       <c r="E1554" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1554" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1555" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1554" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1554" t="str">
+        <f t="shared" si="2"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1554">
+        <v>7</v>
+      </c>
+      <c r="I1554">
+        <v>6</v>
+      </c>
+      <c r="J1554" s="10">
+        <v>7.4135451388888884E-2</v>
+      </c>
+      <c r="K1554" s="11">
+        <v>1.1441319444444446E-3</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1555" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1555">
+        <v>15</v>
+      </c>
       <c r="E1555" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1555" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1556" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1555" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1555" t="str">
+        <f t="shared" si="2"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1555">
+        <v>8</v>
+      </c>
+      <c r="I1555">
+        <v>4</v>
+      </c>
+      <c r="J1555" s="10">
+        <v>7.4145162037037041E-2</v>
+      </c>
+      <c r="K1555" s="11">
+        <v>1.1439930555555556E-3</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1556" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1556">
+        <v>15</v>
+      </c>
       <c r="E1556" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1556" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1557" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1556" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1556" t="str">
+        <f t="shared" si="2"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1556">
+        <v>9</v>
+      </c>
+      <c r="I1556">
+        <v>2</v>
+      </c>
+      <c r="J1556" s="10">
+        <v>7.4167326388888885E-2</v>
+      </c>
+      <c r="K1556" s="11">
+        <v>1.1392939814814816E-3</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1557" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1557">
+        <v>15</v>
+      </c>
       <c r="E1557" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1557" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1558" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1557" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1557" t="str">
+        <f t="shared" si="2"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1557">
+        <v>10</v>
+      </c>
+      <c r="I1557">
+        <v>1</v>
+      </c>
+      <c r="J1557" s="10">
+        <v>7.4186215277777787E-2</v>
+      </c>
+      <c r="K1557" s="11">
+        <v>1.1411458333333334E-3</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1558" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1558">
+        <v>15</v>
+      </c>
       <c r="E1558" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1558" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1559" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1558" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1558" t="str">
+        <f t="shared" si="2"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1558">
+        <v>11</v>
+      </c>
+      <c r="I1558">
+        <v>0</v>
+      </c>
+      <c r="J1558" s="10">
+        <v>7.4099537037037033E-2</v>
+      </c>
+      <c r="K1558" s="11">
+        <v>1.1467708333333334E-3</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1559" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1559">
+        <v>15</v>
+      </c>
       <c r="E1559" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1559" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1560" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1559" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1559" t="str">
+        <f t="shared" si="2"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1559">
+        <v>12</v>
+      </c>
+      <c r="I1559">
+        <v>0</v>
+      </c>
+      <c r="J1559" s="10">
+        <v>7.422671296296296E-2</v>
+      </c>
+      <c r="K1559" s="11">
+        <v>1.1297106481481481E-3</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1560" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1560">
+        <v>15</v>
+      </c>
       <c r="E1560" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1560" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1561" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1560" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1560" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1560">
+        <v>13</v>
+      </c>
+      <c r="I1560">
+        <v>0</v>
+      </c>
+      <c r="J1560" s="10">
+        <v>7.4228032407407399E-2</v>
+      </c>
+      <c r="K1560" s="11">
+        <v>1.1443981481481483E-3</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1561" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1561">
+        <v>15</v>
+      </c>
       <c r="E1561" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1561" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1562" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1561" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1561" t="str">
+        <f t="shared" si="2"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1561">
+        <v>14</v>
+      </c>
+      <c r="I1561">
+        <v>0</v>
+      </c>
+      <c r="J1561" s="10">
+        <v>7.423472222222223E-2</v>
+      </c>
+      <c r="K1561" s="11">
+        <v>1.1471064814814814E-3</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1562" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1562">
+        <v>15</v>
+      </c>
       <c r="E1562" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1562" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1563" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1562" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1562" t="str">
+        <f t="shared" si="2"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1562">
+        <v>15</v>
+      </c>
+      <c r="I1562">
+        <v>0</v>
+      </c>
+      <c r="J1562" s="10">
+        <v>7.4379155092592603E-2</v>
+      </c>
+      <c r="K1562" s="11">
+        <v>1.1502314814814815E-3</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1563" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1563">
+        <v>15</v>
+      </c>
       <c r="E1563" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1563" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1564" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1563" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1563" t="str">
+        <f t="shared" si="2"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1563">
+        <v>16</v>
+      </c>
+      <c r="I1563">
+        <v>0</v>
+      </c>
+      <c r="J1563" s="10">
+        <v>7.4731620370370372E-2</v>
+      </c>
+      <c r="K1563" s="11">
+        <v>1.1508796296296297E-3</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1564" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1564">
+        <v>15</v>
+      </c>
       <c r="E1564" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1564" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1565" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1564" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1564" t="str">
+        <f t="shared" si="2"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1564">
+        <v>17</v>
+      </c>
+      <c r="I1564">
+        <v>0</v>
+      </c>
+      <c r="J1564" s="10">
+        <v>7.479993055555556E-2</v>
+      </c>
+      <c r="K1564" s="11">
+        <v>1.1516666666666665E-3</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1565" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1565">
+        <v>15</v>
+      </c>
       <c r="E1565" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1565" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1566" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1565" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1565" t="str">
+        <f t="shared" si="2"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1565">
+        <v>18</v>
+      </c>
+      <c r="I1565">
+        <v>0</v>
+      </c>
+      <c r="J1565" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1565" s="11">
+        <v>1.1398032407407407E-3</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1566" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1566">
+        <v>15</v>
+      </c>
       <c r="E1566" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1566" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1567" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1566" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1566" t="str">
+        <f t="shared" si="2"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1566">
+        <v>19</v>
+      </c>
+      <c r="I1566">
+        <v>0</v>
+      </c>
+      <c r="J1566" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1566" s="11">
+        <v>1.1530555555555556E-3</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1567" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1567">
+        <v>15</v>
+      </c>
       <c r="E1567" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1567" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1568" spans="5:9" x14ac:dyDescent="0.45">
+        <v>171</v>
+      </c>
+      <c r="F1567" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1567" t="str">
+        <f t="shared" si="2"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1567">
+        <v>20</v>
+      </c>
+      <c r="I1567">
+        <v>0</v>
+      </c>
+      <c r="J1567" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1567" s="11">
+        <v>1.1467013888888889E-3</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1568" t="s">
         <v>37</v>
       </c>
@@ -91184,7 +91744,7 @@
         <v>Marina Bay Street Circuit</v>
       </c>
       <c r="F16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K16" t="s">
         <v>127</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="321" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA0E72C9-EFFF-4A3D-BFF3-06C4E2C94508}"/>
+  <xr:revisionPtr revIDLastSave="330" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F3933D7-5A56-4D5E-9E3A-BF2E158DF81B}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16450" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16451" uniqueCount="201">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -643,6 +643,9 @@
   <si>
     <t>DNF</t>
   </si>
+  <si>
+    <t>Time (Lisbon)</t>
+  </si>
 </sst>
 </file>
 
@@ -712,7 +715,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -725,6 +728,7 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -91319,6 +91323,9 @@
       <c r="F1" s="7" t="s">
         <v>194</v>
       </c>
+      <c r="G1" s="7" t="s">
+        <v>200</v>
+      </c>
       <c r="K1" s="8" t="s">
         <v>26</v>
       </c>
@@ -91762,8 +91769,7 @@
         <v>16</v>
       </c>
       <c r="C17" s="9">
-        <f t="shared" si="4"/>
-        <v>46173</v>
+        <v>46172</v>
       </c>
       <c r="D17" t="s">
         <v>120</v>
@@ -91775,6 +91781,9 @@
       <c r="F17" t="s">
         <v>196</v>
       </c>
+      <c r="G17" s="12">
+        <v>0.25</v>
+      </c>
       <c r="K17" t="s">
         <v>168</v>
       </c>
@@ -91791,7 +91800,6 @@
         <v>17</v>
       </c>
       <c r="C18" s="9">
-        <f t="shared" si="4"/>
         <v>46180</v>
       </c>
       <c r="D18" t="s">
@@ -91804,6 +91812,9 @@
       <c r="F18" t="s">
         <v>196</v>
       </c>
+      <c r="G18" s="12">
+        <v>0.3125</v>
+      </c>
       <c r="K18" t="s">
         <v>17</v>
       </c>
@@ -91833,6 +91844,9 @@
       <c r="F19" t="s">
         <v>196</v>
       </c>
+      <c r="G19" s="12">
+        <v>0.3125</v>
+      </c>
       <c r="K19" t="s">
         <v>118</v>
       </c>
@@ -91862,6 +91876,9 @@
       <c r="F20" t="s">
         <v>196</v>
       </c>
+      <c r="G20" s="12">
+        <v>0.3125</v>
+      </c>
       <c r="K20" t="s">
         <v>174</v>
       </c>
@@ -91891,6 +91908,9 @@
       <c r="F21" t="s">
         <v>196</v>
       </c>
+      <c r="G21" s="12">
+        <v>0.3125</v>
+      </c>
       <c r="K21" t="s">
         <v>20</v>
       </c>
@@ -91920,6 +91940,9 @@
       <c r="F22" t="s">
         <v>196</v>
       </c>
+      <c r="G22" s="12">
+        <v>0.3125</v>
+      </c>
       <c r="K22" t="s">
         <v>124</v>
       </c>
@@ -91949,6 +91972,9 @@
       <c r="F23" t="s">
         <v>196</v>
       </c>
+      <c r="G23" s="12">
+        <v>0.3125</v>
+      </c>
       <c r="K23" t="s">
         <v>123</v>
       </c>
@@ -91977,6 +92003,9 @@
       </c>
       <c r="F24" t="s">
         <v>196</v>
+      </c>
+      <c r="G24" s="12">
+        <v>0.3125</v>
       </c>
       <c r="K24" t="s">
         <v>121</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F3933D7-5A56-4D5E-9E3A-BF2E158DF81B}"/>
+  <xr:revisionPtr revIDLastSave="374" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{990BF967-70BA-43E1-80D6-50A92AEE62DE}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16451" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16512" uniqueCount="201">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -19187,6 +19187,7 @@
     <col min="9" max="9" width="6.265625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.86328125" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
+    <col min="15" max="15" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
@@ -63534,7 +63535,7 @@
         <v>33</v>
       </c>
       <c r="G1509" t="str">
-        <f t="shared" ref="G1509:G1567" si="2">VLOOKUP(F1509,$L$1408:$M$1427,2,FALSE)</f>
+        <f t="shared" ref="G1509:G1572" si="2">VLOOKUP(F1509,$L$1408:$M$1427,2,FALSE)</f>
         <v>Red Bull</v>
       </c>
       <c r="H1509">
@@ -65639,166 +65640,726 @@
       </c>
     </row>
     <row r="1568" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1568" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1568">
+        <v>16</v>
+      </c>
       <c r="E1568" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1568" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1569" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1568" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1568" t="str">
+        <f t="shared" si="2"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1568">
+        <v>1</v>
+      </c>
+      <c r="I1568">
+        <v>25</v>
+      </c>
+      <c r="J1568" s="10">
+        <v>6.6741423611111114E-2</v>
+      </c>
+      <c r="K1568" s="11">
+        <v>1.1471759259259258E-3</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1569" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1569">
+        <v>16</v>
+      </c>
       <c r="E1569" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1569" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1570" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1569" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1569" t="str">
+        <f t="shared" si="2"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1569">
+        <v>2</v>
+      </c>
+      <c r="I1569">
+        <v>18</v>
+      </c>
+      <c r="J1569" s="10">
+        <v>6.7042673611111117E-2</v>
+      </c>
+      <c r="K1569" s="11">
+        <v>1.1476967592592593E-3</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1570" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1570">
+        <v>16</v>
+      </c>
       <c r="E1570" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1570" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1571" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1570" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1570" t="str">
+        <f t="shared" si="2"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1570">
+        <v>3</v>
+      </c>
+      <c r="I1570">
+        <v>15</v>
+      </c>
+      <c r="J1570" s="10">
+        <v>6.716387731481481E-2</v>
+      </c>
+      <c r="K1570" s="11">
+        <v>1.1633564814814816E-3</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1571" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1571">
+        <v>16</v>
+      </c>
       <c r="E1571" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1571" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1572" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1571" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1571" t="str">
+        <f t="shared" si="2"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1571">
+        <v>4</v>
+      </c>
+      <c r="I1571">
+        <v>12</v>
+      </c>
+      <c r="J1571" s="10">
+        <v>6.7396412037037043E-2</v>
+      </c>
+      <c r="K1571" s="11">
+        <v>1.1500694444444444E-3</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1572" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1572">
+        <v>16</v>
+      </c>
       <c r="E1572" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1572" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1573" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1572" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1572" t="str">
+        <f t="shared" si="2"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1572">
+        <v>5</v>
+      </c>
+      <c r="I1572">
+        <v>10</v>
+      </c>
+      <c r="J1572" s="10">
+        <v>6.7437627314814813E-2</v>
+      </c>
+      <c r="K1572" s="11">
+        <v>1.1723032407407409E-3</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1573" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1573">
+        <v>16</v>
+      </c>
       <c r="E1573" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1573" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1574" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1573" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1573" t="str">
+        <f t="shared" ref="G1573:G1587" si="3">VLOOKUP(F1573,$L$1408:$M$1427,2,FALSE)</f>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1573">
+        <v>6</v>
+      </c>
+      <c r="I1573">
+        <v>8</v>
+      </c>
+      <c r="J1573" s="10">
+        <v>6.7454178240740736E-2</v>
+      </c>
+      <c r="K1573" s="11">
+        <v>1.1652430555555554E-3</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1574" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1574">
+        <v>16</v>
+      </c>
       <c r="E1574" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1574" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1575" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1574" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1574" t="str">
+        <f t="shared" si="3"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1574">
+        <v>7</v>
+      </c>
+      <c r="I1574">
+        <v>6</v>
+      </c>
+      <c r="J1574" s="10">
+        <v>6.7478668981481485E-2</v>
+      </c>
+      <c r="K1574" s="11">
+        <v>1.174976851851852E-3</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1575" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1575">
+        <v>16</v>
+      </c>
       <c r="E1575" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1575" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1576" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1575" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1575" t="str">
+        <f t="shared" si="3"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1575">
+        <v>8</v>
+      </c>
+      <c r="I1575">
+        <v>4</v>
+      </c>
+      <c r="J1575" s="10">
+        <v>6.7487731481481475E-2</v>
+      </c>
+      <c r="K1575" s="11">
+        <v>1.1762731481481481E-3</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1576" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1576">
+        <v>16</v>
+      </c>
       <c r="E1576" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1576" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1577" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1576" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1576" t="str">
+        <f t="shared" si="3"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1576">
+        <v>9</v>
+      </c>
+      <c r="I1576">
+        <v>2</v>
+      </c>
+      <c r="J1576" s="10">
+        <v>6.7553842592592589E-2</v>
+      </c>
+      <c r="K1576" s="11">
+        <v>1.1732175925925927E-3</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1577" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1577">
+        <v>16</v>
+      </c>
       <c r="E1577" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1577" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1578" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1577" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1577" t="str">
+        <f t="shared" si="3"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1577">
+        <v>10</v>
+      </c>
+      <c r="I1577">
+        <v>1</v>
+      </c>
+      <c r="J1577" s="10">
+        <v>6.7651574074074072E-2</v>
+      </c>
+      <c r="K1577" s="11">
+        <v>1.1724652777777777E-3</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1578" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1578">
+        <v>16</v>
+      </c>
       <c r="E1578" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1578" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1579" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1578" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1578" t="str">
+        <f t="shared" si="3"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1578">
+        <v>11</v>
+      </c>
+      <c r="I1578">
+        <v>0</v>
+      </c>
+      <c r="J1578" s="10">
+        <v>6.7674374999999995E-2</v>
+      </c>
+      <c r="K1578" s="11">
+        <v>1.167025462962963E-3</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1579" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1579">
+        <v>16</v>
+      </c>
       <c r="E1579" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1579" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1580" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1579" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1579" t="str">
+        <f t="shared" si="3"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1579">
+        <v>12</v>
+      </c>
+      <c r="I1579">
+        <v>0</v>
+      </c>
+      <c r="J1579" s="10">
+        <v>6.7807928240740736E-2</v>
+      </c>
+      <c r="K1579" s="11">
+        <v>1.1755092592592592E-3</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1580" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1580">
+        <v>16</v>
+      </c>
       <c r="E1580" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1580" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1581" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1580" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1580" t="str">
+        <f t="shared" si="3"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1580">
+        <v>13</v>
+      </c>
+      <c r="I1580">
+        <v>0</v>
+      </c>
+      <c r="J1580" s="10">
+        <v>6.6780798611111108E-2</v>
+      </c>
+      <c r="K1580" s="11">
+        <v>1.1837500000000001E-3</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1581" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1581">
+        <v>16</v>
+      </c>
       <c r="E1581" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1581" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1582" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1581" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1581" t="str">
+        <f t="shared" si="3"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1581">
+        <v>14</v>
+      </c>
+      <c r="I1581">
+        <v>0</v>
+      </c>
+      <c r="J1581" s="10">
+        <v>6.6782939814814812E-2</v>
+      </c>
+      <c r="K1581" s="11">
+        <v>1.1440162037037037E-3</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1582" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1582">
+        <v>16</v>
+      </c>
       <c r="E1582" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1582" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1583" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1582" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1582" t="str">
+        <f t="shared" si="3"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1582">
+        <v>15</v>
+      </c>
+      <c r="I1582">
+        <v>0</v>
+      </c>
+      <c r="J1582" s="10">
+        <v>6.680951388888888E-2</v>
+      </c>
+      <c r="K1582" s="11">
+        <v>1.1763425925925925E-3</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1583" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1583">
+        <v>16</v>
+      </c>
       <c r="E1583" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1583" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1584" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1583" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1583" t="str">
+        <f t="shared" si="3"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1583">
+        <v>16</v>
+      </c>
+      <c r="I1583">
+        <v>0</v>
+      </c>
+      <c r="J1583" s="10">
+        <v>6.6845324074074064E-2</v>
+      </c>
+      <c r="K1583" s="11">
+        <v>1.1839583333333333E-3</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1584" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1584">
+        <v>16</v>
+      </c>
       <c r="E1584" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1584" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1585" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1584" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1584" t="str">
+        <f t="shared" si="3"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1584">
+        <v>17</v>
+      </c>
+      <c r="I1584">
+        <v>0</v>
+      </c>
+      <c r="J1584" s="10">
+        <v>6.6931909722222224E-2</v>
+      </c>
+      <c r="K1584" s="11">
+        <v>1.1836458333333332E-3</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1585" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1585">
+        <v>16</v>
+      </c>
       <c r="E1585" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1585" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1586" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1585" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1585" t="str">
+        <f t="shared" si="3"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1585">
+        <v>18</v>
+      </c>
+      <c r="I1585">
+        <v>0</v>
+      </c>
+      <c r="J1585" s="10">
+        <v>6.7022222222222219E-2</v>
+      </c>
+      <c r="K1585" s="11">
+        <v>1.1818171296296297E-3</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1586" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1586">
+        <v>16</v>
+      </c>
       <c r="E1586" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1586" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1587" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1586" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1586" t="str">
+        <f t="shared" si="3"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1586">
+        <v>19</v>
+      </c>
+      <c r="I1586">
+        <v>0</v>
+      </c>
+      <c r="J1586" s="10">
+        <v>6.7417766203703711E-2</v>
+      </c>
+      <c r="K1586" s="11">
+        <v>1.1881481481481482E-3</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1587" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1587">
+        <v>16</v>
+      </c>
       <c r="E1587" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1587" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1588" spans="5:9" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+      <c r="F1587" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1587" t="str">
+        <f t="shared" si="3"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1587">
+        <v>20</v>
+      </c>
+      <c r="I1587">
+        <v>0</v>
+      </c>
+      <c r="J1587" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1587" s="11">
+        <v>1.1902083333333333E-3</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1588" t="s">
         <v>37</v>
       </c>
@@ -65806,7 +66367,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1589" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1589" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1589" t="s">
         <v>37</v>
       </c>
@@ -65814,7 +66375,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1590" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1590" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1590" t="s">
         <v>37</v>
       </c>
@@ -65822,7 +66383,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1591" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1591" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1591" t="s">
         <v>37</v>
       </c>
@@ -65830,7 +66391,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1592" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1592" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1592" t="s">
         <v>37</v>
       </c>
@@ -65838,7 +66399,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1593" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1593" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1593" t="s">
         <v>37</v>
       </c>
@@ -65846,7 +66407,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1594" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1594" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1594" t="s">
         <v>37</v>
       </c>
@@ -65854,7 +66415,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1595" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1595" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1595" t="s">
         <v>37</v>
       </c>
@@ -65862,7 +66423,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1596" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1596" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1596" t="s">
         <v>37</v>
       </c>
@@ -65870,7 +66431,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1597" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1597" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1597" t="s">
         <v>37</v>
       </c>
@@ -65878,7 +66439,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1598" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1598" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1598" t="s">
         <v>37</v>
       </c>
@@ -65886,7 +66447,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1599" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1599" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1599" t="s">
         <v>37</v>
       </c>
@@ -65894,7 +66455,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1600" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1600" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1600" t="s">
         <v>37</v>
       </c>
@@ -91779,7 +92340,7 @@
         <v>Circuit of the Americas</v>
       </c>
       <c r="F17" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G17" s="12">
         <v>0.25</v>
@@ -91813,7 +92374,7 @@
         <v>196</v>
       </c>
       <c r="G18" s="12">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="K18" t="s">
         <v>17</v>
@@ -91845,7 +92406,7 @@
         <v>196</v>
       </c>
       <c r="G19" s="12">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="K19" t="s">
         <v>118</v>
@@ -91877,7 +92438,7 @@
         <v>196</v>
       </c>
       <c r="G20" s="12">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="K20" t="s">
         <v>174</v>
@@ -91909,7 +92470,7 @@
         <v>196</v>
       </c>
       <c r="G21" s="12">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="K21" t="s">
         <v>20</v>
@@ -91941,7 +92502,7 @@
         <v>196</v>
       </c>
       <c r="G22" s="12">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="K22" t="s">
         <v>124</v>
@@ -91973,7 +92534,7 @@
         <v>196</v>
       </c>
       <c r="G23" s="12">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="K23" t="s">
         <v>123</v>
@@ -92005,7 +92566,7 @@
         <v>196</v>
       </c>
       <c r="G24" s="12">
-        <v>0.3125</v>
+        <v>0.25</v>
       </c>
       <c r="K24" t="s">
         <v>121</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="374" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{990BF967-70BA-43E1-80D6-50A92AEE62DE}"/>
+  <xr:revisionPtr revIDLastSave="416" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0187AD65-709B-46BC-9C7E-130684E3827F}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16512" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16574" uniqueCount="201">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -65839,7 +65839,7 @@
         <v>1</v>
       </c>
       <c r="G1573" t="str">
-        <f t="shared" ref="G1573:G1587" si="3">VLOOKUP(F1573,$L$1408:$M$1427,2,FALSE)</f>
+        <f t="shared" ref="G1573:G1607" si="3">VLOOKUP(F1573,$L$1408:$M$1427,2,FALSE)</f>
         <v>Red Bull</v>
       </c>
       <c r="H1573">
@@ -66251,7 +66251,7 @@
         <v>1.1836458333333332E-3</v>
       </c>
     </row>
-    <row r="1585" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1585" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1585" t="s">
         <v>30</v>
       </c>
@@ -66287,7 +66287,7 @@
         <v>1.1818171296296297E-3</v>
       </c>
     </row>
-    <row r="1586" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1586" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1586" t="s">
         <v>30</v>
       </c>
@@ -66323,7 +66323,7 @@
         <v>1.1881481481481482E-3</v>
       </c>
     </row>
-    <row r="1587" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1587" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1587" t="s">
         <v>30</v>
       </c>
@@ -66359,167 +66359,745 @@
         <v>1.1902083333333333E-3</v>
       </c>
     </row>
-    <row r="1588" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1588" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1588" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1588">
+        <v>17</v>
+      </c>
       <c r="E1588" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1588" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1589" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1588" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1588" t="str">
+        <f t="shared" si="3"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1588">
+        <v>1</v>
+      </c>
+      <c r="I1588">
+        <v>25</v>
+      </c>
+      <c r="J1588" s="10">
+        <v>6.9733738425925923E-2</v>
+      </c>
+      <c r="K1588" s="11">
+        <v>9.5912037037037027E-4</v>
+      </c>
+      <c r="L1588" s="10"/>
+    </row>
+    <row r="1589" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1589" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1589">
+        <v>17</v>
+      </c>
       <c r="E1589" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1589" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1590" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1589" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1589" t="str">
+        <f t="shared" si="3"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1589">
+        <v>2</v>
+      </c>
+      <c r="I1589">
+        <v>18</v>
+      </c>
+      <c r="J1589" s="10">
+        <v>6.981037037037037E-2</v>
+      </c>
+      <c r="K1589" s="11">
+        <v>9.3173611111111105E-4</v>
+      </c>
+      <c r="L1589" s="10"/>
+    </row>
+    <row r="1590" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1590" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1590">
+        <v>17</v>
+      </c>
       <c r="E1590" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1590" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1591" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1590" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1590" t="str">
+        <f t="shared" si="3"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1590">
+        <v>3</v>
+      </c>
+      <c r="I1590">
+        <v>15</v>
+      </c>
+      <c r="J1590" s="10">
+        <v>6.9947083333333326E-2</v>
+      </c>
+      <c r="K1590" s="11">
+        <v>9.4765046296296286E-4</v>
+      </c>
+      <c r="L1590" s="10"/>
+    </row>
+    <row r="1591" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1591" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1591">
+        <v>17</v>
+      </c>
       <c r="E1591" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1591" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1592" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1591" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1591" t="str">
+        <f t="shared" si="3"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1591">
+        <v>4</v>
+      </c>
+      <c r="I1591">
+        <v>12</v>
+      </c>
+      <c r="J1591" s="10">
+        <v>7.0045057870370367E-2</v>
+      </c>
+      <c r="K1591" s="11">
+        <v>9.4084490740740738E-4</v>
+      </c>
+      <c r="L1591" s="10"/>
+    </row>
+    <row r="1592" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1592" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1592">
+        <v>17</v>
+      </c>
       <c r="E1592" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1592" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1593" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1592" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1592" t="str">
+        <f t="shared" si="3"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1592">
+        <v>5</v>
+      </c>
+      <c r="I1592">
+        <v>10</v>
+      </c>
+      <c r="J1592" s="10">
+        <v>7.0175706018518511E-2</v>
+      </c>
+      <c r="K1592" s="11">
+        <v>9.4237268518518509E-4</v>
+      </c>
+      <c r="L1592" s="10"/>
+    </row>
+    <row r="1593" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1593" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1593">
+        <v>17</v>
+      </c>
       <c r="E1593" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1593" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1594" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1593" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1593" t="str">
+        <f t="shared" si="3"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1593">
+        <v>6</v>
+      </c>
+      <c r="I1593">
+        <v>8</v>
+      </c>
+      <c r="J1593" s="10">
+        <v>7.0228773148148141E-2</v>
+      </c>
+      <c r="K1593" s="11">
+        <v>9.5089120370370369E-4</v>
+      </c>
+      <c r="L1593" s="10"/>
+    </row>
+    <row r="1594" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1594" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1594">
+        <v>17</v>
+      </c>
       <c r="E1594" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1594" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1595" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1594" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1594" t="str">
+        <f t="shared" si="3"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1594">
+        <v>7</v>
+      </c>
+      <c r="I1594">
+        <v>6</v>
+      </c>
+      <c r="J1594" s="10">
+        <v>7.0258773148148157E-2</v>
+      </c>
+      <c r="K1594" s="11">
+        <v>9.5721064814814822E-4</v>
+      </c>
+      <c r="L1594" s="10"/>
+    </row>
+    <row r="1595" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1595" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1595">
+        <v>17</v>
+      </c>
       <c r="E1595" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1595" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1596" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1595" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1595" t="str">
+        <f t="shared" si="3"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1595">
+        <v>8</v>
+      </c>
+      <c r="I1595">
+        <v>4</v>
+      </c>
+      <c r="J1595" s="10">
+        <v>7.028391203703703E-2</v>
+      </c>
+      <c r="K1595" s="11">
+        <v>9.6894675925925924E-4</v>
+      </c>
+      <c r="L1595" s="10"/>
+    </row>
+    <row r="1596" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1596" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1596">
+        <v>17</v>
+      </c>
       <c r="E1596" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1596" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1597" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1596" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1596" t="str">
+        <f t="shared" si="3"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1596">
+        <v>9</v>
+      </c>
+      <c r="I1596">
+        <v>2</v>
+      </c>
+      <c r="J1596" s="10">
+        <v>7.0346655092592594E-2</v>
+      </c>
+      <c r="K1596" s="11">
+        <v>9.6190972222222229E-4</v>
+      </c>
+      <c r="L1596" s="10"/>
+    </row>
+    <row r="1597" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1597" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1597">
+        <v>17</v>
+      </c>
       <c r="E1597" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1597" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1598" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1597" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1597" t="str">
+        <f t="shared" si="3"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1597">
+        <v>10</v>
+      </c>
+      <c r="I1597">
+        <v>1</v>
+      </c>
+      <c r="J1597" s="10">
+        <v>7.0414988425925917E-2</v>
+      </c>
+      <c r="K1597" s="11">
+        <v>9.5680555555555558E-4</v>
+      </c>
+      <c r="L1597" s="10"/>
+    </row>
+    <row r="1598" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1598" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1598">
+        <v>17</v>
+      </c>
       <c r="E1598" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1598" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1599" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1598" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1598" t="str">
+        <f t="shared" si="3"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1598">
+        <v>11</v>
+      </c>
+      <c r="I1598">
+        <v>0</v>
+      </c>
+      <c r="J1598" s="10">
+        <v>7.0443726851851851E-2</v>
+      </c>
+      <c r="K1598" s="11">
+        <v>9.381134259259259E-4</v>
+      </c>
+      <c r="L1598" s="10"/>
+    </row>
+    <row r="1599" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1599" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1599">
+        <v>17</v>
+      </c>
       <c r="E1599" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1599" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1600" spans="1:11" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1599" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1599" t="str">
+        <f t="shared" si="3"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1599">
+        <v>12</v>
+      </c>
+      <c r="I1599">
+        <v>0</v>
+      </c>
+      <c r="J1599" s="10">
+        <v>7.0524363425925926E-2</v>
+      </c>
+      <c r="K1599" s="11">
+        <v>9.6269675925925917E-4</v>
+      </c>
+      <c r="L1599" s="10"/>
+    </row>
+    <row r="1600" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1600" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1600">
+        <v>17</v>
+      </c>
       <c r="E1600" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1600" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1601" spans="5:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1600" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1600" t="str">
+        <f t="shared" si="3"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1600">
+        <v>13</v>
+      </c>
+      <c r="I1600">
+        <v>0</v>
+      </c>
+      <c r="J1600" s="10">
+        <v>6.9810949074074077E-2</v>
+      </c>
+      <c r="K1600" s="11">
+        <v>9.6093750000000009E-4</v>
+      </c>
+      <c r="L1600" s="10"/>
+    </row>
+    <row r="1601" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1601" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1601">
+        <v>17</v>
+      </c>
       <c r="E1601" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1601" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1602" spans="5:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1601" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1601" t="str">
+        <f t="shared" si="3"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1601">
+        <v>14</v>
+      </c>
+      <c r="I1601">
+        <v>0</v>
+      </c>
+      <c r="J1601" s="10">
+        <v>7.0102662037037036E-2</v>
+      </c>
+      <c r="K1601" s="11">
+        <v>9.5895833333333336E-4</v>
+      </c>
+      <c r="L1601" s="10"/>
+    </row>
+    <row r="1602" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1602" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1602">
+        <v>17</v>
+      </c>
       <c r="E1602" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1602" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1603" spans="5:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1602" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1602" t="str">
+        <f t="shared" si="3"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1602">
+        <v>15</v>
+      </c>
+      <c r="I1602">
+        <v>0</v>
+      </c>
+      <c r="J1602" s="10">
+        <v>7.0140648148148146E-2</v>
+      </c>
+      <c r="K1602" s="11">
+        <v>9.6168981481481485E-4</v>
+      </c>
+      <c r="L1602" s="10"/>
+    </row>
+    <row r="1603" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1603" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1603">
+        <v>17</v>
+      </c>
       <c r="E1603" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1603" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1604" spans="5:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1603" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1603" t="str">
+        <f t="shared" si="3"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1603">
+        <v>16</v>
+      </c>
+      <c r="I1603">
+        <v>0</v>
+      </c>
+      <c r="J1603" s="10">
+        <v>7.016502314814814E-2</v>
+      </c>
+      <c r="K1603" s="11">
+        <v>9.6784722222222226E-4</v>
+      </c>
+      <c r="L1603" s="10"/>
+    </row>
+    <row r="1604" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1604" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1604">
+        <v>17</v>
+      </c>
       <c r="E1604" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1604" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1605" spans="5:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1604" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1604" t="str">
+        <f t="shared" si="3"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1604">
+        <v>17</v>
+      </c>
+      <c r="I1604">
+        <v>0</v>
+      </c>
+      <c r="J1604" s="10">
+        <v>7.0282384259259256E-2</v>
+      </c>
+      <c r="K1604" s="11">
+        <v>9.6285879629629629E-4</v>
+      </c>
+      <c r="L1604" s="10"/>
+    </row>
+    <row r="1605" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1605" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1605">
+        <v>17</v>
+      </c>
       <c r="E1605" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1605" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1606" spans="5:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1605" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1605" t="str">
+        <f t="shared" si="3"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1605">
+        <v>18</v>
+      </c>
+      <c r="I1605">
+        <v>0</v>
+      </c>
+      <c r="J1605" s="10">
+        <v>7.0443067129629625E-2</v>
+      </c>
+      <c r="K1605" s="11">
+        <v>9.7137731481481478E-4</v>
+      </c>
+      <c r="L1605" s="10"/>
+    </row>
+    <row r="1606" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1606" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1606">
+        <v>17</v>
+      </c>
       <c r="E1606" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1606" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1607" spans="5:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1606" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1606" t="str">
+        <f t="shared" si="3"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1606">
+        <v>19</v>
+      </c>
+      <c r="I1606">
+        <v>0</v>
+      </c>
+      <c r="J1606" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1606" s="11">
+        <v>9.5222222222222214E-4</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1607" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1607">
+        <v>17</v>
+      </c>
       <c r="E1607" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1607" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1608" spans="5:9" x14ac:dyDescent="0.45">
+        <v>174</v>
+      </c>
+      <c r="F1607" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1607" t="str">
+        <f t="shared" si="3"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1607">
+        <v>20</v>
+      </c>
+      <c r="I1607">
+        <v>0</v>
+      </c>
+      <c r="J1607" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1607" s="11">
+        <v>9.6890046296296286E-4</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1608" t="s">
         <v>37</v>
       </c>
@@ -66527,7 +67105,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1609" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1609" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1609" t="s">
         <v>37</v>
       </c>
@@ -66535,7 +67113,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1610" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1610" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1610" t="s">
         <v>37</v>
       </c>
@@ -66543,7 +67121,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1611" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1611" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1611" t="s">
         <v>37</v>
       </c>
@@ -66551,7 +67129,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1612" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1612" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1612" t="s">
         <v>37</v>
       </c>
@@ -66559,7 +67137,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1613" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1613" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1613" t="s">
         <v>37</v>
       </c>
@@ -66567,7 +67145,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1614" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1614" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1614" t="s">
         <v>37</v>
       </c>
@@ -66575,7 +67153,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1615" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1615" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1615" t="s">
         <v>37</v>
       </c>
@@ -66583,7 +67161,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1616" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1616" spans="1:12" x14ac:dyDescent="0.45">
       <c r="E1616" t="s">
         <v>37</v>
       </c>
@@ -92371,10 +92949,10 @@
         <v>Autódromo Hermanos Rodríguez</v>
       </c>
       <c r="F18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G18" s="12">
-        <v>0.25</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="K18" t="s">
         <v>17</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="416" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0187AD65-709B-46BC-9C7E-130684E3827F}"/>
+  <xr:revisionPtr revIDLastSave="449" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC4ADD6-C82D-4EDD-BAFF-CEE6AC5E97A4}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16574" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16636" uniqueCount="201">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -65839,7 +65839,7 @@
         <v>1</v>
       </c>
       <c r="G1573" t="str">
-        <f t="shared" ref="G1573:G1607" si="3">VLOOKUP(F1573,$L$1408:$M$1427,2,FALSE)</f>
+        <f t="shared" ref="G1573:G1627" si="3">VLOOKUP(F1573,$L$1408:$M$1427,2,FALSE)</f>
         <v>Red Bull</v>
       </c>
       <c r="H1573">
@@ -67098,166 +67098,726 @@
       </c>
     </row>
     <row r="1608" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1608" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1608">
+        <v>18</v>
+      </c>
       <c r="E1608" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1608" t="s">
-        <v>37</v>
+        <v>115</v>
+      </c>
+      <c r="F1608" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1608" t="str">
+        <f t="shared" si="3"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1608">
+        <v>1</v>
+      </c>
+      <c r="I1608">
+        <v>25</v>
+      </c>
+      <c r="J1608" s="10">
+        <v>5.7484317129629633E-2</v>
+      </c>
+      <c r="K1608" s="11">
+        <v>9.5979166666666674E-4</v>
       </c>
     </row>
     <row r="1609" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1609" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1609">
+        <v>18</v>
+      </c>
       <c r="E1609" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1609" t="s">
-        <v>37</v>
+        <v>115</v>
+      </c>
+      <c r="F1609" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1609" t="str">
+        <f t="shared" si="3"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1609">
+        <v>2</v>
+      </c>
+      <c r="I1609">
+        <v>18</v>
+      </c>
+      <c r="J1609" s="10">
+        <v>5.801526620370371E-2</v>
+      </c>
+      <c r="K1609" s="11">
+        <v>9.7291666666666674E-4</v>
       </c>
     </row>
     <row r="1610" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1610" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1610">
+        <v>18</v>
+      </c>
       <c r="E1610" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1610" t="s">
-        <v>37</v>
+        <v>115</v>
+      </c>
+      <c r="F1610" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1610" t="str">
+        <f t="shared" si="3"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1610">
+        <v>3</v>
+      </c>
+      <c r="I1610">
+        <v>15</v>
+      </c>
+      <c r="J1610" s="10">
+        <v>5.8060081018518513E-2</v>
+      </c>
+      <c r="K1610" s="11">
+        <v>9.8109953703703705E-4</v>
       </c>
     </row>
     <row r="1611" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1611" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1611">
+        <v>18</v>
+      </c>
       <c r="E1611" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1611" t="s">
-        <v>37</v>
+        <v>115</v>
+      </c>
+      <c r="F1611" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1611" t="str">
+        <f t="shared" si="3"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1611">
+        <v>4</v>
+      </c>
+      <c r="I1611">
+        <v>12</v>
+      </c>
+      <c r="J1611" s="10">
+        <v>5.8209699074074077E-2</v>
+      </c>
+      <c r="K1611" s="11">
+        <v>9.6856481481481479E-4</v>
       </c>
     </row>
     <row r="1612" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1612" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1612">
+        <v>18</v>
+      </c>
       <c r="E1612" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1612" t="s">
-        <v>37</v>
+        <v>115</v>
+      </c>
+      <c r="F1612" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1612" t="str">
+        <f t="shared" si="3"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1612">
+        <v>5</v>
+      </c>
+      <c r="I1612">
+        <v>10</v>
+      </c>
+      <c r="J1612" s="10">
+        <v>5.8309328703703707E-2</v>
+      </c>
+      <c r="K1612" s="11">
+        <v>9.7488425925925932E-4</v>
       </c>
     </row>
     <row r="1613" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1613" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1613">
+        <v>18</v>
+      </c>
       <c r="E1613" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1613" t="s">
-        <v>37</v>
+        <v>115</v>
+      </c>
+      <c r="F1613" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1613" t="str">
+        <f t="shared" si="3"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1613">
+        <v>6</v>
+      </c>
+      <c r="I1613">
+        <v>8</v>
+      </c>
+      <c r="J1613" s="10">
+        <v>5.7570173611111115E-2</v>
+      </c>
+      <c r="K1613" s="11">
+        <v>9.7722222222222221E-4</v>
       </c>
     </row>
     <row r="1614" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1614" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1614">
+        <v>18</v>
+      </c>
       <c r="E1614" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1614" t="s">
-        <v>37</v>
+        <v>115</v>
+      </c>
+      <c r="F1614" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1614" t="str">
+        <f t="shared" si="3"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1614">
+        <v>7</v>
+      </c>
+      <c r="I1614">
+        <v>6</v>
+      </c>
+      <c r="J1614" s="10">
+        <v>5.7614479166666663E-2</v>
+      </c>
+      <c r="K1614" s="11">
+        <v>9.8716435185185192E-4</v>
       </c>
     </row>
     <row r="1615" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1615" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1615">
+        <v>18</v>
+      </c>
       <c r="E1615" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1615" t="s">
-        <v>37</v>
+        <v>115</v>
+      </c>
+      <c r="F1615" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1615" t="str">
+        <f t="shared" si="3"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1615">
+        <v>8</v>
+      </c>
+      <c r="I1615">
+        <v>4</v>
+      </c>
+      <c r="J1615" s="10">
+        <v>5.7637175925925925E-2</v>
+      </c>
+      <c r="K1615" s="11">
+        <v>9.8804398148148146E-4</v>
       </c>
     </row>
     <row r="1616" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1616" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1616">
+        <v>18</v>
+      </c>
       <c r="E1616" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1616" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1617" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1616" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1616" t="str">
+        <f t="shared" si="3"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1616">
+        <v>9</v>
+      </c>
+      <c r="I1616">
+        <v>2</v>
+      </c>
+      <c r="J1616" s="10">
+        <v>5.8104178240740739E-2</v>
+      </c>
+      <c r="K1616" s="11">
+        <v>1.0029629629629631E-3</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1617" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1617">
+        <v>18</v>
+      </c>
       <c r="E1617" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1617" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1618" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1617" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1617" t="str">
+        <f t="shared" si="3"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1617">
+        <v>10</v>
+      </c>
+      <c r="I1617">
+        <v>1</v>
+      </c>
+      <c r="J1617" s="10">
+        <v>5.8154340277777779E-2</v>
+      </c>
+      <c r="K1617" s="11">
+        <v>9.965509259259259E-4</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1618" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1618">
+        <v>18</v>
+      </c>
       <c r="E1618" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1618" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1619" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1618" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1618" t="str">
+        <f t="shared" si="3"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1618">
+        <v>11</v>
+      </c>
+      <c r="I1618">
+        <v>0</v>
+      </c>
+      <c r="J1618" s="10">
+        <v>5.8173217592592592E-2</v>
+      </c>
+      <c r="K1618" s="11">
+        <v>9.8875000000000005E-4</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1619" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1619">
+        <v>18</v>
+      </c>
       <c r="E1619" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1619" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1620" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1619" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1619" t="str">
+        <f t="shared" si="3"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1619">
+        <v>12</v>
+      </c>
+      <c r="I1619">
+        <v>0</v>
+      </c>
+      <c r="J1619" s="10">
+        <v>5.8231215277777776E-2</v>
+      </c>
+      <c r="K1619" s="11">
+        <v>9.9081018518518507E-4</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1620" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1620">
+        <v>18</v>
+      </c>
       <c r="E1620" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1620" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1621" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1620" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1620" t="str">
+        <f t="shared" si="3"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1620">
+        <v>13</v>
+      </c>
+      <c r="I1620">
+        <v>0</v>
+      </c>
+      <c r="J1620" s="10">
+        <v>5.8259131944444445E-2</v>
+      </c>
+      <c r="K1620" s="11">
+        <v>1.000162037037037E-3</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1621" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1621">
+        <v>18</v>
+      </c>
       <c r="E1621" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1621" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1622" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1621" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1621" t="str">
+        <f t="shared" si="3"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1621">
+        <v>14</v>
+      </c>
+      <c r="I1621">
+        <v>0</v>
+      </c>
+      <c r="J1621" s="10">
+        <v>5.8297557870370366E-2</v>
+      </c>
+      <c r="K1621" s="11">
+        <v>9.9614583333333348E-4</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1622" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1622">
+        <v>18</v>
+      </c>
       <c r="E1622" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1622" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1623" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1622" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1622" t="str">
+        <f t="shared" si="3"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1622">
+        <v>15</v>
+      </c>
+      <c r="I1622">
+        <v>0</v>
+      </c>
+      <c r="J1622" s="10">
+        <v>5.8302025462962967E-2</v>
+      </c>
+      <c r="K1622" s="11">
+        <v>9.9490740740740746E-4</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1623" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1623">
+        <v>18</v>
+      </c>
       <c r="E1623" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1623" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1624" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1623" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1623" t="str">
+        <f t="shared" si="3"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1623">
+        <v>16</v>
+      </c>
+      <c r="I1623">
+        <v>0</v>
+      </c>
+      <c r="J1623" s="10">
+        <v>5.8392870370370373E-2</v>
+      </c>
+      <c r="K1623" s="11">
+        <v>9.9586805555555561E-4</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1624" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1624">
+        <v>18</v>
+      </c>
       <c r="E1624" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1624" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1625" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1624" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1624" t="str">
+        <f t="shared" si="3"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1624">
+        <v>17</v>
+      </c>
+      <c r="I1624">
+        <v>0</v>
+      </c>
+      <c r="J1624" s="10">
+        <v>5.7673055555555561E-2</v>
+      </c>
+      <c r="K1624" s="11">
+        <v>9.9767361111111107E-4</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1625" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1625">
+        <v>18</v>
+      </c>
       <c r="E1625" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1625" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1626" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1625" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1625" t="str">
+        <f t="shared" si="3"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1625">
+        <v>18</v>
+      </c>
+      <c r="I1625">
+        <v>0</v>
+      </c>
+      <c r="J1625" s="10">
+        <v>5.7696932870370372E-2</v>
+      </c>
+      <c r="K1625" s="11">
+        <v>1.0048726851851853E-3</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1626" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1626">
+        <v>18</v>
+      </c>
       <c r="E1626" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1626" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1627" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1626" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1626" t="str">
+        <f t="shared" si="3"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1626">
+        <v>19</v>
+      </c>
+      <c r="I1626">
+        <v>0</v>
+      </c>
+      <c r="J1626" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1626" s="11">
+        <v>9.787731481481481E-4</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1627" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1627">
+        <v>18</v>
+      </c>
       <c r="E1627" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1627" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1628" spans="5:9" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+      <c r="F1627" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1627" t="str">
+        <f t="shared" si="3"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1627">
+        <v>20</v>
+      </c>
+      <c r="I1627">
+        <v>0</v>
+      </c>
+      <c r="J1627" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1627" s="11">
+        <v>9.8826388888888879E-4</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1628" t="s">
         <v>37</v>
       </c>
@@ -67265,7 +67825,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1629" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1629" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1629" t="s">
         <v>37</v>
       </c>
@@ -67273,7 +67833,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1630" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1630" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1630" t="s">
         <v>37</v>
       </c>
@@ -67281,7 +67841,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1631" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1631" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1631" t="s">
         <v>37</v>
       </c>
@@ -67289,7 +67849,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1632" spans="5:9" x14ac:dyDescent="0.45">
+    <row r="1632" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1632" t="s">
         <v>37</v>
       </c>
@@ -92981,10 +93541,10 @@
         <v>Albert Park Circuit</v>
       </c>
       <c r="F19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G19" s="12">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="K19" t="s">
         <v>118</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="449" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FC4ADD6-C82D-4EDD-BAFF-CEE6AC5E97A4}"/>
+  <xr:revisionPtr revIDLastSave="483" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C987267-BC6E-4CE3-A21A-329597F81EA5}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="10" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16636" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16696" uniqueCount="201">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -67818,172 +67818,734 @@
       </c>
     </row>
     <row r="1628" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1628" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1628">
+        <v>19</v>
+      </c>
       <c r="E1628" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1628" t="s">
-        <v>37</v>
+        <v>176</v>
+      </c>
+      <c r="F1628" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1628" t="str">
+        <f t="shared" ref="G1628:G1647" si="4">VLOOKUP(F1628,$L$1408:$M$1427,2,FALSE)</f>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1628">
+        <v>1</v>
+      </c>
+      <c r="I1628">
+        <v>25</v>
+      </c>
+      <c r="J1628" s="10">
+        <v>6.2205034722222226E-2</v>
+      </c>
+      <c r="K1628" s="11">
+        <v>8.5525462962962975E-4</v>
       </c>
     </row>
     <row r="1629" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1629" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1629">
+        <v>19</v>
+      </c>
       <c r="E1629" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1629" t="s">
-        <v>37</v>
+        <v>176</v>
+      </c>
+      <c r="F1629" t="s">
+        <v>32</v>
+      </c>
+      <c r="G1629" t="str">
+        <f t="shared" si="4"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1629">
+        <v>2</v>
+      </c>
+      <c r="I1629">
+        <v>18</v>
+      </c>
+      <c r="J1629" s="10">
+        <v>6.2239259259259258E-2</v>
+      </c>
+      <c r="K1629" s="11">
+        <v>8.4116898148148137E-4</v>
       </c>
     </row>
     <row r="1630" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1630" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1630">
+        <v>19</v>
+      </c>
       <c r="E1630" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1630" t="s">
-        <v>37</v>
+        <v>176</v>
+      </c>
+      <c r="F1630" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1630" t="str">
+        <f t="shared" si="4"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1630">
+        <v>3</v>
+      </c>
+      <c r="I1630">
+        <v>15</v>
+      </c>
+      <c r="J1630" s="10">
+        <v>6.251797453703703E-2</v>
+      </c>
+      <c r="K1630" s="11">
+        <v>8.5622685185185183E-4</v>
       </c>
     </row>
     <row r="1631" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1631" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1631">
+        <v>19</v>
+      </c>
       <c r="E1631" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1631" t="s">
-        <v>37</v>
+        <v>176</v>
+      </c>
+      <c r="F1631" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1631" t="str">
+        <f t="shared" si="4"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1631">
+        <v>4</v>
+      </c>
+      <c r="I1631">
+        <v>12</v>
+      </c>
+      <c r="J1631" s="10">
+        <v>6.279717592592593E-2</v>
+      </c>
+      <c r="K1631" s="11">
+        <v>8.6243055555555552E-4</v>
       </c>
     </row>
     <row r="1632" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1632" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1632">
+        <v>19</v>
+      </c>
       <c r="E1632" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1632" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1633" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1632" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1632" t="str">
+        <f t="shared" si="4"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1632">
+        <v>5</v>
+      </c>
+      <c r="I1632">
+        <v>10</v>
+      </c>
+      <c r="J1632" s="10">
+        <v>6.2855196759259269E-2</v>
+      </c>
+      <c r="K1632" s="11">
+        <v>8.5746527777777785E-4</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1633" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1633">
+        <v>19</v>
+      </c>
       <c r="E1633" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1633" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1634" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1633" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1633" t="str">
+        <f t="shared" si="4"/>
+        <v>Red Bull</v>
+      </c>
+      <c r="H1633">
+        <v>6</v>
+      </c>
+      <c r="I1633">
+        <v>8</v>
+      </c>
+      <c r="J1633" s="10">
+        <v>6.292738425925927E-2</v>
+      </c>
+      <c r="K1633" s="11">
+        <v>8.5505787037037028E-4</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1634" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1634">
+        <v>19</v>
+      </c>
       <c r="E1634" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1634" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1635" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1634" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1634" t="str">
+        <f t="shared" si="4"/>
+        <v>Mercedes</v>
+      </c>
+      <c r="H1634">
+        <v>7</v>
+      </c>
+      <c r="I1634">
+        <v>6</v>
+      </c>
+      <c r="J1634" s="10">
+        <v>6.2972372685185185E-2</v>
+      </c>
+      <c r="K1634" s="11">
+        <v>8.6474537037037032E-4</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1635" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1635">
+        <v>19</v>
+      </c>
       <c r="E1635" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1635" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1636" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1635" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1635" t="str">
+        <f t="shared" si="4"/>
+        <v>Ferrari</v>
+      </c>
+      <c r="H1635">
+        <v>8</v>
+      </c>
+      <c r="I1635">
+        <v>4</v>
+      </c>
+      <c r="J1635" s="10">
+        <v>6.2206770833333334E-2</v>
+      </c>
+      <c r="K1635" s="11">
+        <v>8.6629629629629632E-4</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1636" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1636">
+        <v>19</v>
+      </c>
       <c r="E1636" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1636" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1637" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1636" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1636" t="str">
+        <f t="shared" si="4"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1636">
+        <v>9</v>
+      </c>
+      <c r="I1636">
+        <v>2</v>
+      </c>
+      <c r="J1636" s="10">
+        <v>6.2209085648148144E-2</v>
+      </c>
+      <c r="K1636" s="11">
+        <v>8.5674768518518511E-4</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1637" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1637">
+        <v>19</v>
+      </c>
       <c r="E1637" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1637" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1638" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1637" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1637" t="str">
+        <f t="shared" si="4"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1637">
+        <v>10</v>
+      </c>
+      <c r="I1637">
+        <v>1</v>
+      </c>
+      <c r="J1637" s="10">
+        <v>6.2212835648148154E-2</v>
+      </c>
+      <c r="K1637" s="11">
+        <v>8.6275462962962966E-4</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1638" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1638">
+        <v>19</v>
+      </c>
       <c r="E1638" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1638" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1639" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1638" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1638" t="str">
+        <f t="shared" si="4"/>
+        <v>McLaren</v>
+      </c>
+      <c r="H1638">
+        <v>11</v>
+      </c>
+      <c r="I1638">
+        <v>0</v>
+      </c>
+      <c r="J1638" s="10">
+        <v>6.2343449074074075E-2</v>
+      </c>
+      <c r="K1638" s="11">
+        <v>8.6203703703703713E-4</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1639" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1639">
+        <v>19</v>
+      </c>
       <c r="E1639" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1639" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1640" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1639" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1639" t="str">
+        <f t="shared" si="4"/>
+        <v>Alpine</v>
+      </c>
+      <c r="H1639">
+        <v>12</v>
+      </c>
+      <c r="I1639">
+        <v>0</v>
+      </c>
+      <c r="J1639" s="10">
+        <v>6.2444259259259262E-2</v>
+      </c>
+      <c r="K1639" s="11">
+        <v>8.6327546296296304E-4</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1640" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1640">
+        <v>19</v>
+      </c>
       <c r="E1640" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1640" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1641" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1640" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1640" t="str">
+        <f t="shared" si="4"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1640">
+        <v>13</v>
+      </c>
+      <c r="I1640">
+        <v>0</v>
+      </c>
+      <c r="J1640" s="10">
+        <v>6.2473437499999999E-2</v>
+      </c>
+      <c r="K1640" s="11">
+        <v>8.6774305555555552E-4</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1641" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1641">
+        <v>19</v>
+      </c>
       <c r="E1641" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1641" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1642" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1641" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1641" t="str">
+        <f t="shared" si="4"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1641">
+        <v>14</v>
+      </c>
+      <c r="I1641">
+        <v>0</v>
+      </c>
+      <c r="J1641" s="10">
+        <v>6.2493437499999999E-2</v>
+      </c>
+      <c r="K1641" s="11">
+        <v>8.6796296296296307E-4</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1642" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1642">
+        <v>19</v>
+      </c>
       <c r="E1642" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1642" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1643" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1642" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1642" t="str">
+        <f t="shared" si="4"/>
+        <v>Williams</v>
+      </c>
+      <c r="H1642">
+        <v>15</v>
+      </c>
+      <c r="I1642">
+        <v>0</v>
+      </c>
+      <c r="J1642" s="10">
+        <v>6.2520879629629628E-2</v>
+      </c>
+      <c r="K1642" s="11">
+        <v>8.6412037037037035E-4</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1643" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1643">
+        <v>19</v>
+      </c>
       <c r="E1643" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1643" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1644" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1643" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1643" t="str">
+        <f t="shared" si="4"/>
+        <v>Haas</v>
+      </c>
+      <c r="H1643">
+        <v>16</v>
+      </c>
+      <c r="I1643">
+        <v>0</v>
+      </c>
+      <c r="J1643" s="10">
+        <v>6.265545138888888E-2</v>
+      </c>
+      <c r="K1643" s="11">
+        <v>8.6387731481481472E-4</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1644" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1644">
+        <v>19</v>
+      </c>
       <c r="E1644" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1644" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1645" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1644" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1644" t="str">
+        <f t="shared" si="4"/>
+        <v>Kick Sauber</v>
+      </c>
+      <c r="H1644">
+        <v>17</v>
+      </c>
+      <c r="I1644">
+        <v>0</v>
+      </c>
+      <c r="J1644" s="10">
+        <v>6.2667418981481482E-2</v>
+      </c>
+      <c r="K1644" s="11">
+        <v>8.7114583333333326E-4</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1645" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1645">
+        <v>19</v>
+      </c>
       <c r="E1645" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1645" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1646" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1645" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1645" t="str">
+        <f t="shared" si="4"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1645">
+        <v>18</v>
+      </c>
+      <c r="I1645">
+        <v>0</v>
+      </c>
+      <c r="J1645" s="10">
+        <v>6.3050497685185183E-2</v>
+      </c>
+      <c r="K1645" s="11">
+        <v>8.6414351851851854E-4</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1646" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1646">
+        <v>19</v>
+      </c>
       <c r="E1646" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1646" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1647" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1646" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1646" t="str">
+        <f t="shared" si="4"/>
+        <v>Racing Bulls</v>
+      </c>
+      <c r="H1646">
+        <v>19</v>
+      </c>
+      <c r="I1646">
+        <v>0</v>
+      </c>
+      <c r="J1646" s="10">
+        <v>6.2324502314814817E-2</v>
+      </c>
+      <c r="K1646" s="11">
+        <v>8.7724537037037035E-4</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A1647" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>109</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1647">
+        <v>19</v>
+      </c>
       <c r="E1647" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1647" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="1648" spans="5:9" x14ac:dyDescent="0.45">
+        <v>176</v>
+      </c>
+      <c r="F1647" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1647" t="str">
+        <f t="shared" si="4"/>
+        <v>Aston Martin</v>
+      </c>
+      <c r="H1647">
+        <v>20</v>
+      </c>
+      <c r="I1647">
+        <v>0</v>
+      </c>
+      <c r="J1647" s="10">
+        <v>6.2613599537037032E-2</v>
+      </c>
+      <c r="K1647" s="11">
+        <v>8.7168981481481472E-4</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:11" x14ac:dyDescent="0.45">
       <c r="E1648" t="s">
         <v>37</v>
       </c>
       <c r="I1648" t="s">
         <v>37</v>
       </c>
+      <c r="J1648" s="10"/>
+      <c r="K1648" s="11"/>
     </row>
     <row r="1649" spans="5:9" x14ac:dyDescent="0.45">
       <c r="E1649" t="s">
@@ -93566,17 +94128,17 @@
         <v>46194</v>
       </c>
       <c r="D20" t="s">
-        <v>117</v>
+        <v>176</v>
       </c>
       <c r="E20" t="str">
-        <f t="shared" si="3"/>
-        <v>Shanghai International Circuit</v>
+        <f t="shared" ref="E20:E21" si="5">VLOOKUP(D20,$K$1:$L$33,2,FALSE)</f>
+        <v>Autódromo José Carlos Pace (Interlagos)</v>
       </c>
       <c r="F20" t="s">
         <v>196</v>
       </c>
       <c r="G20" s="12">
-        <v>0.25</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="K20" t="s">
         <v>174</v>
@@ -93598,11 +94160,11 @@
         <v>46201</v>
       </c>
       <c r="D21" t="s">
-        <v>176</v>
+        <v>117</v>
       </c>
       <c r="E21" t="str">
-        <f t="shared" si="3"/>
-        <v>Autódromo José Carlos Pace (Interlagos)</v>
+        <f t="shared" si="5"/>
+        <v>Shanghai International Circuit</v>
       </c>
       <c r="F21" t="s">
         <v>196</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="483" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C987267-BC6E-4CE3-A21A-329597F81EA5}"/>
+  <xr:revisionPtr revIDLastSave="484" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C72B57-EDA8-4BB6-900A-D30F28944705}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -94170,7 +94170,7 @@
         <v>196</v>
       </c>
       <c r="G21" s="12">
-        <v>0.25</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="K21" t="s">
         <v>20</v>
@@ -94202,7 +94202,7 @@
         <v>196</v>
       </c>
       <c r="G22" s="12">
-        <v>0.25</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="K22" t="s">
         <v>124</v>
@@ -94234,7 +94234,7 @@
         <v>196</v>
       </c>
       <c r="G23" s="12">
-        <v>0.25</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="K23" t="s">
         <v>123</v>
@@ -94266,7 +94266,7 @@
         <v>196</v>
       </c>
       <c r="G24" s="12">
-        <v>0.25</v>
+        <v>0.27083333333333331</v>
       </c>
       <c r="K24" t="s">
         <v>121</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/MyTrainings/MyAntiGravityProjects/F1gameDashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="484" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6C72B57-EDA8-4BB6-900A-D30F28944705}"/>
+  <xr:revisionPtr revIDLastSave="485" documentId="13_ncr:1_{546CA201-7B2D-4523-9F6A-9ED9E409A803}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF1EBED7-E07E-40AE-B939-334F37601B4E}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="10" r:id="rId1"/>
@@ -94135,7 +94135,7 @@
         <v>Autódromo José Carlos Pace (Interlagos)</v>
       </c>
       <c r="F20" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G20" s="12">
         <v>0.27083333333333331</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -60892,11 +60892,59 @@
       </c>
     </row>
     <row r="1780" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1780" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1780" t="s">
-        <v>37</v>
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1780">
+        <v>5</v>
+      </c>
+      <c r="E1780" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1780" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1780" t="inlineStr">
+        <is>
+          <t>TomasRodri21</t>
+        </is>
+      </c>
+      <c r="H1780" t="inlineStr">
+        <is>
+          <t>McLaren</t>
+        </is>
+      </c>
+      <c r="I1780">
+        <v>1</v>
+      </c>
+      <c r="J1780">
+        <v>25</v>
+      </c>
+      <c r="K1780" t="inlineStr">
+        <is>
+          <t>83:34.419</t>
+        </is>
+      </c>
+      <c r="L1780" t="inlineStr">
+        <is>
+          <t>1:22.018</t>
+        </is>
       </c>
       <c r="O1780" t="s">
         <v>35</v>
@@ -60906,11 +60954,59 @@
       </c>
     </row>
     <row r="1781" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1781" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1781" t="s">
-        <v>37</v>
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1781">
+        <v>5</v>
+      </c>
+      <c r="E1781" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1781" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1781" t="inlineStr">
+        <is>
+          <t>Charles Leclerc</t>
+        </is>
+      </c>
+      <c r="H1781" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="I1781">
+        <v>2</v>
+      </c>
+      <c r="J1781">
+        <v>18</v>
+      </c>
+      <c r="K1781" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1781" t="inlineStr">
+        <is>
+          <t>1:24.710</t>
+        </is>
       </c>
       <c r="O1781" t="s">
         <v>6</v>
@@ -60920,11 +61016,59 @@
       </c>
     </row>
     <row r="1782" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1782" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1782" t="s">
-        <v>37</v>
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1782">
+        <v>5</v>
+      </c>
+      <c r="E1782" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1782" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1782" t="inlineStr">
+        <is>
+          <t>Kimi Antonelli</t>
+        </is>
+      </c>
+      <c r="H1782" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="I1782">
+        <v>3</v>
+      </c>
+      <c r="J1782">
+        <v>15</v>
+      </c>
+      <c r="K1782" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1782" t="inlineStr">
+        <is>
+          <t>1:24.875</t>
+        </is>
       </c>
       <c r="O1782" t="s">
         <v>10</v>
@@ -60934,11 +61078,59 @@
       </c>
     </row>
     <row r="1783" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1783" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1783" t="s">
-        <v>37</v>
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1783">
+        <v>5</v>
+      </c>
+      <c r="E1783" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1783" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1783" t="inlineStr">
+        <is>
+          <t>Lando Norris</t>
+        </is>
+      </c>
+      <c r="H1783" t="inlineStr">
+        <is>
+          <t>McLaren</t>
+        </is>
+      </c>
+      <c r="I1783">
+        <v>4</v>
+      </c>
+      <c r="J1783">
+        <v>12</v>
+      </c>
+      <c r="K1783" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1783" t="inlineStr">
+        <is>
+          <t>1:25.579</t>
+        </is>
       </c>
       <c r="O1783" t="s">
         <v>79</v>
@@ -60948,11 +61140,59 @@
       </c>
     </row>
     <row r="1784" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1784" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1784" t="s">
-        <v>37</v>
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1784">
+        <v>5</v>
+      </c>
+      <c r="E1784" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1784" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>Lewis Hamilton</t>
+        </is>
+      </c>
+      <c r="H1784" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="I1784">
+        <v>5</v>
+      </c>
+      <c r="J1784">
+        <v>10</v>
+      </c>
+      <c r="K1784" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1784" t="inlineStr">
+        <is>
+          <t>1:25.103</t>
+        </is>
       </c>
       <c r="O1784" t="s">
         <v>55</v>
@@ -60962,11 +61202,59 @@
       </c>
     </row>
     <row r="1785" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1785" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1785" t="s">
-        <v>37</v>
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1785">
+        <v>5</v>
+      </c>
+      <c r="E1785" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1785" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1785" t="inlineStr">
+        <is>
+          <t>Alexander Albon</t>
+        </is>
+      </c>
+      <c r="H1785" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="I1785">
+        <v>6</v>
+      </c>
+      <c r="J1785">
+        <v>8</v>
+      </c>
+      <c r="K1785" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1785" t="inlineStr">
+        <is>
+          <t>1:25.726</t>
+        </is>
       </c>
       <c r="O1785" t="s">
         <v>11</v>
@@ -60976,131 +61264,899 @@
       </c>
     </row>
     <row r="1786" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1786" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1786" t="s">
-        <v>37</v>
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1786">
+        <v>5</v>
+      </c>
+      <c r="E1786" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1786" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1786" t="inlineStr">
+        <is>
+          <t>Carlos Sainz Jr.</t>
+        </is>
+      </c>
+      <c r="H1786" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="I1786">
+        <v>7</v>
+      </c>
+      <c r="J1786">
+        <v>6</v>
+      </c>
+      <c r="K1786" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1786" t="inlineStr">
+        <is>
+          <t>1:26.150</t>
+        </is>
       </c>
     </row>
     <row r="1787" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1787" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1787" t="s">
-        <v>37</v>
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1787">
+        <v>5</v>
+      </c>
+      <c r="E1787" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1787" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1787" t="inlineStr">
+        <is>
+          <t>Pierre Gasly</t>
+        </is>
+      </c>
+      <c r="H1787" t="inlineStr">
+        <is>
+          <t>Alpine</t>
+        </is>
+      </c>
+      <c r="I1787">
+        <v>8</v>
+      </c>
+      <c r="J1787">
+        <v>4</v>
+      </c>
+      <c r="K1787" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1787" t="inlineStr">
+        <is>
+          <t>1:26.089</t>
+        </is>
       </c>
     </row>
     <row r="1788" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1788" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1788" t="s">
-        <v>37</v>
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1788">
+        <v>5</v>
+      </c>
+      <c r="E1788" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1788" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1788" t="inlineStr">
+        <is>
+          <t>Fernando Alonso</t>
+        </is>
+      </c>
+      <c r="H1788" t="inlineStr">
+        <is>
+          <t>Aston Martin</t>
+        </is>
+      </c>
+      <c r="I1788">
+        <v>9</v>
+      </c>
+      <c r="J1788">
+        <v>2</v>
+      </c>
+      <c r="K1788" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1788" t="inlineStr">
+        <is>
+          <t>1:26.614</t>
+        </is>
       </c>
     </row>
     <row r="1789" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1789" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1789" t="s">
-        <v>37</v>
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1789">
+        <v>5</v>
+      </c>
+      <c r="E1789" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1789" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>Nico Hülkenberg</t>
+        </is>
+      </c>
+      <c r="H1789" t="inlineStr">
+        <is>
+          <t>Audi</t>
+        </is>
+      </c>
+      <c r="I1789">
+        <v>10</v>
+      </c>
+      <c r="J1789">
+        <v>1</v>
+      </c>
+      <c r="K1789" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1789" t="inlineStr">
+        <is>
+          <t>1:26.857</t>
+        </is>
       </c>
     </row>
     <row r="1790" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1790" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1790" t="s">
-        <v>37</v>
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1790">
+        <v>5</v>
+      </c>
+      <c r="E1790" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1790" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1790" t="inlineStr">
+        <is>
+          <t>Arvid Lidblad</t>
+        </is>
+      </c>
+      <c r="H1790" t="inlineStr">
+        <is>
+          <t>Racing Bulls</t>
+        </is>
+      </c>
+      <c r="I1790">
+        <v>11</v>
+      </c>
+      <c r="J1790">
+        <v>0</v>
+      </c>
+      <c r="K1790" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1790" t="inlineStr">
+        <is>
+          <t>1:26.706</t>
+        </is>
       </c>
     </row>
     <row r="1791" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1791" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1791" t="s">
-        <v>37</v>
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1791">
+        <v>5</v>
+      </c>
+      <c r="E1791" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1791" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1791" t="inlineStr">
+        <is>
+          <t>Oliver Bearman</t>
+        </is>
+      </c>
+      <c r="H1791" t="inlineStr">
+        <is>
+          <t>Haas</t>
+        </is>
+      </c>
+      <c r="I1791">
+        <v>12</v>
+      </c>
+      <c r="J1791">
+        <v>0</v>
+      </c>
+      <c r="K1791" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1791" t="inlineStr">
+        <is>
+          <t>1:26.658</t>
+        </is>
       </c>
     </row>
     <row r="1792" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="F1792" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1792" t="s">
-        <v>37</v>
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1792">
+        <v>5</v>
+      </c>
+      <c r="E1792" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1792" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1792" t="inlineStr">
+        <is>
+          <t>Sergio Perez</t>
+        </is>
+      </c>
+      <c r="H1792" t="inlineStr">
+        <is>
+          <t>Cadillac</t>
+        </is>
+      </c>
+      <c r="I1792">
+        <v>13</v>
+      </c>
+      <c r="J1792">
+        <v>0</v>
+      </c>
+      <c r="K1792" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1792" t="inlineStr">
+        <is>
+          <t>1:25.731</t>
+        </is>
       </c>
     </row>
     <row r="1793" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1793" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1793" t="s">
-        <v>37</v>
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1793">
+        <v>5</v>
+      </c>
+      <c r="E1793" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1793" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1793" t="inlineStr">
+        <is>
+          <t>Esteban Ocon</t>
+        </is>
+      </c>
+      <c r="H1793" t="inlineStr">
+        <is>
+          <t>Haas</t>
+        </is>
+      </c>
+      <c r="I1793">
+        <v>14</v>
+      </c>
+      <c r="J1793">
+        <v>0</v>
+      </c>
+      <c r="K1793" t="inlineStr">
+        <is>
+          <t>+2 Laps</t>
+        </is>
+      </c>
+      <c r="L1793" t="inlineStr">
+        <is>
+          <t>1:25.800</t>
+        </is>
       </c>
     </row>
     <row r="1794" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1794" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1794" t="s">
-        <v>37</v>
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1794">
+        <v>5</v>
+      </c>
+      <c r="E1794" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1794" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1794" t="inlineStr">
+        <is>
+          <t>Valtteri Bottas</t>
+        </is>
+      </c>
+      <c r="H1794" t="inlineStr">
+        <is>
+          <t>Cadillac</t>
+        </is>
+      </c>
+      <c r="I1794">
+        <v>15</v>
+      </c>
+      <c r="J1794">
+        <v>0</v>
+      </c>
+      <c r="K1794" t="inlineStr">
+        <is>
+          <t>+2 Laps</t>
+        </is>
+      </c>
+      <c r="L1794" t="inlineStr">
+        <is>
+          <t>1:26.235</t>
+        </is>
       </c>
     </row>
     <row r="1795" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1795" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1795" t="s">
-        <v>37</v>
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1795">
+        <v>5</v>
+      </c>
+      <c r="E1795" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1795" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1795" t="inlineStr">
+        <is>
+          <t>Franco Colapinto</t>
+        </is>
+      </c>
+      <c r="H1795" t="inlineStr">
+        <is>
+          <t>Alpine</t>
+        </is>
+      </c>
+      <c r="I1795">
+        <v>16</v>
+      </c>
+      <c r="J1795">
+        <v>0</v>
+      </c>
+      <c r="K1795" t="inlineStr">
+        <is>
+          <t>+2 Laps</t>
+        </is>
+      </c>
+      <c r="L1795" t="inlineStr">
+        <is>
+          <t>1:27.023</t>
+        </is>
       </c>
     </row>
     <row r="1796" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1796" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1796" t="s">
-        <v>37</v>
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1796">
+        <v>5</v>
+      </c>
+      <c r="E1796" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1796" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>Liam Lawson</t>
+        </is>
+      </c>
+      <c r="H1796" t="inlineStr">
+        <is>
+          <t>Racing Bulls</t>
+        </is>
+      </c>
+      <c r="I1796">
+        <v>17</v>
+      </c>
+      <c r="J1796">
+        <v>0</v>
+      </c>
+      <c r="K1796" t="inlineStr">
+        <is>
+          <t>+2 Laps</t>
+        </is>
+      </c>
+      <c r="L1796" t="inlineStr">
+        <is>
+          <t>1:26.206</t>
+        </is>
       </c>
     </row>
     <row r="1797" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1797" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1797" t="s">
-        <v>37</v>
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1797">
+        <v>5</v>
+      </c>
+      <c r="E1797" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1797" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1797" t="inlineStr">
+        <is>
+          <t>Lance Stroll</t>
+        </is>
+      </c>
+      <c r="H1797" t="inlineStr">
+        <is>
+          <t>Aston Martin</t>
+        </is>
+      </c>
+      <c r="I1797">
+        <v>18</v>
+      </c>
+      <c r="J1797">
+        <v>0</v>
+      </c>
+      <c r="K1797" t="inlineStr">
+        <is>
+          <t>+2 Laps</t>
+        </is>
+      </c>
+      <c r="L1797" t="inlineStr">
+        <is>
+          <t>1:27.388</t>
+        </is>
       </c>
     </row>
     <row r="1798" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1798" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1798" t="s">
-        <v>37</v>
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1798">
+        <v>5</v>
+      </c>
+      <c r="E1798" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1798" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1798" t="inlineStr">
+        <is>
+          <t>Fatacuida</t>
+        </is>
+      </c>
+      <c r="H1798" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="I1798">
+        <v>19</v>
+      </c>
+      <c r="J1798">
+        <v>0</v>
+      </c>
+      <c r="K1798" t="inlineStr">
+        <is>
+          <t>+6 Laps</t>
+        </is>
+      </c>
+      <c r="L1798" t="inlineStr">
+        <is>
+          <t>1:22.970</t>
+        </is>
       </c>
     </row>
     <row r="1799" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1799" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1799" t="s">
-        <v>37</v>
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1799">
+        <v>5</v>
+      </c>
+      <c r="E1799" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1799" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>Gabriel Bortoleto</t>
+        </is>
+      </c>
+      <c r="H1799" t="inlineStr">
+        <is>
+          <t>Audi</t>
+        </is>
+      </c>
+      <c r="I1799">
+        <v>20</v>
+      </c>
+      <c r="J1799">
+        <v>0</v>
+      </c>
+      <c r="K1799" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1799" t="inlineStr">
+        <is>
+          <t>1:26.621</t>
+        </is>
       </c>
     </row>
     <row r="1800" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1800" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1800" t="s">
-        <v>37</v>
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1800">
+        <v>5</v>
+      </c>
+      <c r="E1800" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1800" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1800" t="inlineStr">
+        <is>
+          <t>Max Verstappen</t>
+        </is>
+      </c>
+      <c r="H1800" t="inlineStr">
+        <is>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="I1800">
+        <v>21</v>
+      </c>
+      <c r="J1800">
+        <v>0</v>
+      </c>
+      <c r="K1800" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1800" t="inlineStr">
+        <is>
+          <t>1:25.731</t>
+        </is>
       </c>
     </row>
     <row r="1801" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1801" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1801" t="s">
-        <v>37</v>
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1801">
+        <v>5</v>
+      </c>
+      <c r="E1801" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1801" t="inlineStr">
+        <is>
+          <t>Australian GP</t>
+        </is>
+      </c>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>Polingua</t>
+        </is>
+      </c>
+      <c r="H1801" t="inlineStr">
+        <is>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="I1801">
+        <v>22</v>
+      </c>
+      <c r="J1801">
+        <v>0</v>
+      </c>
+      <c r="K1801" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1801" t="inlineStr">
+        <is>
+          <t>1:35.614</t>
+        </is>
       </c>
     </row>
     <row r="1802" spans="6:10" x14ac:dyDescent="0.45">
@@ -85622,8 +86678,10 @@
         <f t="shared" si="4"/>
         <v>Albert Park Circuit</v>
       </c>
-      <c r="F25" t="s">
-        <v>191</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="G25" s="11">
         <v>0.25</v>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/GitHub/f1-game-dashboard/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruiro\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:1_{424E60AC-F408-4D54-998B-C422FCFB6C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA6EAF35-995A-4E2B-B925-53ADD6A2FCA1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{165239E0-7DB1-4443-8D6D-AA08C95311DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19062" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19210" uniqueCount="431">
   <si>
     <t>Lewis Hamilton</t>
   </si>
@@ -1282,6 +1282,75 @@
   <si>
     <t>+1:09.705</t>
   </si>
+  <si>
+    <t>83:34.419</t>
+  </si>
+  <si>
+    <t>1:22.018</t>
+  </si>
+  <si>
+    <t>1:24.710</t>
+  </si>
+  <si>
+    <t>1:24.875</t>
+  </si>
+  <si>
+    <t>1:25.579</t>
+  </si>
+  <si>
+    <t>1:25.103</t>
+  </si>
+  <si>
+    <t>1:25.726</t>
+  </si>
+  <si>
+    <t>1:26.150</t>
+  </si>
+  <si>
+    <t>1:26.089</t>
+  </si>
+  <si>
+    <t>1:26.614</t>
+  </si>
+  <si>
+    <t>1:26.857</t>
+  </si>
+  <si>
+    <t>1:26.706</t>
+  </si>
+  <si>
+    <t>1:26.658</t>
+  </si>
+  <si>
+    <t>1:25.731</t>
+  </si>
+  <si>
+    <t>1:25.800</t>
+  </si>
+  <si>
+    <t>1:26.235</t>
+  </si>
+  <si>
+    <t>1:27.023</t>
+  </si>
+  <si>
+    <t>1:26.206</t>
+  </si>
+  <si>
+    <t>1:27.388</t>
+  </si>
+  <si>
+    <t>+6 Laps</t>
+  </si>
+  <si>
+    <t>1:22.970</t>
+  </si>
+  <si>
+    <t>1:26.621</t>
+  </si>
+  <si>
+    <t>1:35.614</t>
+  </si>
 </sst>
 </file>
 
@@ -60892,43 +60961,29 @@
       </c>
     </row>
     <row r="1780" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1780" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1780" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1780" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1780" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>205</v>
       </c>
       <c r="D1780">
         <v>5</v>
       </c>
-      <c r="E1780" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1780" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1780" t="inlineStr">
-        <is>
-          <t>TomasRodri21</t>
-        </is>
-      </c>
-      <c r="H1780" t="inlineStr">
-        <is>
-          <t>McLaren</t>
-        </is>
+      <c r="E1780" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1780" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1780" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1780" t="s">
+        <v>143</v>
       </c>
       <c r="I1780">
         <v>1</v>
@@ -60936,15 +60991,11 @@
       <c r="J1780">
         <v>25</v>
       </c>
-      <c r="K1780" t="inlineStr">
-        <is>
-          <t>83:34.419</t>
-        </is>
-      </c>
-      <c r="L1780" t="inlineStr">
-        <is>
-          <t>1:22.018</t>
-        </is>
+      <c r="K1780" t="s">
+        <v>408</v>
+      </c>
+      <c r="L1780" t="s">
+        <v>409</v>
       </c>
       <c r="O1780" t="s">
         <v>35</v>
@@ -60954,43 +61005,29 @@
       </c>
     </row>
     <row r="1781" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1781" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1781" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1781" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1781" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>205</v>
       </c>
       <c r="D1781">
         <v>5</v>
       </c>
-      <c r="E1781" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1781" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1781" t="inlineStr">
-        <is>
-          <t>Charles Leclerc</t>
-        </is>
-      </c>
-      <c r="H1781" t="inlineStr">
-        <is>
-          <t>Ferrari</t>
-        </is>
+      <c r="E1781" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1781" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1781" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1781" t="s">
+        <v>138</v>
       </c>
       <c r="I1781">
         <v>2</v>
@@ -60998,15 +61035,11 @@
       <c r="J1781">
         <v>18</v>
       </c>
-      <c r="K1781" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1781" t="inlineStr">
-        <is>
-          <t>1:24.710</t>
-        </is>
+      <c r="K1781" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1781" t="s">
+        <v>410</v>
       </c>
       <c r="O1781" t="s">
         <v>6</v>
@@ -61016,43 +61049,29 @@
       </c>
     </row>
     <row r="1782" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1782" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1782" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1782" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1782" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>205</v>
       </c>
       <c r="D1782">
         <v>5</v>
       </c>
-      <c r="E1782" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1782" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1782" t="inlineStr">
-        <is>
-          <t>Kimi Antonelli</t>
-        </is>
-      </c>
-      <c r="H1782" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
+      <c r="E1782" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1782" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1782" t="s">
+        <v>200</v>
+      </c>
+      <c r="H1782" t="s">
+        <v>134</v>
       </c>
       <c r="I1782">
         <v>3</v>
@@ -61060,15 +61079,11 @@
       <c r="J1782">
         <v>15</v>
       </c>
-      <c r="K1782" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1782" t="inlineStr">
-        <is>
-          <t>1:24.875</t>
-        </is>
+      <c r="K1782" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1782" t="s">
+        <v>411</v>
       </c>
       <c r="O1782" t="s">
         <v>10</v>
@@ -61078,43 +61093,29 @@
       </c>
     </row>
     <row r="1783" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1783" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1783" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1783" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1783" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>205</v>
       </c>
       <c r="D1783">
         <v>5</v>
       </c>
-      <c r="E1783" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1783" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1783" t="inlineStr">
-        <is>
-          <t>Lando Norris</t>
-        </is>
-      </c>
-      <c r="H1783" t="inlineStr">
-        <is>
-          <t>McLaren</t>
-        </is>
+      <c r="E1783" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1783" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1783" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1783" t="s">
+        <v>143</v>
       </c>
       <c r="I1783">
         <v>4</v>
@@ -61122,15 +61123,11 @@
       <c r="J1783">
         <v>12</v>
       </c>
-      <c r="K1783" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1783" t="inlineStr">
-        <is>
-          <t>1:25.579</t>
-        </is>
+      <c r="K1783" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1783" t="s">
+        <v>412</v>
       </c>
       <c r="O1783" t="s">
         <v>79</v>
@@ -61140,43 +61137,29 @@
       </c>
     </row>
     <row r="1784" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1784" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1784" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1784" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1784" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>205</v>
       </c>
       <c r="D1784">
         <v>5</v>
       </c>
-      <c r="E1784" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1784" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1784" t="inlineStr">
-        <is>
-          <t>Lewis Hamilton</t>
-        </is>
-      </c>
-      <c r="H1784" t="inlineStr">
-        <is>
-          <t>Ferrari</t>
-        </is>
+      <c r="E1784" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1784" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1784" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1784" t="s">
+        <v>138</v>
       </c>
       <c r="I1784">
         <v>5</v>
@@ -61184,15 +61167,11 @@
       <c r="J1784">
         <v>10</v>
       </c>
-      <c r="K1784" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1784" t="inlineStr">
-        <is>
-          <t>1:25.103</t>
-        </is>
+      <c r="K1784" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1784" t="s">
+        <v>413</v>
       </c>
       <c r="O1784" t="s">
         <v>55</v>
@@ -61202,43 +61181,29 @@
       </c>
     </row>
     <row r="1785" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1785" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1785" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1785" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1785" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>205</v>
       </c>
       <c r="D1785">
         <v>5</v>
       </c>
-      <c r="E1785" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1785" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1785" t="inlineStr">
-        <is>
-          <t>Alexander Albon</t>
-        </is>
-      </c>
-      <c r="H1785" t="inlineStr">
-        <is>
-          <t>Williams</t>
-        </is>
+      <c r="E1785" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1785" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1785" t="s">
+        <v>12</v>
+      </c>
+      <c r="H1785" t="s">
+        <v>139</v>
       </c>
       <c r="I1785">
         <v>6</v>
@@ -61246,15 +61211,11 @@
       <c r="J1785">
         <v>8</v>
       </c>
-      <c r="K1785" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1785" t="inlineStr">
-        <is>
-          <t>1:25.726</t>
-        </is>
+      <c r="K1785" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1785" t="s">
+        <v>414</v>
       </c>
       <c r="O1785" t="s">
         <v>11</v>
@@ -61264,43 +61225,29 @@
       </c>
     </row>
     <row r="1786" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1786" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1786" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1786" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1786" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>205</v>
       </c>
       <c r="D1786">
         <v>5</v>
       </c>
-      <c r="E1786" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1786" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1786" t="inlineStr">
-        <is>
-          <t>Carlos Sainz Jr.</t>
-        </is>
-      </c>
-      <c r="H1786" t="inlineStr">
-        <is>
-          <t>Williams</t>
-        </is>
+      <c r="E1786" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1786" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1786" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1786" t="s">
+        <v>139</v>
       </c>
       <c r="I1786">
         <v>7</v>
@@ -61308,55 +61255,37 @@
       <c r="J1786">
         <v>6</v>
       </c>
-      <c r="K1786" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1786" t="inlineStr">
-        <is>
-          <t>1:26.150</t>
-        </is>
+      <c r="K1786" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1786" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="1787" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1787" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1787" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1787" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1787" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1787" t="s">
+        <v>205</v>
       </c>
       <c r="D1787">
         <v>5</v>
       </c>
-      <c r="E1787" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1787" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1787" t="inlineStr">
-        <is>
-          <t>Pierre Gasly</t>
-        </is>
-      </c>
-      <c r="H1787" t="inlineStr">
-        <is>
-          <t>Alpine</t>
-        </is>
+      <c r="E1787" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1787" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1787" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1787" t="s">
+        <v>140</v>
       </c>
       <c r="I1787">
         <v>8</v>
@@ -61364,55 +61293,37 @@
       <c r="J1787">
         <v>4</v>
       </c>
-      <c r="K1787" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1787" t="inlineStr">
-        <is>
-          <t>1:26.089</t>
-        </is>
+      <c r="K1787" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1787" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="1788" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1788" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1788" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1788" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1788" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1788" t="s">
+        <v>205</v>
       </c>
       <c r="D1788">
         <v>5</v>
       </c>
-      <c r="E1788" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1788" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1788" t="inlineStr">
-        <is>
-          <t>Fernando Alonso</t>
-        </is>
-      </c>
-      <c r="H1788" t="inlineStr">
-        <is>
-          <t>Aston Martin</t>
-        </is>
+      <c r="E1788" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1788" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1788" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1788" t="s">
+        <v>133</v>
       </c>
       <c r="I1788">
         <v>9</v>
@@ -61420,55 +61331,37 @@
       <c r="J1788">
         <v>2</v>
       </c>
-      <c r="K1788" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1788" t="inlineStr">
-        <is>
-          <t>1:26.614</t>
-        </is>
+      <c r="K1788" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1788" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="1789" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1789" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1789" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1789" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1789" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1789" t="s">
+        <v>205</v>
       </c>
       <c r="D1789">
         <v>5</v>
       </c>
-      <c r="E1789" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1789" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1789" t="inlineStr">
-        <is>
-          <t>Nico Hülkenberg</t>
-        </is>
-      </c>
-      <c r="H1789" t="inlineStr">
-        <is>
-          <t>Audi</t>
-        </is>
+      <c r="E1789" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1789" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1789" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1789" t="s">
+        <v>198</v>
       </c>
       <c r="I1789">
         <v>10</v>
@@ -61476,55 +61369,37 @@
       <c r="J1789">
         <v>1</v>
       </c>
-      <c r="K1789" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1789" t="inlineStr">
-        <is>
-          <t>1:26.857</t>
-        </is>
+      <c r="K1789" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1789" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="1790" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1790" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1790" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1790" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1790" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>205</v>
       </c>
       <c r="D1790">
         <v>5</v>
       </c>
-      <c r="E1790" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1790" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1790" t="inlineStr">
-        <is>
-          <t>Arvid Lidblad</t>
-        </is>
-      </c>
-      <c r="H1790" t="inlineStr">
-        <is>
-          <t>Racing Bulls</t>
-        </is>
+      <c r="E1790" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1790" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1790" t="s">
+        <v>202</v>
+      </c>
+      <c r="H1790" t="s">
+        <v>144</v>
       </c>
       <c r="I1790">
         <v>11</v>
@@ -61532,55 +61407,37 @@
       <c r="J1790">
         <v>0</v>
       </c>
-      <c r="K1790" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1790" t="inlineStr">
-        <is>
-          <t>1:26.706</t>
-        </is>
+      <c r="K1790" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1790" t="s">
+        <v>419</v>
       </c>
     </row>
     <row r="1791" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1791" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1791" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1791" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1791" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1791" t="s">
+        <v>205</v>
       </c>
       <c r="D1791">
         <v>5</v>
       </c>
-      <c r="E1791" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1791" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1791" t="inlineStr">
-        <is>
-          <t>Oliver Bearman</t>
-        </is>
-      </c>
-      <c r="H1791" t="inlineStr">
-        <is>
-          <t>Haas</t>
-        </is>
+      <c r="E1791" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1791" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1791" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1791" t="s">
+        <v>137</v>
       </c>
       <c r="I1791">
         <v>12</v>
@@ -61588,55 +61445,37 @@
       <c r="J1791">
         <v>0</v>
       </c>
-      <c r="K1791" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1791" t="inlineStr">
-        <is>
-          <t>1:26.658</t>
-        </is>
+      <c r="K1791" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1791" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="1792" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A1792" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1792" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1792" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="A1792" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1792" t="s">
+        <v>205</v>
       </c>
       <c r="D1792">
         <v>5</v>
       </c>
-      <c r="E1792" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1792" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1792" t="inlineStr">
-        <is>
-          <t>Sergio Perez</t>
-        </is>
-      </c>
-      <c r="H1792" t="inlineStr">
-        <is>
-          <t>Cadillac</t>
-        </is>
+      <c r="E1792" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1792" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1792" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1792" t="s">
+        <v>199</v>
       </c>
       <c r="I1792">
         <v>13</v>
@@ -61644,55 +61483,37 @@
       <c r="J1792">
         <v>0</v>
       </c>
-      <c r="K1792" t="inlineStr">
-        <is>
-          <t>+1 Lap</t>
-        </is>
-      </c>
-      <c r="L1792" t="inlineStr">
-        <is>
-          <t>1:25.731</t>
-        </is>
-      </c>
-    </row>
-    <row r="1793" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1793" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1793" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1793" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1792" t="s">
+        <v>237</v>
+      </c>
+      <c r="L1792" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1793" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1793" t="s">
+        <v>205</v>
       </c>
       <c r="D1793">
         <v>5</v>
       </c>
-      <c r="E1793" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1793" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1793" t="inlineStr">
-        <is>
-          <t>Esteban Ocon</t>
-        </is>
-      </c>
-      <c r="H1793" t="inlineStr">
-        <is>
-          <t>Haas</t>
-        </is>
+      <c r="E1793" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1793" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1793" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1793" t="s">
+        <v>137</v>
       </c>
       <c r="I1793">
         <v>14</v>
@@ -61700,55 +61521,37 @@
       <c r="J1793">
         <v>0</v>
       </c>
-      <c r="K1793" t="inlineStr">
-        <is>
-          <t>+2 Laps</t>
-        </is>
-      </c>
-      <c r="L1793" t="inlineStr">
-        <is>
-          <t>1:25.800</t>
-        </is>
-      </c>
-    </row>
-    <row r="1794" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1794" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1794" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1794" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1793" t="s">
+        <v>238</v>
+      </c>
+      <c r="L1793" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1794" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1794" t="s">
+        <v>205</v>
       </c>
       <c r="D1794">
         <v>5</v>
       </c>
-      <c r="E1794" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1794" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1794" t="inlineStr">
-        <is>
-          <t>Valtteri Bottas</t>
-        </is>
-      </c>
-      <c r="H1794" t="inlineStr">
-        <is>
-          <t>Cadillac</t>
-        </is>
+      <c r="E1794" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1794" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1794" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1794" t="s">
+        <v>199</v>
       </c>
       <c r="I1794">
         <v>15</v>
@@ -61756,55 +61559,37 @@
       <c r="J1794">
         <v>0</v>
       </c>
-      <c r="K1794" t="inlineStr">
-        <is>
-          <t>+2 Laps</t>
-        </is>
-      </c>
-      <c r="L1794" t="inlineStr">
-        <is>
-          <t>1:26.235</t>
-        </is>
-      </c>
-    </row>
-    <row r="1795" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1795" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1795" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1795" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1794" t="s">
+        <v>238</v>
+      </c>
+      <c r="L1794" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1795" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1795" t="s">
+        <v>205</v>
       </c>
       <c r="D1795">
         <v>5</v>
       </c>
-      <c r="E1795" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1795" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1795" t="inlineStr">
-        <is>
-          <t>Franco Colapinto</t>
-        </is>
-      </c>
-      <c r="H1795" t="inlineStr">
-        <is>
-          <t>Alpine</t>
-        </is>
+      <c r="E1795" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1795" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1795" t="s">
+        <v>201</v>
+      </c>
+      <c r="H1795" t="s">
+        <v>140</v>
       </c>
       <c r="I1795">
         <v>16</v>
@@ -61812,55 +61597,37 @@
       <c r="J1795">
         <v>0</v>
       </c>
-      <c r="K1795" t="inlineStr">
-        <is>
-          <t>+2 Laps</t>
-        </is>
-      </c>
-      <c r="L1795" t="inlineStr">
-        <is>
-          <t>1:27.023</t>
-        </is>
-      </c>
-    </row>
-    <row r="1796" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1796" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1796" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1796" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1795" t="s">
+        <v>238</v>
+      </c>
+      <c r="L1795" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1796" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1796" t="s">
+        <v>205</v>
       </c>
       <c r="D1796">
         <v>5</v>
       </c>
-      <c r="E1796" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1796" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1796" t="inlineStr">
-        <is>
-          <t>Liam Lawson</t>
-        </is>
-      </c>
-      <c r="H1796" t="inlineStr">
-        <is>
-          <t>Racing Bulls</t>
-        </is>
+      <c r="E1796" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1796" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1796" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1796" t="s">
+        <v>144</v>
       </c>
       <c r="I1796">
         <v>17</v>
@@ -61868,55 +61635,37 @@
       <c r="J1796">
         <v>0</v>
       </c>
-      <c r="K1796" t="inlineStr">
-        <is>
-          <t>+2 Laps</t>
-        </is>
-      </c>
-      <c r="L1796" t="inlineStr">
-        <is>
-          <t>1:26.206</t>
-        </is>
-      </c>
-    </row>
-    <row r="1797" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1797" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1797" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1797" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1796" t="s">
+        <v>238</v>
+      </c>
+      <c r="L1796" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1797" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1797" t="s">
+        <v>205</v>
       </c>
       <c r="D1797">
         <v>5</v>
       </c>
-      <c r="E1797" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1797" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1797" t="inlineStr">
-        <is>
-          <t>Lance Stroll</t>
-        </is>
-      </c>
-      <c r="H1797" t="inlineStr">
-        <is>
-          <t>Aston Martin</t>
-        </is>
+      <c r="E1797" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1797" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1797" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1797" t="s">
+        <v>133</v>
       </c>
       <c r="I1797">
         <v>18</v>
@@ -61924,55 +61673,37 @@
       <c r="J1797">
         <v>0</v>
       </c>
-      <c r="K1797" t="inlineStr">
-        <is>
-          <t>+2 Laps</t>
-        </is>
-      </c>
-      <c r="L1797" t="inlineStr">
-        <is>
-          <t>1:27.388</t>
-        </is>
-      </c>
-    </row>
-    <row r="1798" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1798" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1798" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1798" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1797" t="s">
+        <v>238</v>
+      </c>
+      <c r="L1797" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1798" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1798" t="s">
+        <v>205</v>
       </c>
       <c r="D1798">
         <v>5</v>
       </c>
-      <c r="E1798" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1798" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1798" t="inlineStr">
-        <is>
-          <t>Fatacuida</t>
-        </is>
-      </c>
-      <c r="H1798" t="inlineStr">
-        <is>
-          <t>Mercedes</t>
-        </is>
+      <c r="E1798" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1798" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1798" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1798" t="s">
+        <v>134</v>
       </c>
       <c r="I1798">
         <v>19</v>
@@ -61980,55 +61711,37 @@
       <c r="J1798">
         <v>0</v>
       </c>
-      <c r="K1798" t="inlineStr">
-        <is>
-          <t>+6 Laps</t>
-        </is>
-      </c>
-      <c r="L1798" t="inlineStr">
-        <is>
-          <t>1:22.970</t>
-        </is>
-      </c>
-    </row>
-    <row r="1799" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1799" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1799" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1799" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1798" t="s">
+        <v>427</v>
+      </c>
+      <c r="L1798" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1799" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1799" t="s">
+        <v>205</v>
       </c>
       <c r="D1799">
         <v>5</v>
       </c>
-      <c r="E1799" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1799" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1799" t="inlineStr">
-        <is>
-          <t>Gabriel Bortoleto</t>
-        </is>
-      </c>
-      <c r="H1799" t="inlineStr">
-        <is>
-          <t>Audi</t>
-        </is>
+      <c r="E1799" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1799" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1799" t="s">
+        <v>35</v>
+      </c>
+      <c r="H1799" t="s">
+        <v>198</v>
       </c>
       <c r="I1799">
         <v>20</v>
@@ -62036,55 +61749,37 @@
       <c r="J1799">
         <v>0</v>
       </c>
-      <c r="K1799" t="inlineStr">
-        <is>
-          <t>DNF</t>
-        </is>
-      </c>
-      <c r="L1799" t="inlineStr">
-        <is>
-          <t>1:26.621</t>
-        </is>
-      </c>
-    </row>
-    <row r="1800" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1800" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1800" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1800" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1799" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1799" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1800" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1800" t="s">
+        <v>205</v>
       </c>
       <c r="D1800">
         <v>5</v>
       </c>
-      <c r="E1800" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1800" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1800" t="inlineStr">
-        <is>
-          <t>Max Verstappen</t>
-        </is>
-      </c>
-      <c r="H1800" t="inlineStr">
-        <is>
-          <t>Red Bull</t>
-        </is>
+      <c r="E1800" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1800" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1800" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1800" t="s">
+        <v>135</v>
       </c>
       <c r="I1800">
         <v>21</v>
@@ -62092,55 +61787,37 @@
       <c r="J1800">
         <v>0</v>
       </c>
-      <c r="K1800" t="inlineStr">
-        <is>
-          <t>DNF</t>
-        </is>
-      </c>
-      <c r="L1800" t="inlineStr">
-        <is>
-          <t>1:25.731</t>
-        </is>
-      </c>
-    </row>
-    <row r="1801" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="A1801" t="inlineStr">
-        <is>
-          <t>F1 25: 2026 Season pack</t>
-        </is>
-      </c>
-      <c r="B1801" t="inlineStr">
-        <is>
-          <t>2026-T02</t>
-        </is>
-      </c>
-      <c r="C1801" t="inlineStr">
-        <is>
-          <t>Teikirise</t>
-        </is>
+      <c r="K1800" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1800" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A1801" t="s">
+        <v>197</v>
+      </c>
+      <c r="B1801" t="s">
+        <v>196</v>
+      </c>
+      <c r="C1801" t="s">
+        <v>205</v>
       </c>
       <c r="D1801">
         <v>5</v>
       </c>
-      <c r="E1801" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="F1801" t="inlineStr">
-        <is>
-          <t>Australian GP</t>
-        </is>
-      </c>
-      <c r="G1801" t="inlineStr">
-        <is>
-          <t>Polingua</t>
-        </is>
-      </c>
-      <c r="H1801" t="inlineStr">
-        <is>
-          <t>Red Bull</t>
-        </is>
+      <c r="E1801" t="s">
+        <v>207</v>
+      </c>
+      <c r="F1801" t="s">
+        <v>112</v>
+      </c>
+      <c r="G1801" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1801" t="s">
+        <v>135</v>
       </c>
       <c r="I1801">
         <v>22</v>
@@ -62148,18 +61825,14 @@
       <c r="J1801">
         <v>0</v>
       </c>
-      <c r="K1801" t="inlineStr">
-        <is>
-          <t>DNF</t>
-        </is>
-      </c>
-      <c r="L1801" t="inlineStr">
-        <is>
-          <t>1:35.614</t>
-        </is>
-      </c>
-    </row>
-    <row r="1802" spans="6:10" x14ac:dyDescent="0.45">
+      <c r="K1801" t="s">
+        <v>194</v>
+      </c>
+      <c r="L1801" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1802" t="s">
         <v>37</v>
       </c>
@@ -62167,7 +61840,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1803" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1803" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1803" t="s">
         <v>37</v>
       </c>
@@ -62175,7 +61848,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1804" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1804" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1804" t="s">
         <v>37</v>
       </c>
@@ -62183,7 +61856,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1805" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1805" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1805" t="s">
         <v>37</v>
       </c>
@@ -62191,7 +61864,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1806" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1806" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1806" t="s">
         <v>37</v>
       </c>
@@ -62199,7 +61872,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1807" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1807" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1807" t="s">
         <v>37</v>
       </c>
@@ -62207,7 +61880,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="1808" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="1808" spans="1:12" x14ac:dyDescent="0.45">
       <c r="F1808" t="s">
         <v>37</v>
       </c>
@@ -86678,10 +86351,8 @@
         <f t="shared" si="4"/>
         <v>Albert Park Circuit</v>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
+      <c r="F25" t="s">
+        <v>190</v>
       </c>
       <c r="G25" s="11">
         <v>0.25</v>
@@ -86860,11 +86531,11 @@
         <v>46313</v>
       </c>
       <c r="D31" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E31" t="str">
-        <f t="shared" si="5"/>
-        <v>Circuit de Barcelona-Catalunya</v>
+        <f t="shared" ref="E31" si="6">VLOOKUP(D31,$K$1:$L$43,2,FALSE)</f>
+        <v>Algarve International Circuit</v>
       </c>
       <c r="F31" t="s">
         <v>191</v>
@@ -87159,11 +86830,11 @@
         <v>46390</v>
       </c>
       <c r="D42" t="s">
-        <v>121</v>
+        <v>20</v>
       </c>
       <c r="E42" t="str">
-        <f t="shared" si="5"/>
-        <v>Circuit de Monaco</v>
+        <f t="shared" ref="E42" si="7">VLOOKUP(D42,$K$1:$L$43,2,FALSE)</f>
+        <v>Miami International Autodrome</v>
       </c>
       <c r="F42" t="s">
         <v>191</v>
@@ -87173,55 +86844,12 @@
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>205</v>
-      </c>
-      <c r="B43">
-        <f t="shared" si="1"/>
-        <v>23</v>
-      </c>
-      <c r="C43" s="8">
-        <v>46397</v>
-      </c>
-      <c r="D43" t="s">
-        <v>120</v>
-      </c>
-      <c r="E43" t="str">
-        <f t="shared" si="5"/>
-        <v>Algarve International Circuit</v>
-      </c>
-      <c r="F43" t="s">
-        <v>191</v>
-      </c>
-      <c r="G43" s="11">
-        <v>0.25</v>
-      </c>
+      <c r="C43" s="8"/>
+      <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>205</v>
-      </c>
-      <c r="B44">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
-      <c r="C44" s="8">
-        <f>C43+7</f>
-        <v>46404</v>
-      </c>
-      <c r="D44" t="s">
-        <v>20</v>
-      </c>
-      <c r="E44" t="str">
-        <f t="shared" si="5"/>
-        <v>Miami International Autodrome</v>
-      </c>
-      <c r="F44" t="s">
-        <v>191</v>
-      </c>
-      <c r="G44" s="11">
-        <v>0.25</v>
-      </c>
+      <c r="C44" s="8"/>
+      <c r="G44" s="11"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.45">
       <c r="C45" s="8"/>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ruiro\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dfb38b975c490ec7/Documents/GitHub/f1-game-dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{165239E0-7DB1-4443-8D6D-AA08C95311DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{0B843773-94E9-49D3-8F32-6702027EA788}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1EF9A62-3719-4F0A-AEAA-7864F6F7F673}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Leagues" sheetId="10" r:id="rId1"/>
@@ -53417,7 +53417,7 @@
         <v>207</v>
       </c>
       <c r="F1588" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1588" t="s">
         <v>1</v>
@@ -53456,7 +53456,7 @@
         <v>207</v>
       </c>
       <c r="F1589" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1589" t="s">
         <v>32</v>
@@ -53495,7 +53495,7 @@
         <v>207</v>
       </c>
       <c r="F1590" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1590" t="s">
         <v>3</v>
@@ -53534,7 +53534,7 @@
         <v>207</v>
       </c>
       <c r="F1591" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1591" t="s">
         <v>33</v>
@@ -53573,7 +53573,7 @@
         <v>207</v>
       </c>
       <c r="F1592" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1592" t="s">
         <v>7</v>
@@ -53612,7 +53612,7 @@
         <v>207</v>
       </c>
       <c r="F1593" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1593" t="s">
         <v>0</v>
@@ -53651,7 +53651,7 @@
         <v>207</v>
       </c>
       <c r="F1594" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1594" t="s">
         <v>4</v>
@@ -53690,7 +53690,7 @@
         <v>207</v>
       </c>
       <c r="F1595" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1595" t="s">
         <v>2</v>
@@ -53729,7 +53729,7 @@
         <v>207</v>
       </c>
       <c r="F1596" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1596" t="s">
         <v>6</v>
@@ -53768,7 +53768,7 @@
         <v>207</v>
       </c>
       <c r="F1597" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1597" t="s">
         <v>12</v>
@@ -53807,7 +53807,7 @@
         <v>207</v>
       </c>
       <c r="F1598" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1598" t="s">
         <v>34</v>
@@ -53846,7 +53846,7 @@
         <v>207</v>
       </c>
       <c r="F1599" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1599" t="s">
         <v>9</v>
@@ -53885,7 +53885,7 @@
         <v>207</v>
       </c>
       <c r="F1600" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1600" t="s">
         <v>10</v>
@@ -53924,7 +53924,7 @@
         <v>207</v>
       </c>
       <c r="F1601" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1601" t="s">
         <v>14</v>
@@ -53963,7 +53963,7 @@
         <v>207</v>
       </c>
       <c r="F1602" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1602" t="s">
         <v>5</v>
@@ -54002,7 +54002,7 @@
         <v>207</v>
       </c>
       <c r="F1603" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1603" t="s">
         <v>13</v>
@@ -54041,7 +54041,7 @@
         <v>207</v>
       </c>
       <c r="F1604" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1604" t="s">
         <v>11</v>
@@ -54080,7 +54080,7 @@
         <v>207</v>
       </c>
       <c r="F1605" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1605" t="s">
         <v>36</v>
@@ -54119,7 +54119,7 @@
         <v>207</v>
       </c>
       <c r="F1606" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1606" t="s">
         <v>35</v>
@@ -54157,7 +54157,7 @@
         <v>207</v>
       </c>
       <c r="F1607" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="G1607" t="s">
         <v>8</v>
@@ -54955,7 +54955,7 @@
         <v>207</v>
       </c>
       <c r="F1628" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1628" t="s">
         <v>33</v>
@@ -54993,7 +54993,7 @@
         <v>207</v>
       </c>
       <c r="F1629" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1629" t="s">
         <v>32</v>
@@ -55031,7 +55031,7 @@
         <v>207</v>
       </c>
       <c r="F1630" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1630" t="s">
         <v>34</v>
@@ -55069,7 +55069,7 @@
         <v>207</v>
       </c>
       <c r="F1631" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1631" t="s">
         <v>7</v>
@@ -55107,7 +55107,7 @@
         <v>207</v>
       </c>
       <c r="F1632" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1632" t="s">
         <v>0</v>
@@ -55145,7 +55145,7 @@
         <v>207</v>
       </c>
       <c r="F1633" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1633" t="s">
         <v>1</v>
@@ -55183,7 +55183,7 @@
         <v>207</v>
       </c>
       <c r="F1634" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1634" t="s">
         <v>4</v>
@@ -55221,7 +55221,7 @@
         <v>207</v>
       </c>
       <c r="F1635" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1635" t="s">
         <v>2</v>
@@ -55259,7 +55259,7 @@
         <v>207</v>
       </c>
       <c r="F1636" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1636" t="s">
         <v>6</v>
@@ -55297,7 +55297,7 @@
         <v>207</v>
       </c>
       <c r="F1637" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1637" t="s">
         <v>12</v>
@@ -55335,7 +55335,7 @@
         <v>207</v>
       </c>
       <c r="F1638" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1638" t="s">
         <v>3</v>
@@ -55373,7 +55373,7 @@
         <v>207</v>
       </c>
       <c r="F1639" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1639" t="s">
         <v>8</v>
@@ -55411,7 +55411,7 @@
         <v>207</v>
       </c>
       <c r="F1640" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1640" t="s">
         <v>10</v>
@@ -55449,7 +55449,7 @@
         <v>207</v>
       </c>
       <c r="F1641" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1641" t="s">
         <v>9</v>
@@ -55487,7 +55487,7 @@
         <v>207</v>
       </c>
       <c r="F1642" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1642" t="s">
         <v>5</v>
@@ -55525,7 +55525,7 @@
         <v>207</v>
       </c>
       <c r="F1643" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1643" t="s">
         <v>14</v>
@@ -55563,7 +55563,7 @@
         <v>207</v>
       </c>
       <c r="F1644" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1644" t="s">
         <v>35</v>
@@ -55601,7 +55601,7 @@
         <v>207</v>
       </c>
       <c r="F1645" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1645" t="s">
         <v>13</v>
@@ -55639,7 +55639,7 @@
         <v>207</v>
       </c>
       <c r="F1646" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1646" t="s">
         <v>36</v>
@@ -55677,7 +55677,7 @@
         <v>207</v>
       </c>
       <c r="F1647" t="s">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G1647" t="s">
         <v>11</v>
@@ -85689,7 +85689,7 @@
         <v>31</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B44" si="1">B2+1</f>
+        <f t="shared" ref="B3:B42" si="1">B2+1</f>
         <v>2</v>
       </c>
       <c r="C3" s="8">
@@ -86379,7 +86379,7 @@
         <v>113</v>
       </c>
       <c r="E26" t="str">
-        <f t="shared" ref="E26:E44" si="5">VLOOKUP(D26,$K$1:$L$43,2,FALSE)</f>
+        <f t="shared" ref="E26:E41" si="5">VLOOKUP(D26,$K$1:$L$43,2,FALSE)</f>
         <v>Circuit de Barcelona-Catalunya</v>
       </c>
       <c r="F26" t="s">

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -9696,8 +9696,10 @@
       <c r="E248" t="s">
         <v>207</v>
       </c>
-      <c r="F248" t="s">
-        <v>113</v>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G248" t="s">
         <v>55</v>
@@ -9728,8 +9730,10 @@
       <c r="E249" t="s">
         <v>207</v>
       </c>
-      <c r="F249" t="s">
-        <v>113</v>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G249" t="s">
         <v>68</v>
@@ -9760,8 +9764,10 @@
       <c r="E250" t="s">
         <v>207</v>
       </c>
-      <c r="F250" t="s">
-        <v>113</v>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G250" t="s">
         <v>45</v>
@@ -9792,8 +9798,10 @@
       <c r="E251" t="s">
         <v>207</v>
       </c>
-      <c r="F251" t="s">
-        <v>113</v>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G251" t="s">
         <v>6</v>
@@ -9824,8 +9832,10 @@
       <c r="E252" t="s">
         <v>207</v>
       </c>
-      <c r="F252" t="s">
-        <v>113</v>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G252" t="s">
         <v>2</v>
@@ -9856,8 +9866,10 @@
       <c r="E253" t="s">
         <v>207</v>
       </c>
-      <c r="F253" t="s">
-        <v>113</v>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G253" t="s">
         <v>110</v>
@@ -9888,8 +9900,10 @@
       <c r="E254" t="s">
         <v>207</v>
       </c>
-      <c r="F254" t="s">
-        <v>113</v>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G254" t="s">
         <v>43</v>
@@ -9920,8 +9934,10 @@
       <c r="E255" t="s">
         <v>207</v>
       </c>
-      <c r="F255" t="s">
-        <v>113</v>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G255" t="s">
         <v>5</v>
@@ -9952,8 +9968,10 @@
       <c r="E256" t="s">
         <v>207</v>
       </c>
-      <c r="F256" t="s">
-        <v>113</v>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G256" t="s">
         <v>8</v>
@@ -9984,8 +10002,10 @@
       <c r="E257" t="s">
         <v>207</v>
       </c>
-      <c r="F257" t="s">
-        <v>113</v>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G257" t="s">
         <v>48</v>
@@ -10016,8 +10036,10 @@
       <c r="E258" t="s">
         <v>207</v>
       </c>
-      <c r="F258" t="s">
-        <v>113</v>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G258" t="s">
         <v>70</v>
@@ -10048,8 +10070,10 @@
       <c r="E259" t="s">
         <v>207</v>
       </c>
-      <c r="F259" t="s">
-        <v>113</v>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G259" t="s">
         <v>4</v>
@@ -10080,8 +10104,10 @@
       <c r="E260" t="s">
         <v>207</v>
       </c>
-      <c r="F260" t="s">
-        <v>113</v>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G260" t="s">
         <v>33</v>
@@ -10112,8 +10138,10 @@
       <c r="E261" t="s">
         <v>207</v>
       </c>
-      <c r="F261" t="s">
-        <v>113</v>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G261" t="s">
         <v>34</v>
@@ -10144,8 +10172,10 @@
       <c r="E262" t="s">
         <v>207</v>
       </c>
-      <c r="F262" t="s">
-        <v>113</v>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G262" t="s">
         <v>71</v>
@@ -10176,8 +10206,10 @@
       <c r="E263" t="s">
         <v>207</v>
       </c>
-      <c r="F263" t="s">
-        <v>113</v>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G263" t="s">
         <v>9</v>
@@ -10208,8 +10240,10 @@
       <c r="E264" t="s">
         <v>207</v>
       </c>
-      <c r="F264" t="s">
-        <v>113</v>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G264" t="s">
         <v>69</v>
@@ -10240,8 +10274,10 @@
       <c r="E265" t="s">
         <v>207</v>
       </c>
-      <c r="F265" t="s">
-        <v>113</v>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G265" t="s">
         <v>3</v>
@@ -10272,8 +10308,10 @@
       <c r="E266" t="s">
         <v>207</v>
       </c>
-      <c r="F266" t="s">
-        <v>113</v>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G266" t="s">
         <v>32</v>
@@ -10304,8 +10342,10 @@
       <c r="E267" t="s">
         <v>207</v>
       </c>
-      <c r="F267" t="s">
-        <v>113</v>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G267" t="s">
         <v>11</v>
@@ -34656,8 +34696,10 @@
       <c r="E1028" t="s">
         <v>207</v>
       </c>
-      <c r="F1028" t="s">
-        <v>113</v>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1028" t="s">
         <v>1</v>
@@ -34688,8 +34730,10 @@
       <c r="E1029" t="s">
         <v>207</v>
       </c>
-      <c r="F1029" t="s">
-        <v>113</v>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1029" t="s">
         <v>7</v>
@@ -34720,8 +34764,10 @@
       <c r="E1030" t="s">
         <v>207</v>
       </c>
-      <c r="F1030" t="s">
-        <v>113</v>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1030" t="s">
         <v>85</v>
@@ -34752,8 +34798,10 @@
       <c r="E1031" t="s">
         <v>207</v>
       </c>
-      <c r="F1031" t="s">
-        <v>113</v>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1031" t="s">
         <v>32</v>
@@ -34784,8 +34832,10 @@
       <c r="E1032" t="s">
         <v>207</v>
       </c>
-      <c r="F1032" t="s">
-        <v>113</v>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1032" t="s">
         <v>0</v>
@@ -34816,8 +34866,10 @@
       <c r="E1033" t="s">
         <v>207</v>
       </c>
-      <c r="F1033" t="s">
-        <v>113</v>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1033" t="s">
         <v>6</v>
@@ -34848,8 +34900,10 @@
       <c r="E1034" t="s">
         <v>207</v>
       </c>
-      <c r="F1034" t="s">
-        <v>113</v>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1034" t="s">
         <v>2</v>
@@ -34880,8 +34934,10 @@
       <c r="E1035" t="s">
         <v>207</v>
       </c>
-      <c r="F1035" t="s">
-        <v>113</v>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1035" t="s">
         <v>4</v>
@@ -34912,8 +34968,10 @@
       <c r="E1036" t="s">
         <v>207</v>
       </c>
-      <c r="F1036" t="s">
-        <v>113</v>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1036" t="s">
         <v>3</v>
@@ -34944,8 +35002,10 @@
       <c r="E1037" t="s">
         <v>207</v>
       </c>
-      <c r="F1037" t="s">
-        <v>113</v>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1037" t="s">
         <v>68</v>
@@ -34976,8 +35036,10 @@
       <c r="E1038" t="s">
         <v>207</v>
       </c>
-      <c r="F1038" t="s">
-        <v>113</v>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1038" t="s">
         <v>36</v>
@@ -35008,8 +35070,10 @@
       <c r="E1039" t="s">
         <v>207</v>
       </c>
-      <c r="F1039" t="s">
-        <v>113</v>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1039" t="s">
         <v>86</v>
@@ -35040,8 +35104,10 @@
       <c r="E1040" t="s">
         <v>207</v>
       </c>
-      <c r="F1040" t="s">
-        <v>113</v>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1040" t="s">
         <v>5</v>
@@ -35072,8 +35138,10 @@
       <c r="E1041" t="s">
         <v>207</v>
       </c>
-      <c r="F1041" t="s">
-        <v>113</v>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1041" t="s">
         <v>9</v>
@@ -35104,8 +35172,10 @@
       <c r="E1042" t="s">
         <v>207</v>
       </c>
-      <c r="F1042" t="s">
-        <v>113</v>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1042" t="s">
         <v>8</v>
@@ -35136,8 +35206,10 @@
       <c r="E1043" t="s">
         <v>207</v>
       </c>
-      <c r="F1043" t="s">
-        <v>113</v>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1043" t="s">
         <v>13</v>
@@ -35168,8 +35240,10 @@
       <c r="E1044" t="s">
         <v>207</v>
       </c>
-      <c r="F1044" t="s">
-        <v>113</v>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1044" t="s">
         <v>10</v>
@@ -35200,8 +35274,10 @@
       <c r="E1045" t="s">
         <v>207</v>
       </c>
-      <c r="F1045" t="s">
-        <v>113</v>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1045" t="s">
         <v>12</v>
@@ -35232,8 +35308,10 @@
       <c r="E1046" t="s">
         <v>207</v>
       </c>
-      <c r="F1046" t="s">
-        <v>113</v>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1046" t="s">
         <v>33</v>
@@ -35264,8 +35342,10 @@
       <c r="E1047" t="s">
         <v>207</v>
       </c>
-      <c r="F1047" t="s">
-        <v>113</v>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1047" t="s">
         <v>34</v>
@@ -46816,8 +46896,10 @@
       <c r="E1408" t="s">
         <v>207</v>
       </c>
-      <c r="F1408" t="s">
-        <v>113</v>
+      <c r="F1408" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1408" t="s">
         <v>32</v>
@@ -46848,8 +46930,10 @@
       <c r="E1409" t="s">
         <v>207</v>
       </c>
-      <c r="F1409" t="s">
-        <v>113</v>
+      <c r="F1409" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1409" t="s">
         <v>34</v>
@@ -46880,8 +46964,10 @@
       <c r="E1410" t="s">
         <v>207</v>
       </c>
-      <c r="F1410" t="s">
-        <v>113</v>
+      <c r="F1410" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1410" t="s">
         <v>35</v>
@@ -46912,8 +46998,10 @@
       <c r="E1411" t="s">
         <v>207</v>
       </c>
-      <c r="F1411" t="s">
-        <v>113</v>
+      <c r="F1411" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1411" t="s">
         <v>5</v>
@@ -46944,8 +47032,10 @@
       <c r="E1412" t="s">
         <v>207</v>
       </c>
-      <c r="F1412" t="s">
-        <v>113</v>
+      <c r="F1412" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1412" t="s">
         <v>2</v>
@@ -46976,8 +47066,10 @@
       <c r="E1413" t="s">
         <v>207</v>
       </c>
-      <c r="F1413" t="s">
-        <v>113</v>
+      <c r="F1413" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1413" t="s">
         <v>3</v>
@@ -47008,8 +47100,10 @@
       <c r="E1414" t="s">
         <v>207</v>
       </c>
-      <c r="F1414" t="s">
-        <v>113</v>
+      <c r="F1414" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1414" t="s">
         <v>6</v>
@@ -47040,8 +47134,10 @@
       <c r="E1415" t="s">
         <v>207</v>
       </c>
-      <c r="F1415" t="s">
-        <v>113</v>
+      <c r="F1415" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1415" t="s">
         <v>0</v>
@@ -47072,8 +47168,10 @@
       <c r="E1416" t="s">
         <v>207</v>
       </c>
-      <c r="F1416" t="s">
-        <v>113</v>
+      <c r="F1416" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1416" t="s">
         <v>4</v>
@@ -47104,8 +47202,10 @@
       <c r="E1417" t="s">
         <v>207</v>
       </c>
-      <c r="F1417" t="s">
-        <v>113</v>
+      <c r="F1417" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1417" t="s">
         <v>33</v>
@@ -47136,8 +47236,10 @@
       <c r="E1418" t="s">
         <v>207</v>
       </c>
-      <c r="F1418" t="s">
-        <v>113</v>
+      <c r="F1418" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1418" t="s">
         <v>7</v>
@@ -47168,8 +47270,10 @@
       <c r="E1419" t="s">
         <v>207</v>
       </c>
-      <c r="F1419" t="s">
-        <v>113</v>
+      <c r="F1419" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1419" t="s">
         <v>12</v>
@@ -47200,8 +47304,10 @@
       <c r="E1420" t="s">
         <v>207</v>
       </c>
-      <c r="F1420" t="s">
-        <v>113</v>
+      <c r="F1420" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1420" t="s">
         <v>11</v>
@@ -47232,8 +47338,10 @@
       <c r="E1421" t="s">
         <v>207</v>
       </c>
-      <c r="F1421" t="s">
-        <v>113</v>
+      <c r="F1421" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1421" t="s">
         <v>9</v>
@@ -47264,8 +47372,10 @@
       <c r="E1422" t="s">
         <v>207</v>
       </c>
-      <c r="F1422" t="s">
-        <v>113</v>
+      <c r="F1422" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1422" t="s">
         <v>13</v>
@@ -47296,8 +47406,10 @@
       <c r="E1423" t="s">
         <v>207</v>
       </c>
-      <c r="F1423" t="s">
-        <v>113</v>
+      <c r="F1423" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1423" t="s">
         <v>14</v>
@@ -47328,8 +47440,10 @@
       <c r="E1424" t="s">
         <v>207</v>
       </c>
-      <c r="F1424" t="s">
-        <v>113</v>
+      <c r="F1424" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1424" t="s">
         <v>36</v>
@@ -47360,8 +47474,10 @@
       <c r="E1425" t="s">
         <v>207</v>
       </c>
-      <c r="F1425" t="s">
-        <v>113</v>
+      <c r="F1425" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1425" t="s">
         <v>1</v>
@@ -47392,8 +47508,10 @@
       <c r="E1426" t="s">
         <v>207</v>
       </c>
-      <c r="F1426" t="s">
-        <v>113</v>
+      <c r="F1426" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1426" t="s">
         <v>10</v>
@@ -47424,8 +47542,10 @@
       <c r="E1427" t="s">
         <v>207</v>
       </c>
-      <c r="F1427" t="s">
-        <v>113</v>
+      <c r="F1427" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="G1427" t="s">
         <v>8</v>
@@ -85869,8 +85989,10 @@
       <c r="C9" s="8">
         <v>46074</v>
       </c>
-      <c r="D9" t="s">
-        <v>113</v>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="2"/>
@@ -86375,8 +86497,10 @@
       <c r="C26" s="8">
         <v>46278</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>113</v>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="E26" t="str">
         <f t="shared" ref="E26:E41" si="5">VLOOKUP(D26,$K$1:$L$43,2,FALSE)</f>
@@ -86481,8 +86605,10 @@
       <c r="G29" s="11">
         <v>0.25</v>
       </c>
-      <c r="K29" t="s">
-        <v>113</v>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
       </c>
       <c r="L29" t="s">
         <v>157</v>
@@ -86636,8 +86762,10 @@
       <c r="G34" s="11">
         <v>0.25</v>
       </c>
-      <c r="K34" t="s">
-        <v>204</v>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Spanish GP</t>
+        </is>
       </c>
       <c r="L34" t="s">
         <v>203</v>
@@ -86804,8 +86932,10 @@
       <c r="C41" s="8">
         <v>46383</v>
       </c>
-      <c r="D41" t="s">
-        <v>204</v>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Spanish GP</t>
+        </is>
       </c>
       <c r="E41" t="str">
         <f t="shared" si="5"/>

--- a/F1_Standings.xlsx
+++ b/F1_Standings.xlsx
@@ -61953,179 +61953,1235 @@
       </c>
     </row>
     <row r="1802" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="F1802" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1802" t="s">
-        <v>37</v>
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1802">
+        <v>6</v>
+      </c>
+      <c r="E1802" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1802" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1802" t="inlineStr">
+        <is>
+          <t>TomasRodri21</t>
+        </is>
+      </c>
+      <c r="H1802" t="inlineStr">
+        <is>
+          <t>McLaren</t>
+        </is>
+      </c>
+      <c r="I1802">
+        <v>1</v>
+      </c>
+      <c r="J1802">
+        <v>25</v>
+      </c>
+      <c r="K1802" t="inlineStr">
+        <is>
+          <t>90:46.401</t>
+        </is>
+      </c>
+      <c r="L1802" t="inlineStr">
+        <is>
+          <t>1:18.091</t>
+        </is>
       </c>
     </row>
     <row r="1803" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="F1803" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1803" t="s">
-        <v>37</v>
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1803">
+        <v>6</v>
+      </c>
+      <c r="E1803" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1803" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1803" t="inlineStr">
+        <is>
+          <t>Polingua</t>
+        </is>
+      </c>
+      <c r="H1803" t="inlineStr">
+        <is>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="I1803">
+        <v>2</v>
+      </c>
+      <c r="J1803">
+        <v>18</v>
+      </c>
+      <c r="K1803" t="inlineStr">
+        <is>
+          <t>+28.697</t>
+        </is>
+      </c>
+      <c r="L1803" t="inlineStr">
+        <is>
+          <t>1:17.311</t>
+        </is>
       </c>
     </row>
     <row r="1804" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="F1804" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1804" t="s">
-        <v>37</v>
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1804">
+        <v>6</v>
+      </c>
+      <c r="E1804" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1804" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1804" t="inlineStr">
+        <is>
+          <t>Charles Leclerc</t>
+        </is>
+      </c>
+      <c r="H1804" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="I1804">
+        <v>3</v>
+      </c>
+      <c r="J1804">
+        <v>15</v>
+      </c>
+      <c r="K1804" t="inlineStr">
+        <is>
+          <t>+29.749</t>
+        </is>
+      </c>
+      <c r="L1804" t="inlineStr">
+        <is>
+          <t>1:19.163</t>
+        </is>
       </c>
     </row>
     <row r="1805" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="F1805" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1805" t="s">
-        <v>37</v>
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1805">
+        <v>6</v>
+      </c>
+      <c r="E1805" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1805" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1805" t="inlineStr">
+        <is>
+          <t>Kimi Antonelli</t>
+        </is>
+      </c>
+      <c r="H1805" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="I1805">
+        <v>4</v>
+      </c>
+      <c r="J1805">
+        <v>12</v>
+      </c>
+      <c r="K1805" t="inlineStr">
+        <is>
+          <t>+30.216</t>
+        </is>
+      </c>
+      <c r="L1805" t="inlineStr">
+        <is>
+          <t>1:19.234</t>
+        </is>
       </c>
     </row>
     <row r="1806" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="F1806" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1806" t="s">
-        <v>37</v>
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1806">
+        <v>6</v>
+      </c>
+      <c r="E1806" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1806" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1806" t="inlineStr">
+        <is>
+          <t>Lewis Hamilton</t>
+        </is>
+      </c>
+      <c r="H1806" t="inlineStr">
+        <is>
+          <t>Ferrari</t>
+        </is>
+      </c>
+      <c r="I1806">
+        <v>5</v>
+      </c>
+      <c r="J1806">
+        <v>10</v>
+      </c>
+      <c r="K1806" t="inlineStr">
+        <is>
+          <t>+33.751</t>
+        </is>
+      </c>
+      <c r="L1806" t="inlineStr">
+        <is>
+          <t>1:19.064</t>
+        </is>
       </c>
     </row>
     <row r="1807" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="F1807" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1807" t="s">
-        <v>37</v>
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1807">
+        <v>6</v>
+      </c>
+      <c r="E1807" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1807" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1807" t="inlineStr">
+        <is>
+          <t>Max Verstappen</t>
+        </is>
+      </c>
+      <c r="H1807" t="inlineStr">
+        <is>
+          <t>Red Bull</t>
+        </is>
+      </c>
+      <c r="I1807">
+        <v>6</v>
+      </c>
+      <c r="J1807">
+        <v>8</v>
+      </c>
+      <c r="K1807" t="inlineStr">
+        <is>
+          <t>+39.225</t>
+        </is>
+      </c>
+      <c r="L1807" t="inlineStr">
+        <is>
+          <t>1:19.240</t>
+        </is>
       </c>
     </row>
     <row r="1808" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="F1808" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1808" t="s">
-        <v>37</v>
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1808">
+        <v>6</v>
+      </c>
+      <c r="E1808" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1808" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1808" t="inlineStr">
+        <is>
+          <t>Carlos Sainz Jr.</t>
+        </is>
+      </c>
+      <c r="H1808" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="I1808">
+        <v>7</v>
+      </c>
+      <c r="J1808">
+        <v>6</v>
+      </c>
+      <c r="K1808" t="inlineStr">
+        <is>
+          <t>+58.210</t>
+        </is>
+      </c>
+      <c r="L1808" t="inlineStr">
+        <is>
+          <t>1:19.987</t>
+        </is>
       </c>
     </row>
     <row r="1809" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1809" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1809" t="s">
-        <v>37</v>
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1809">
+        <v>6</v>
+      </c>
+      <c r="E1809" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1809" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1809" t="inlineStr">
+        <is>
+          <t>Alexander Albon</t>
+        </is>
+      </c>
+      <c r="H1809" t="inlineStr">
+        <is>
+          <t>Williams</t>
+        </is>
+      </c>
+      <c r="I1809">
+        <v>8</v>
+      </c>
+      <c r="J1809">
+        <v>4</v>
+      </c>
+      <c r="K1809" t="inlineStr">
+        <is>
+          <t>+1:00.187</t>
+        </is>
+      </c>
+      <c r="L1809" t="inlineStr">
+        <is>
+          <t>1:19.975</t>
+        </is>
       </c>
     </row>
     <row r="1810" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1810" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1810" t="s">
-        <v>37</v>
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1810">
+        <v>6</v>
+      </c>
+      <c r="E1810" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1810" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1810" t="inlineStr">
+        <is>
+          <t>Pierre Gasly</t>
+        </is>
+      </c>
+      <c r="H1810" t="inlineStr">
+        <is>
+          <t>Alpine</t>
+        </is>
+      </c>
+      <c r="I1810">
+        <v>9</v>
+      </c>
+      <c r="J1810">
+        <v>2</v>
+      </c>
+      <c r="K1810" t="inlineStr">
+        <is>
+          <t>+1:13.080</t>
+        </is>
+      </c>
+      <c r="L1810" t="inlineStr">
+        <is>
+          <t>1:20.055</t>
+        </is>
       </c>
     </row>
     <row r="1811" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1811" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1811" t="s">
-        <v>37</v>
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1811">
+        <v>6</v>
+      </c>
+      <c r="E1811" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1811" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1811" t="inlineStr">
+        <is>
+          <t>Arvid Lidblad</t>
+        </is>
+      </c>
+      <c r="H1811" t="inlineStr">
+        <is>
+          <t>Racing Bulls</t>
+        </is>
+      </c>
+      <c r="I1811">
+        <v>10</v>
+      </c>
+      <c r="J1811">
+        <v>1</v>
+      </c>
+      <c r="K1811" t="inlineStr">
+        <is>
+          <t>+1:13.676</t>
+        </is>
+      </c>
+      <c r="L1811" t="inlineStr">
+        <is>
+          <t>1:20.558</t>
+        </is>
       </c>
     </row>
     <row r="1812" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1812" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1812" t="s">
-        <v>37</v>
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1812">
+        <v>6</v>
+      </c>
+      <c r="E1812" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1812" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1812" t="inlineStr">
+        <is>
+          <t>Franco Colapinto</t>
+        </is>
+      </c>
+      <c r="H1812" t="inlineStr">
+        <is>
+          <t>Alpine</t>
+        </is>
+      </c>
+      <c r="I1812">
+        <v>11</v>
+      </c>
+      <c r="J1812">
+        <v>0</v>
+      </c>
+      <c r="K1812" t="inlineStr">
+        <is>
+          <t>+1:21.947</t>
+        </is>
+      </c>
+      <c r="L1812" t="inlineStr">
+        <is>
+          <t>1:20.411</t>
+        </is>
       </c>
     </row>
     <row r="1813" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1813" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1813" t="s">
-        <v>37</v>
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1813">
+        <v>6</v>
+      </c>
+      <c r="E1813" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1813" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1813" t="inlineStr">
+        <is>
+          <t>Fernando Alonso</t>
+        </is>
+      </c>
+      <c r="H1813" t="inlineStr">
+        <is>
+          <t>Aston Martin</t>
+        </is>
+      </c>
+      <c r="I1813">
+        <v>12</v>
+      </c>
+      <c r="J1813">
+        <v>0</v>
+      </c>
+      <c r="K1813" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1813" t="inlineStr">
+        <is>
+          <t>1:20.130</t>
+        </is>
       </c>
     </row>
     <row r="1814" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1814" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1814" t="s">
-        <v>37</v>
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1814">
+        <v>6</v>
+      </c>
+      <c r="E1814" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1814" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1814" t="inlineStr">
+        <is>
+          <t>Nico Hülkenberg</t>
+        </is>
+      </c>
+      <c r="H1814" t="inlineStr">
+        <is>
+          <t>Audi</t>
+        </is>
+      </c>
+      <c r="I1814">
+        <v>13</v>
+      </c>
+      <c r="J1814">
+        <v>0</v>
+      </c>
+      <c r="K1814" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1814" t="inlineStr">
+        <is>
+          <t>1:20.555</t>
+        </is>
       </c>
     </row>
     <row r="1815" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1815" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1815" t="s">
-        <v>37</v>
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1815">
+        <v>6</v>
+      </c>
+      <c r="E1815" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1815" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1815" t="inlineStr">
+        <is>
+          <t>Sergio Perez</t>
+        </is>
+      </c>
+      <c r="H1815" t="inlineStr">
+        <is>
+          <t>Cadillac</t>
+        </is>
+      </c>
+      <c r="I1815">
+        <v>14</v>
+      </c>
+      <c r="J1815">
+        <v>0</v>
+      </c>
+      <c r="K1815" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1815" t="inlineStr">
+        <is>
+          <t>1:20.831</t>
+        </is>
       </c>
     </row>
     <row r="1816" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1816" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1816" t="s">
-        <v>37</v>
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1816">
+        <v>6</v>
+      </c>
+      <c r="E1816" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1816" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1816" t="inlineStr">
+        <is>
+          <t>Lance Stroll</t>
+        </is>
+      </c>
+      <c r="H1816" t="inlineStr">
+        <is>
+          <t>Aston Martin</t>
+        </is>
+      </c>
+      <c r="I1816">
+        <v>15</v>
+      </c>
+      <c r="J1816">
+        <v>0</v>
+      </c>
+      <c r="K1816" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1816" t="inlineStr">
+        <is>
+          <t>1:21.203</t>
+        </is>
       </c>
     </row>
     <row r="1817" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1817" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1817" t="s">
-        <v>37</v>
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1817">
+        <v>6</v>
+      </c>
+      <c r="E1817" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1817" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1817" t="inlineStr">
+        <is>
+          <t>Oliver Bearman</t>
+        </is>
+      </c>
+      <c r="H1817" t="inlineStr">
+        <is>
+          <t>Haas</t>
+        </is>
+      </c>
+      <c r="I1817">
+        <v>16</v>
+      </c>
+      <c r="J1817">
+        <v>0</v>
+      </c>
+      <c r="K1817" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1817" t="inlineStr">
+        <is>
+          <t>1:20.637</t>
+        </is>
       </c>
     </row>
     <row r="1818" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1818" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1818" t="s">
-        <v>37</v>
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1818">
+        <v>6</v>
+      </c>
+      <c r="E1818" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1818" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1818" t="inlineStr">
+        <is>
+          <t>Esteban Ocon</t>
+        </is>
+      </c>
+      <c r="H1818" t="inlineStr">
+        <is>
+          <t>Haas</t>
+        </is>
+      </c>
+      <c r="I1818">
+        <v>17</v>
+      </c>
+      <c r="J1818">
+        <v>0</v>
+      </c>
+      <c r="K1818" t="inlineStr">
+        <is>
+          <t>+1 Lap</t>
+        </is>
+      </c>
+      <c r="L1818" t="inlineStr">
+        <is>
+          <t>1:21.392</t>
+        </is>
       </c>
     </row>
     <row r="1819" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1819" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1819" t="s">
-        <v>37</v>
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1819">
+        <v>6</v>
+      </c>
+      <c r="E1819" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1819" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1819" t="inlineStr">
+        <is>
+          <t>Valtteri Bottas</t>
+        </is>
+      </c>
+      <c r="H1819" t="inlineStr">
+        <is>
+          <t>Cadillac</t>
+        </is>
+      </c>
+      <c r="I1819">
+        <v>18</v>
+      </c>
+      <c r="J1819">
+        <v>0</v>
+      </c>
+      <c r="K1819" t="inlineStr">
+        <is>
+          <t>+2 Laps</t>
+        </is>
+      </c>
+      <c r="L1819" t="inlineStr">
+        <is>
+          <t>1:21.630</t>
+        </is>
       </c>
     </row>
     <row r="1820" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1820" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1820" t="s">
-        <v>37</v>
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1820">
+        <v>6</v>
+      </c>
+      <c r="E1820" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1820" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1820" t="inlineStr">
+        <is>
+          <t>Gabriel Bortoleto</t>
+        </is>
+      </c>
+      <c r="H1820" t="inlineStr">
+        <is>
+          <t>Audi</t>
+        </is>
+      </c>
+      <c r="I1820">
+        <v>19</v>
+      </c>
+      <c r="J1820">
+        <v>0</v>
+      </c>
+      <c r="K1820" t="inlineStr">
+        <is>
+          <t>+2 Laps</t>
+        </is>
+      </c>
+      <c r="L1820" t="inlineStr">
+        <is>
+          <t>1:21.409</t>
+        </is>
       </c>
     </row>
     <row r="1821" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1821" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1821" t="s">
-        <v>37</v>
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1821">
+        <v>6</v>
+      </c>
+      <c r="E1821" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1821" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1821" t="inlineStr">
+        <is>
+          <t>Fatacuida</t>
+        </is>
+      </c>
+      <c r="H1821" t="inlineStr">
+        <is>
+          <t>Mercedes</t>
+        </is>
+      </c>
+      <c r="I1821">
+        <v>20</v>
+      </c>
+      <c r="J1821">
+        <v>0</v>
+      </c>
+      <c r="K1821" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1821" t="inlineStr">
+        <is>
+          <t>1:20.229</t>
+        </is>
       </c>
     </row>
     <row r="1822" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1822" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1822" t="s">
-        <v>37</v>
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1822">
+        <v>6</v>
+      </c>
+      <c r="E1822" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1822" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1822" t="inlineStr">
+        <is>
+          <t>Liam Lawson</t>
+        </is>
+      </c>
+      <c r="H1822" t="inlineStr">
+        <is>
+          <t>Racing Bulls</t>
+        </is>
+      </c>
+      <c r="I1822">
+        <v>21</v>
+      </c>
+      <c r="J1822">
+        <v>0</v>
+      </c>
+      <c r="K1822" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1822" t="inlineStr">
+        <is>
+          <t>1:20.825</t>
+        </is>
       </c>
     </row>
     <row r="1823" spans="6:10" x14ac:dyDescent="0.45">
-      <c r="F1823" t="s">
-        <v>37</v>
-      </c>
-      <c r="J1823" t="s">
-        <v>37</v>
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>F1 25: 2026 Season pack</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>2026-T02</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>Teikirise</t>
+        </is>
+      </c>
+      <c r="D1823">
+        <v>6</v>
+      </c>
+      <c r="E1823" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F1823" t="inlineStr">
+        <is>
+          <t>Barcelona-Catalunya GP</t>
+        </is>
+      </c>
+      <c r="G1823" t="inlineStr">
+        <is>
+          <t>Lando Norris</t>
+        </is>
+      </c>
+      <c r="H1823" t="inlineStr">
+        <is>
+          <t>McLaren</t>
+        </is>
+      </c>
+      <c r="I1823">
+        <v>22</v>
+      </c>
+      <c r="J1823">
+        <v>0</v>
+      </c>
+      <c r="K1823" t="inlineStr">
+        <is>
+          <t>DNF</t>
+        </is>
+      </c>
+      <c r="L1823" t="inlineStr">
+        <is>
+          <t>1:19.683</t>
+        </is>
       </c>
     </row>
     <row r="1824" spans="6:10" x14ac:dyDescent="0.45">
@@ -86506,8 +87562,10 @@
         <f t="shared" ref="E26:E41" si="5">VLOOKUP(D26,$K$1:$L$43,2,FALSE)</f>
         <v>Circuit de Barcelona-Catalunya</v>
       </c>
-      <c r="F26" t="s">
-        <v>191</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
       </c>
       <c r="G26" s="11">
         <v>0.25</v>
